--- a/reference/functions/spline_curve/waypoint.xlsx
+++ b/reference/functions/spline_curve/waypoint.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="26924"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70D906E4-BB9E-4E58-BE7A-8F14C442A4BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2085" yWindow="2085" windowWidth="21600" windowHeight="11100" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2085" yWindow="2085" windowWidth="21600" windowHeight="11100" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -19,13 +19,15 @@
     <sheet name="MyNewSheet" sheetId="4" r:id="rId4"/>
     <sheet name="new" sheetId="5" r:id="rId5"/>
     <sheet name="new40" sheetId="6" r:id="rId6"/>
+    <sheet name="fish" sheetId="7" r:id="rId10"/>
+    <sheet name="fish2" sheetId="8" r:id="rId11"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="162913" fullCalcOnLoad="true"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="24">
   <si>
     <t>x_wp</t>
     <phoneticPr fontId="1"/>
@@ -44,6 +46,30 @@
   </si>
   <si>
     <t>t</t>
+  </si>
+  <si>
+    <t>posi_1</t>
+  </si>
+  <si>
+    <t>posi_2</t>
+  </si>
+  <si>
+    <t>posi_3</t>
+  </si>
+  <si>
+    <t>time</t>
+  </si>
+  <si>
+    <t>posi_1</t>
+  </si>
+  <si>
+    <t>posi_2</t>
+  </si>
+  <si>
+    <t>posi_3</t>
+  </si>
+  <si>
+    <t>time</t>
   </si>
   <si>
     <t>posi_1</t>
@@ -114,7 +140,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -122,13 +148,15 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border/>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="22" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="true"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -446,7 +474,7 @@
   <dimension ref="A1:D26"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1">
       <c r="A1" s="1" t="s">
         <v>3</v>
       </c>
@@ -460,7 +488,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2">
       <c r="A2">
         <v>0</v>
       </c>
@@ -474,7 +502,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:4">
+    <row r="3">
       <c r="A3">
         <v>1.5</v>
       </c>
@@ -488,7 +516,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="4" spans="1:4">
+    <row r="4">
       <c r="A4">
         <v>3</v>
       </c>
@@ -502,7 +530,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:4">
+    <row r="5">
       <c r="A5">
         <v>4.5</v>
       </c>
@@ -516,7 +544,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="6" spans="1:4">
+    <row r="6">
       <c r="A6">
         <v>6</v>
       </c>
@@ -530,7 +558,7 @@
         <v>1.3</v>
       </c>
     </row>
-    <row r="7" spans="1:4">
+    <row r="7">
       <c r="A7">
         <v>7.5</v>
       </c>
@@ -544,7 +572,7 @@
         <v>1.4000000000000001</v>
       </c>
     </row>
-    <row r="8" spans="1:4">
+    <row r="8">
       <c r="A8">
         <v>9</v>
       </c>
@@ -558,7 +586,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="9" spans="1:4">
+    <row r="9">
       <c r="A9">
         <v>10.5</v>
       </c>
@@ -572,7 +600,7 @@
         <v>1.3</v>
       </c>
     </row>
-    <row r="10" spans="1:4">
+    <row r="10">
       <c r="A10">
         <v>12</v>
       </c>
@@ -586,7 +614,7 @@
         <v>1.2000000000000002</v>
       </c>
     </row>
-    <row r="11" spans="1:4">
+    <row r="11">
       <c r="A11">
         <v>13.5</v>
       </c>
@@ -600,7 +628,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:4">
+    <row r="12">
       <c r="A12">
         <v>15</v>
       </c>
@@ -614,7 +642,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="13" spans="1:4">
+    <row r="13">
       <c r="A13">
         <v>16.5</v>
       </c>
@@ -628,7 +656,7 @@
         <v>0.70000000000000007</v>
       </c>
     </row>
-    <row r="14" spans="1:4">
+    <row r="14">
       <c r="A14">
         <v>18</v>
       </c>
@@ -642,7 +670,7 @@
         <v>0.60000000000000009</v>
       </c>
     </row>
-    <row r="15" spans="1:4">
+    <row r="15">
       <c r="A15">
         <v>19.5</v>
       </c>
@@ -656,7 +684,7 @@
         <v>0.70000000000000007</v>
       </c>
     </row>
-    <row r="16" spans="1:4">
+    <row r="16">
       <c r="A16">
         <v>21</v>
       </c>
@@ -670,7 +698,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="17" spans="1:4">
+    <row r="17">
       <c r="A17">
         <v>22.5</v>
       </c>
@@ -684,7 +712,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:4">
+    <row r="18">
       <c r="A18">
         <v>24</v>
       </c>
@@ -698,7 +726,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="19" spans="1:4">
+    <row r="19">
       <c r="A19">
         <v>25.5</v>
       </c>
@@ -712,7 +740,7 @@
         <v>1.2000000000000002</v>
       </c>
     </row>
-    <row r="20" spans="1:4">
+    <row r="20">
       <c r="A20">
         <v>27</v>
       </c>
@@ -726,7 +754,7 @@
         <v>1.3</v>
       </c>
     </row>
-    <row r="21" spans="1:4">
+    <row r="21">
       <c r="A21">
         <v>28.5</v>
       </c>
@@ -740,7 +768,7 @@
         <v>1.2000000000000002</v>
       </c>
     </row>
-    <row r="22" spans="1:4">
+    <row r="22">
       <c r="A22">
         <v>30</v>
       </c>
@@ -754,7 +782,7 @@
         <v>1.3</v>
       </c>
     </row>
-    <row r="23" spans="1:4">
+    <row r="23">
       <c r="A23">
         <v>31.5</v>
       </c>
@@ -768,7 +796,7 @@
         <v>1.2000000000000002</v>
       </c>
     </row>
-    <row r="24" spans="1:4">
+    <row r="24">
       <c r="A24">
         <v>33</v>
       </c>
@@ -782,7 +810,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="25" spans="1:4">
+    <row r="25">
       <c r="A25">
         <v>34.5</v>
       </c>
@@ -796,7 +824,7 @@
         <v>1.05</v>
       </c>
     </row>
-    <row r="26" spans="1:4">
+    <row r="26">
       <c r="A26">
         <v>36</v>
       </c>
@@ -822,7 +850,7 @@
   <dimension ref="A1:D26"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1">
       <c r="A1" s="1" t="s">
         <v>3</v>
       </c>
@@ -836,7 +864,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2">
       <c r="A2">
         <v>0</v>
       </c>
@@ -850,7 +878,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:4">
+    <row r="3">
       <c r="A3">
         <v>2</v>
       </c>
@@ -864,7 +892,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="4" spans="1:4">
+    <row r="4">
       <c r="A4">
         <v>4</v>
       </c>
@@ -878,7 +906,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:4">
+    <row r="5">
       <c r="A5">
         <v>6</v>
       </c>
@@ -892,7 +920,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="6" spans="1:4">
+    <row r="6">
       <c r="A6">
         <v>8</v>
       </c>
@@ -906,7 +934,7 @@
         <v>1.3</v>
       </c>
     </row>
-    <row r="7" spans="1:4">
+    <row r="7">
       <c r="A7">
         <v>10</v>
       </c>
@@ -920,7 +948,7 @@
         <v>1.4000000000000001</v>
       </c>
     </row>
-    <row r="8" spans="1:4">
+    <row r="8">
       <c r="A8">
         <v>12</v>
       </c>
@@ -934,7 +962,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="9" spans="1:4">
+    <row r="9">
       <c r="A9">
         <v>14</v>
       </c>
@@ -948,7 +976,7 @@
         <v>1.3</v>
       </c>
     </row>
-    <row r="10" spans="1:4">
+    <row r="10">
       <c r="A10">
         <v>16</v>
       </c>
@@ -962,7 +990,7 @@
         <v>1.2000000000000002</v>
       </c>
     </row>
-    <row r="11" spans="1:4">
+    <row r="11">
       <c r="A11">
         <v>18</v>
       </c>
@@ -976,7 +1004,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:4">
+    <row r="12">
       <c r="A12">
         <v>20</v>
       </c>
@@ -990,7 +1018,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="13" spans="1:4">
+    <row r="13">
       <c r="A13">
         <v>22</v>
       </c>
@@ -1004,7 +1032,7 @@
         <v>0.70000000000000007</v>
       </c>
     </row>
-    <row r="14" spans="1:4">
+    <row r="14">
       <c r="A14">
         <v>24</v>
       </c>
@@ -1018,7 +1046,7 @@
         <v>0.60000000000000009</v>
       </c>
     </row>
-    <row r="15" spans="1:4">
+    <row r="15">
       <c r="A15">
         <v>26</v>
       </c>
@@ -1032,7 +1060,7 @@
         <v>0.70000000000000007</v>
       </c>
     </row>
-    <row r="16" spans="1:4">
+    <row r="16">
       <c r="A16">
         <v>28</v>
       </c>
@@ -1046,7 +1074,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="17" spans="1:4">
+    <row r="17">
       <c r="A17">
         <v>30</v>
       </c>
@@ -1060,7 +1088,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:4">
+    <row r="18">
       <c r="A18">
         <v>32</v>
       </c>
@@ -1074,7 +1102,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="19" spans="1:4">
+    <row r="19">
       <c r="A19">
         <v>34</v>
       </c>
@@ -1088,7 +1116,7 @@
         <v>1.2000000000000002</v>
       </c>
     </row>
-    <row r="20" spans="1:4">
+    <row r="20">
       <c r="A20">
         <v>36</v>
       </c>
@@ -1102,7 +1130,7 @@
         <v>1.3</v>
       </c>
     </row>
-    <row r="21" spans="1:4">
+    <row r="21">
       <c r="A21">
         <v>38</v>
       </c>
@@ -1116,7 +1144,7 @@
         <v>1.2000000000000002</v>
       </c>
     </row>
-    <row r="22" spans="1:4">
+    <row r="22">
       <c r="A22">
         <v>40</v>
       </c>
@@ -1130,7 +1158,7 @@
         <v>1.3</v>
       </c>
     </row>
-    <row r="23" spans="1:4">
+    <row r="23">
       <c r="A23">
         <v>42</v>
       </c>
@@ -1144,7 +1172,7 @@
         <v>1.2000000000000002</v>
       </c>
     </row>
-    <row r="24" spans="1:4">
+    <row r="24">
       <c r="A24">
         <v>44</v>
       </c>
@@ -1158,7 +1186,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="25" spans="1:4">
+    <row r="25">
       <c r="A25">
         <v>46</v>
       </c>
@@ -1172,7 +1200,7 @@
         <v>1.05</v>
       </c>
     </row>
-    <row r="26" spans="1:4">
+    <row r="26">
       <c r="A26">
         <v>48</v>
       </c>
@@ -1198,7 +1226,7 @@
   <dimension ref="A1:D26"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1">
       <c r="A1" s="1" t="s">
         <v>3</v>
       </c>
@@ -1212,7 +1240,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2">
       <c r="A2">
         <v>0</v>
       </c>
@@ -1226,7 +1254,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:4">
+    <row r="3">
       <c r="A3">
         <v>3</v>
       </c>
@@ -1240,7 +1268,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="4" spans="1:4">
+    <row r="4">
       <c r="A4">
         <v>6</v>
       </c>
@@ -1254,7 +1282,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:4">
+    <row r="5">
       <c r="A5">
         <v>9</v>
       </c>
@@ -1268,7 +1296,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="6" spans="1:4">
+    <row r="6">
       <c r="A6">
         <v>12</v>
       </c>
@@ -1282,7 +1310,7 @@
         <v>1.3</v>
       </c>
     </row>
-    <row r="7" spans="1:4">
+    <row r="7">
       <c r="A7">
         <v>15</v>
       </c>
@@ -1296,7 +1324,7 @@
         <v>1.4000000000000001</v>
       </c>
     </row>
-    <row r="8" spans="1:4">
+    <row r="8">
       <c r="A8">
         <v>18</v>
       </c>
@@ -1310,7 +1338,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="9" spans="1:4">
+    <row r="9">
       <c r="A9">
         <v>21</v>
       </c>
@@ -1324,7 +1352,7 @@
         <v>1.3</v>
       </c>
     </row>
-    <row r="10" spans="1:4">
+    <row r="10">
       <c r="A10">
         <v>24</v>
       </c>
@@ -1338,7 +1366,7 @@
         <v>1.2000000000000002</v>
       </c>
     </row>
-    <row r="11" spans="1:4">
+    <row r="11">
       <c r="A11">
         <v>27</v>
       </c>
@@ -1352,7 +1380,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:4">
+    <row r="12">
       <c r="A12">
         <v>30</v>
       </c>
@@ -1366,7 +1394,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="13" spans="1:4">
+    <row r="13">
       <c r="A13">
         <v>33</v>
       </c>
@@ -1380,7 +1408,7 @@
         <v>0.70000000000000007</v>
       </c>
     </row>
-    <row r="14" spans="1:4">
+    <row r="14">
       <c r="A14">
         <v>36</v>
       </c>
@@ -1394,7 +1422,7 @@
         <v>0.60000000000000009</v>
       </c>
     </row>
-    <row r="15" spans="1:4">
+    <row r="15">
       <c r="A15">
         <v>39</v>
       </c>
@@ -1408,7 +1436,7 @@
         <v>0.70000000000000007</v>
       </c>
     </row>
-    <row r="16" spans="1:4">
+    <row r="16">
       <c r="A16">
         <v>42</v>
       </c>
@@ -1422,7 +1450,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="17" spans="1:4">
+    <row r="17">
       <c r="A17">
         <v>45</v>
       </c>
@@ -1436,7 +1464,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:4">
+    <row r="18">
       <c r="A18">
         <v>48</v>
       </c>
@@ -1450,7 +1478,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="19" spans="1:4">
+    <row r="19">
       <c r="A19">
         <v>51</v>
       </c>
@@ -1464,7 +1492,7 @@
         <v>1.2000000000000002</v>
       </c>
     </row>
-    <row r="20" spans="1:4">
+    <row r="20">
       <c r="A20">
         <v>54</v>
       </c>
@@ -1478,7 +1506,7 @@
         <v>1.3</v>
       </c>
     </row>
-    <row r="21" spans="1:4">
+    <row r="21">
       <c r="A21">
         <v>57</v>
       </c>
@@ -1492,7 +1520,7 @@
         <v>1.2000000000000002</v>
       </c>
     </row>
-    <row r="22" spans="1:4">
+    <row r="22">
       <c r="A22">
         <v>60</v>
       </c>
@@ -1506,7 +1534,7 @@
         <v>1.3</v>
       </c>
     </row>
-    <row r="23" spans="1:4">
+    <row r="23">
       <c r="A23">
         <v>63</v>
       </c>
@@ -1520,7 +1548,7 @@
         <v>1.2000000000000002</v>
       </c>
     </row>
-    <row r="24" spans="1:4">
+    <row r="24">
       <c r="A24">
         <v>66</v>
       </c>
@@ -1534,7 +1562,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="25" spans="1:4">
+    <row r="25">
       <c r="A25">
         <v>69</v>
       </c>
@@ -1548,7 +1576,7 @@
         <v>1.05</v>
       </c>
     </row>
-    <row r="26" spans="1:4">
+    <row r="26">
       <c r="A26">
         <v>72</v>
       </c>
@@ -1574,11 +1602,11 @@
   <dimension ref="A1:D3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="2.140625" customWidth="1"/>
-    <col min="2" max="4" width="6.85546875" customWidth="1"/>
+    <col min="1" max="1" width="2.140625" customWidth="true"/>
+    <col min="2" max="4" width="6.85546875" customWidth="true"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1">
       <c r="A1" t="s">
         <v>4</v>
       </c>
@@ -1592,7 +1620,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2">
       <c r="A2">
         <v>0</v>
       </c>
@@ -1606,7 +1634,7 @@
         <v>0.60000000000000009</v>
       </c>
     </row>
-    <row r="3" spans="1:4">
+    <row r="3">
       <c r="A3">
         <v>5</v>
       </c>
@@ -1631,11 +1659,11 @@
   <dimension ref="A1:D31"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="5.28515625" customWidth="1"/>
-    <col min="2" max="4" width="6.85546875" customWidth="1"/>
+    <col min="1" max="1" width="5.28515625" customWidth="true"/>
+    <col min="2" max="4" width="6.85546875" customWidth="true"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1">
       <c r="A1" t="s">
         <v>8</v>
       </c>
@@ -1649,7 +1677,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2">
       <c r="A2">
         <v>0</v>
       </c>
@@ -1663,7 +1691,7 @@
         <v>0.45</v>
       </c>
     </row>
-    <row r="3" spans="1:4">
+    <row r="3">
       <c r="A3">
         <v>3</v>
       </c>
@@ -1677,7 +1705,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="4" spans="1:4">
+    <row r="4">
       <c r="A4">
         <v>6</v>
       </c>
@@ -1691,7 +1719,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="5" spans="1:4">
+    <row r="5">
       <c r="A5">
         <v>9</v>
       </c>
@@ -1705,7 +1733,7 @@
         <v>1.35</v>
       </c>
     </row>
-    <row r="6" spans="1:4">
+    <row r="6">
       <c r="A6">
         <v>12</v>
       </c>
@@ -1719,7 +1747,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="7" spans="1:4">
+    <row r="7">
       <c r="A7">
         <v>15</v>
       </c>
@@ -1733,7 +1761,7 @@
         <v>1.6500000000000001</v>
       </c>
     </row>
-    <row r="8" spans="1:4">
+    <row r="8">
       <c r="A8">
         <v>18</v>
       </c>
@@ -1747,7 +1775,7 @@
         <v>1.8</v>
       </c>
     </row>
-    <row r="9" spans="1:4">
+    <row r="9">
       <c r="A9">
         <v>21</v>
       </c>
@@ -1761,7 +1789,7 @@
         <v>1.7500000000000002</v>
       </c>
     </row>
-    <row r="10" spans="1:4">
+    <row r="10">
       <c r="A10">
         <v>24</v>
       </c>
@@ -1775,7 +1803,7 @@
         <v>1.6500000000000001</v>
       </c>
     </row>
-    <row r="11" spans="1:4">
+    <row r="11">
       <c r="A11">
         <v>27</v>
       </c>
@@ -1789,7 +1817,7 @@
         <v>1.3</v>
       </c>
     </row>
-    <row r="12" spans="1:4">
+    <row r="12">
       <c r="A12">
         <v>30</v>
       </c>
@@ -1803,7 +1831,7 @@
         <v>1.55</v>
       </c>
     </row>
-    <row r="13" spans="1:4">
+    <row r="13">
       <c r="A13">
         <v>33</v>
       </c>
@@ -1817,7 +1845,7 @@
         <v>1.6500000000000001</v>
       </c>
     </row>
-    <row r="14" spans="1:4">
+    <row r="14">
       <c r="A14">
         <v>36</v>
       </c>
@@ -1831,7 +1859,7 @@
         <v>1.7000000000000002</v>
       </c>
     </row>
-    <row r="15" spans="1:4">
+    <row r="15">
       <c r="A15">
         <v>39</v>
       </c>
@@ -1845,7 +1873,7 @@
         <v>1.4500000000000002</v>
       </c>
     </row>
-    <row r="16" spans="1:4">
+    <row r="16">
       <c r="A16">
         <v>42</v>
       </c>
@@ -1859,7 +1887,7 @@
         <v>1.3</v>
       </c>
     </row>
-    <row r="17" spans="1:4">
+    <row r="17">
       <c r="A17">
         <v>45</v>
       </c>
@@ -1873,7 +1901,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:4">
+    <row r="18">
       <c r="A18">
         <v>48</v>
       </c>
@@ -1887,7 +1915,7 @@
         <v>0.85000000000000009</v>
       </c>
     </row>
-    <row r="19" spans="1:4">
+    <row r="19">
       <c r="A19">
         <v>51</v>
       </c>
@@ -1901,7 +1929,7 @@
         <v>0.60000000000000009</v>
       </c>
     </row>
-    <row r="20" spans="1:4">
+    <row r="20">
       <c r="A20">
         <v>54</v>
       </c>
@@ -1915,7 +1943,7 @@
         <v>0.35000000000000003</v>
       </c>
     </row>
-    <row r="21" spans="1:4">
+    <row r="21">
       <c r="A21">
         <v>57</v>
       </c>
@@ -1929,7 +1957,7 @@
         <v>0.15000000000000002</v>
       </c>
     </row>
-    <row r="22" spans="1:4">
+    <row r="22">
       <c r="A22">
         <v>60</v>
       </c>
@@ -1943,7 +1971,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="23" spans="1:4">
+    <row r="23">
       <c r="A23">
         <v>63</v>
       </c>
@@ -1957,7 +1985,7 @@
         <v>0.45</v>
       </c>
     </row>
-    <row r="24" spans="1:4">
+    <row r="24">
       <c r="A24">
         <v>66</v>
       </c>
@@ -1971,7 +1999,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="25" spans="1:4">
+    <row r="25">
       <c r="A25">
         <v>69</v>
       </c>
@@ -1985,7 +2013,7 @@
         <v>0.70000000000000007</v>
       </c>
     </row>
-    <row r="26" spans="1:4">
+    <row r="26">
       <c r="A26">
         <v>72</v>
       </c>
@@ -1999,7 +2027,7 @@
         <v>0.35000000000000003</v>
       </c>
     </row>
-    <row r="27" spans="1:4">
+    <row r="27">
       <c r="A27">
         <v>75</v>
       </c>
@@ -2013,7 +2041,7 @@
         <v>0.55000000000000004</v>
       </c>
     </row>
-    <row r="28" spans="1:4">
+    <row r="28">
       <c r="A28">
         <v>78</v>
       </c>
@@ -2027,7 +2055,7 @@
         <v>0.85000000000000009</v>
       </c>
     </row>
-    <row r="29" spans="1:4">
+    <row r="29">
       <c r="A29">
         <v>81</v>
       </c>
@@ -2041,7 +2069,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="30" spans="1:4">
+    <row r="30">
       <c r="A30">
         <v>84</v>
       </c>
@@ -2055,7 +2083,7 @@
         <v>0.95000000000000007</v>
       </c>
     </row>
-    <row r="31" spans="1:4">
+    <row r="31">
       <c r="A31">
         <v>87</v>
       </c>
@@ -2080,11 +2108,11 @@
   <dimension ref="A1:D41"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="5.28515625" customWidth="1"/>
-    <col min="2" max="4" width="6.85546875" customWidth="1"/>
+    <col min="1" max="1" width="5.28515625" customWidth="true"/>
+    <col min="2" max="4" width="6.85546875" customWidth="true"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1">
       <c r="A1" t="s">
         <v>12</v>
       </c>
@@ -2098,7 +2126,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2">
       <c r="A2">
         <v>0</v>
       </c>
@@ -2112,7 +2140,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="3" spans="1:4">
+    <row r="3">
       <c r="A3">
         <v>2</v>
       </c>
@@ -2126,7 +2154,7 @@
         <v>0.30000000000000004</v>
       </c>
     </row>
-    <row r="4" spans="1:4">
+    <row r="4">
       <c r="A4">
         <v>4</v>
       </c>
@@ -2140,7 +2168,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="5" spans="1:4">
+    <row r="5">
       <c r="A5">
         <v>6</v>
       </c>
@@ -2154,7 +2182,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="6" spans="1:4">
+    <row r="6">
       <c r="A6">
         <v>8</v>
       </c>
@@ -2168,7 +2196,7 @@
         <v>0.30000000000000004</v>
       </c>
     </row>
-    <row r="7" spans="1:4">
+    <row r="7">
       <c r="A7">
         <v>10</v>
       </c>
@@ -2182,7 +2210,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:4">
+    <row r="8">
       <c r="A8">
         <v>12</v>
       </c>
@@ -2196,7 +2224,7 @@
         <v>1.2000000000000002</v>
       </c>
     </row>
-    <row r="9" spans="1:4">
+    <row r="9">
       <c r="A9">
         <v>14</v>
       </c>
@@ -2210,7 +2238,7 @@
         <v>1.2000000000000002</v>
       </c>
     </row>
-    <row r="10" spans="1:4">
+    <row r="10">
       <c r="A10">
         <v>16</v>
       </c>
@@ -2224,7 +2252,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="11" spans="1:4">
+    <row r="11">
       <c r="A11">
         <v>18</v>
       </c>
@@ -2238,7 +2266,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="12" spans="1:4">
+    <row r="12">
       <c r="A12">
         <v>20</v>
       </c>
@@ -2252,7 +2280,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="13" spans="1:4">
+    <row r="13">
       <c r="A13">
         <v>22</v>
       </c>
@@ -2266,7 +2294,7 @@
         <v>0.70000000000000007</v>
       </c>
     </row>
-    <row r="14" spans="1:4">
+    <row r="14">
       <c r="A14">
         <v>24</v>
       </c>
@@ -2280,7 +2308,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="15" spans="1:4">
+    <row r="15">
       <c r="A15">
         <v>26</v>
       </c>
@@ -2294,7 +2322,7 @@
         <v>1.2000000000000002</v>
       </c>
     </row>
-    <row r="16" spans="1:4">
+    <row r="16">
       <c r="A16">
         <v>28</v>
       </c>
@@ -2308,7 +2336,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="17" spans="1:4">
+    <row r="17">
       <c r="A17">
         <v>30</v>
       </c>
@@ -2322,7 +2350,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="18" spans="1:4">
+    <row r="18">
       <c r="A18">
         <v>32</v>
       </c>
@@ -2336,7 +2364,7 @@
         <v>1.3000000000000003</v>
       </c>
     </row>
-    <row r="19" spans="1:4">
+    <row r="19">
       <c r="A19">
         <v>34</v>
       </c>
@@ -2350,7 +2378,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="20" spans="1:4">
+    <row r="20">
       <c r="A20">
         <v>36</v>
       </c>
@@ -2364,7 +2392,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="21" spans="1:4">
+    <row r="21">
       <c r="A21">
         <v>38</v>
       </c>
@@ -2378,7 +2406,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="22" spans="1:4">
+    <row r="22">
       <c r="A22">
         <v>40</v>
       </c>
@@ -2392,7 +2420,7 @@
         <v>0.70000000000000007</v>
       </c>
     </row>
-    <row r="23" spans="1:4">
+    <row r="23">
       <c r="A23">
         <v>42</v>
       </c>
@@ -2406,7 +2434,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="24" spans="1:4">
+    <row r="24">
       <c r="A24">
         <v>44</v>
       </c>
@@ -2420,7 +2448,7 @@
         <v>1.5000000000000002</v>
       </c>
     </row>
-    <row r="25" spans="1:4">
+    <row r="25">
       <c r="A25">
         <v>46</v>
       </c>
@@ -2434,7 +2462,7 @@
         <v>1.2000000000000002</v>
       </c>
     </row>
-    <row r="26" spans="1:4">
+    <row r="26">
       <c r="A26">
         <v>48</v>
       </c>
@@ -2448,7 +2476,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="27" spans="1:4">
+    <row r="27">
       <c r="A27">
         <v>50</v>
       </c>
@@ -2462,7 +2490,7 @@
         <v>0.70000000000000007</v>
       </c>
     </row>
-    <row r="28" spans="1:4">
+    <row r="28">
       <c r="A28">
         <v>52</v>
       </c>
@@ -2476,7 +2504,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="29" spans="1:4">
+    <row r="29">
       <c r="A29">
         <v>54</v>
       </c>
@@ -2490,7 +2518,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="30" spans="1:4">
+    <row r="30">
       <c r="A30">
         <v>56</v>
       </c>
@@ -2504,7 +2532,7 @@
         <v>1.4000000000000001</v>
       </c>
     </row>
-    <row r="31" spans="1:4">
+    <row r="31">
       <c r="A31">
         <v>58</v>
       </c>
@@ -2518,7 +2546,7 @@
         <v>1.4000000000000001</v>
       </c>
     </row>
-    <row r="32" spans="1:4">
+    <row r="32">
       <c r="A32">
         <v>60</v>
       </c>
@@ -2532,7 +2560,7 @@
         <v>1.6</v>
       </c>
     </row>
-    <row r="33" spans="1:4">
+    <row r="33">
       <c r="A33">
         <v>62</v>
       </c>
@@ -2546,7 +2574,7 @@
         <v>1.6</v>
       </c>
     </row>
-    <row r="34" spans="1:4">
+    <row r="34">
       <c r="A34">
         <v>64</v>
       </c>
@@ -2560,7 +2588,7 @@
         <v>1.2000000000000002</v>
       </c>
     </row>
-    <row r="35" spans="1:4">
+    <row r="35">
       <c r="A35">
         <v>66</v>
       </c>
@@ -2574,7 +2602,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="36" spans="1:4">
+    <row r="36">
       <c r="A36">
         <v>68</v>
       </c>
@@ -2588,7 +2616,7 @@
         <v>0.60000000000000009</v>
       </c>
     </row>
-    <row r="37" spans="1:4">
+    <row r="37">
       <c r="A37">
         <v>70</v>
       </c>
@@ -2602,7 +2630,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="38" spans="1:4">
+    <row r="38">
       <c r="A38">
         <v>72</v>
       </c>
@@ -2616,7 +2644,7 @@
         <v>0.60000000000000009</v>
       </c>
     </row>
-    <row r="39" spans="1:4">
+    <row r="39">
       <c r="A39">
         <v>74</v>
       </c>
@@ -2630,7 +2658,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="40" spans="1:4">
+    <row r="40">
       <c r="A40">
         <v>76</v>
       </c>
@@ -2644,7 +2672,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="41" spans="1:4">
+    <row r="41">
       <c r="A41">
         <v>78</v>
       </c>
@@ -2662,4 +2690,944 @@
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:D34"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="4.89453125" customWidth="true"/>
+    <col min="2" max="2" width="6.62109375" customWidth="true"/>
+    <col min="3" max="3" width="6.62109375" customWidth="true"/>
+    <col min="4" max="4" width="6.62109375" customWidth="true"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" s="0" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="D1" s="0" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="0">
+        <v>0</v>
+      </c>
+      <c r="B2" s="0">
+        <v>0</v>
+      </c>
+      <c r="C2" s="0">
+        <v>-0</v>
+      </c>
+      <c r="D2" s="0">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="0">
+        <v>1.5</v>
+      </c>
+      <c r="B3" s="0">
+        <v>0.20000000000000001</v>
+      </c>
+      <c r="C3" s="0">
+        <v>0.29999999999999999</v>
+      </c>
+      <c r="D3" s="0">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="0">
+        <v>3</v>
+      </c>
+      <c r="B4" s="0">
+        <v>0.40000000000000002</v>
+      </c>
+      <c r="C4" s="0">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="D4" s="0">
+        <v>1.1000000000000001</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="0">
+        <v>4.5</v>
+      </c>
+      <c r="B5" s="0">
+        <v>0.85000000000000009</v>
+      </c>
+      <c r="C5" s="0">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="D5" s="0">
+        <v>1.1500000000000001</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="0">
+        <v>6</v>
+      </c>
+      <c r="B6" s="0">
+        <v>1.2000000000000002</v>
+      </c>
+      <c r="C6" s="0">
+        <v>0.30000000000000004</v>
+      </c>
+      <c r="D6" s="0">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="0">
+        <v>7.5</v>
+      </c>
+      <c r="B7" s="0">
+        <v>1.3</v>
+      </c>
+      <c r="C7" s="0">
+        <v>-0</v>
+      </c>
+      <c r="D7" s="0">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="0">
+        <v>9</v>
+      </c>
+      <c r="B8" s="0">
+        <v>1.2500000000000002</v>
+      </c>
+      <c r="C8" s="0">
+        <v>-0.35000000000000003</v>
+      </c>
+      <c r="D8" s="0">
+        <v>1.4000000000000001</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="0">
+        <v>10.5</v>
+      </c>
+      <c r="B9" s="0">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="C9" s="0">
+        <v>-0.60000000000000009</v>
+      </c>
+      <c r="D9" s="0">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="0">
+        <v>12</v>
+      </c>
+      <c r="B10" s="0">
+        <v>0.80000000000000004</v>
+      </c>
+      <c r="C10" s="0">
+        <v>-0.70000000000000007</v>
+      </c>
+      <c r="D10" s="0">
+        <v>1.2500000000000002</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="0">
+        <v>13.5</v>
+      </c>
+      <c r="B11" s="0">
+        <v>0.40000000000000002</v>
+      </c>
+      <c r="C11" s="0">
+        <v>-0.70000000000000007</v>
+      </c>
+      <c r="D11" s="0">
+        <v>1.1500000000000001</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="0">
+        <v>15</v>
+      </c>
+      <c r="B12" s="0">
+        <v>0.10000000000000001</v>
+      </c>
+      <c r="C12" s="0">
+        <v>-0.45000000000000001</v>
+      </c>
+      <c r="D12" s="0">
+        <v>1.05</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="0">
+        <v>16.5</v>
+      </c>
+      <c r="B13" s="0">
+        <v>-0.050000000000000003</v>
+      </c>
+      <c r="C13" s="0">
+        <v>-0.10000000000000001</v>
+      </c>
+      <c r="D13" s="0">
+        <v>0.95000000000000007</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="0">
+        <v>18</v>
+      </c>
+      <c r="B14" s="0">
+        <v>-0.25</v>
+      </c>
+      <c r="C14" s="0">
+        <v>0.35000000000000003</v>
+      </c>
+      <c r="D14" s="0">
+        <v>0.85000000000000009</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="0">
+        <v>19.5</v>
+      </c>
+      <c r="B15" s="0">
+        <v>-0.5</v>
+      </c>
+      <c r="C15" s="0">
+        <v>0.75000000000000011</v>
+      </c>
+      <c r="D15" s="0">
+        <v>0.80000000000000004</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="0">
+        <v>21</v>
+      </c>
+      <c r="B16" s="0">
+        <v>-0.85000000000000009</v>
+      </c>
+      <c r="C16" s="0">
+        <v>0.85000000000000009</v>
+      </c>
+      <c r="D16" s="0">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="0">
+        <v>22.5</v>
+      </c>
+      <c r="B17" s="0">
+        <v>-1.1500000000000001</v>
+      </c>
+      <c r="C17" s="0">
+        <v>0.75</v>
+      </c>
+      <c r="D17" s="0">
+        <v>0.70000000000000007</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="0">
+        <v>24</v>
+      </c>
+      <c r="B18" s="0">
+        <v>-1.3</v>
+      </c>
+      <c r="C18" s="0">
+        <v>0.60000000000000009</v>
+      </c>
+      <c r="D18" s="0">
+        <v>0.70000000000000007</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="0">
+        <v>25.5</v>
+      </c>
+      <c r="B19" s="0">
+        <v>-1.1000000000000001</v>
+      </c>
+      <c r="C19" s="0">
+        <v>0.35000000000000003</v>
+      </c>
+      <c r="D19" s="0">
+        <v>0.65000000000000002</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="0">
+        <v>27</v>
+      </c>
+      <c r="B20" s="0">
+        <v>-0.65000000000000013</v>
+      </c>
+      <c r="C20" s="0">
+        <v>0.29999999999999999</v>
+      </c>
+      <c r="D20" s="0">
+        <v>0.65000000000000013</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="0">
+        <v>28.5</v>
+      </c>
+      <c r="B21" s="0">
+        <v>-0.45000000000000001</v>
+      </c>
+      <c r="C21" s="0">
+        <v>0.10000000000000001</v>
+      </c>
+      <c r="D21" s="0">
+        <v>0.70000000000000007</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="0">
+        <v>30</v>
+      </c>
+      <c r="B22" s="0">
+        <v>-0.70000000000000007</v>
+      </c>
+      <c r="C22" s="0">
+        <v>0.050000000000000003</v>
+      </c>
+      <c r="D22" s="0">
+        <v>0.70000000000000007</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="0">
+        <v>31.5</v>
+      </c>
+      <c r="B23" s="0">
+        <v>-1.05</v>
+      </c>
+      <c r="C23" s="0">
+        <v>0</v>
+      </c>
+      <c r="D23" s="0">
+        <v>0.75000000000000011</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="0">
+        <v>33</v>
+      </c>
+      <c r="B24" s="0">
+        <v>-1.2500000000000002</v>
+      </c>
+      <c r="C24" s="0">
+        <v>-0.10000000000000001</v>
+      </c>
+      <c r="D24" s="0">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="0">
+        <v>34.5</v>
+      </c>
+      <c r="B25" s="0">
+        <v>-1.1500000000000001</v>
+      </c>
+      <c r="C25" s="0">
+        <v>-0.29999999999999999</v>
+      </c>
+      <c r="D25" s="0">
+        <v>0.80000000000000004</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="0">
+        <v>36</v>
+      </c>
+      <c r="B26" s="0">
+        <v>-0.90000000000000013</v>
+      </c>
+      <c r="C26" s="0">
+        <v>-0.35000000000000003</v>
+      </c>
+      <c r="D26" s="0">
+        <v>0.85000000000000009</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="0">
+        <v>37.5</v>
+      </c>
+      <c r="B27" s="0">
+        <v>-0.45000000000000001</v>
+      </c>
+      <c r="C27" s="0">
+        <v>-0.35000000000000003</v>
+      </c>
+      <c r="D27" s="0">
+        <v>0.85000000000000009</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="0">
+        <v>39</v>
+      </c>
+      <c r="B28" s="0">
+        <v>-0.45000000000000001</v>
+      </c>
+      <c r="C28" s="0">
+        <v>-0.5</v>
+      </c>
+      <c r="D28" s="0">
+        <v>0.90000000000000002</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="0">
+        <v>40.5</v>
+      </c>
+      <c r="B29" s="0">
+        <v>-0.70000000000000007</v>
+      </c>
+      <c r="C29" s="0">
+        <v>-0.55000000000000004</v>
+      </c>
+      <c r="D29" s="0">
+        <v>0.90000000000000002</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="0">
+        <v>42</v>
+      </c>
+      <c r="B30" s="0">
+        <v>-1.05</v>
+      </c>
+      <c r="C30" s="0">
+        <v>-0.70000000000000007</v>
+      </c>
+      <c r="D30" s="0">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="0">
+        <v>43.5</v>
+      </c>
+      <c r="B31" s="0">
+        <v>-0.95000000000000007</v>
+      </c>
+      <c r="C31" s="0">
+        <v>-0.90000000000000013</v>
+      </c>
+      <c r="D31" s="0">
+        <v>1.05</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="0">
+        <v>45</v>
+      </c>
+      <c r="B32" s="0">
+        <v>-0.60000000000000009</v>
+      </c>
+      <c r="C32" s="0">
+        <v>-1</v>
+      </c>
+      <c r="D32" s="0">
+        <v>1.1000000000000001</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="0">
+        <v>46.5</v>
+      </c>
+      <c r="B33" s="0">
+        <v>-0.20000000000000001</v>
+      </c>
+      <c r="C33" s="0">
+        <v>-0.80000000000000004</v>
+      </c>
+      <c r="D33" s="0">
+        <v>1.1000000000000001</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="0">
+        <v>48</v>
+      </c>
+      <c r="B34" s="0">
+        <v>-0</v>
+      </c>
+      <c r="C34" s="0">
+        <v>-0.45000000000000001</v>
+      </c>
+      <c r="D34" s="0">
+        <v>1.2000000000000002</v>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:D31"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="4.89453125" customWidth="true"/>
+    <col min="2" max="2" width="6.62109375" customWidth="true"/>
+    <col min="3" max="3" width="6.62109375" customWidth="true"/>
+    <col min="4" max="4" width="6.62109375" customWidth="true"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="B1" s="0" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1" s="0" t="s">
+        <v>22</v>
+      </c>
+      <c r="D1" s="0" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="0">
+        <v>0</v>
+      </c>
+      <c r="B2" s="0">
+        <v>0</v>
+      </c>
+      <c r="C2" s="0">
+        <v>-0</v>
+      </c>
+      <c r="D2" s="0">
+        <v>0.95000000000000007</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="0">
+        <v>1.5</v>
+      </c>
+      <c r="B3" s="0">
+        <v>0.15000000000000002</v>
+      </c>
+      <c r="C3" s="0">
+        <v>0.40000000000000002</v>
+      </c>
+      <c r="D3" s="0">
+        <v>1.1500000000000001</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="0">
+        <v>3</v>
+      </c>
+      <c r="B4" s="0">
+        <v>0.35000000000000003</v>
+      </c>
+      <c r="C4" s="0">
+        <v>0.70000000000000007</v>
+      </c>
+      <c r="D4" s="0">
+        <v>1.2500000000000002</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="0">
+        <v>4.5</v>
+      </c>
+      <c r="B5" s="0">
+        <v>0.90000000000000013</v>
+      </c>
+      <c r="C5" s="0">
+        <v>0.80000000000000004</v>
+      </c>
+      <c r="D5" s="0">
+        <v>1.3500000000000001</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="0">
+        <v>6</v>
+      </c>
+      <c r="B6" s="0">
+        <v>1.3500000000000001</v>
+      </c>
+      <c r="C6" s="0">
+        <v>0.30000000000000004</v>
+      </c>
+      <c r="D6" s="0">
+        <v>1.2000000000000002</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="0">
+        <v>7.5</v>
+      </c>
+      <c r="B7" s="0">
+        <v>1.4500000000000002</v>
+      </c>
+      <c r="C7" s="0">
+        <v>-0.15000000000000002</v>
+      </c>
+      <c r="D7" s="0">
+        <v>1.05</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="0">
+        <v>9</v>
+      </c>
+      <c r="B8" s="0">
+        <v>1.25</v>
+      </c>
+      <c r="C8" s="0">
+        <v>-0.70000000000000007</v>
+      </c>
+      <c r="D8" s="0">
+        <v>0.90000000000000002</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="0">
+        <v>10.5</v>
+      </c>
+      <c r="B9" s="0">
+        <v>0.90000000000000013</v>
+      </c>
+      <c r="C9" s="0">
+        <v>-0.95000000000000007</v>
+      </c>
+      <c r="D9" s="0">
+        <v>0.80000000000000004</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="0">
+        <v>12</v>
+      </c>
+      <c r="B10" s="0">
+        <v>0.40000000000000002</v>
+      </c>
+      <c r="C10" s="0">
+        <v>-0.75000000000000011</v>
+      </c>
+      <c r="D10" s="0">
+        <v>0.85000000000000009</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="0">
+        <v>13.5</v>
+      </c>
+      <c r="B11" s="0">
+        <v>0</v>
+      </c>
+      <c r="C11" s="0">
+        <v>-0.15000000000000002</v>
+      </c>
+      <c r="D11" s="0">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="0">
+        <v>15</v>
+      </c>
+      <c r="B12" s="0">
+        <v>-0.10000000000000001</v>
+      </c>
+      <c r="C12" s="0">
+        <v>0.25</v>
+      </c>
+      <c r="D12" s="0">
+        <v>1.1000000000000001</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="0">
+        <v>16.5</v>
+      </c>
+      <c r="B13" s="0">
+        <v>-0.35000000000000003</v>
+      </c>
+      <c r="C13" s="0">
+        <v>0.80000000000000004</v>
+      </c>
+      <c r="D13" s="0">
+        <v>1.2500000000000002</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="0">
+        <v>18</v>
+      </c>
+      <c r="B14" s="0">
+        <v>-0.75000000000000011</v>
+      </c>
+      <c r="C14" s="0">
+        <v>1.1500000000000001</v>
+      </c>
+      <c r="D14" s="0">
+        <v>1.1500000000000001</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="0">
+        <v>19.5</v>
+      </c>
+      <c r="B15" s="0">
+        <v>-1.1500000000000001</v>
+      </c>
+      <c r="C15" s="0">
+        <v>1.2500000000000002</v>
+      </c>
+      <c r="D15" s="0">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="0">
+        <v>21</v>
+      </c>
+      <c r="B16" s="0">
+        <v>-1.3500000000000001</v>
+      </c>
+      <c r="C16" s="0">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="D16" s="0">
+        <v>0.80000000000000004</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="0">
+        <v>22.5</v>
+      </c>
+      <c r="B17" s="0">
+        <v>-1.1500000000000001</v>
+      </c>
+      <c r="C17" s="0">
+        <v>0.70000000000000007</v>
+      </c>
+      <c r="D17" s="0">
+        <v>0.80000000000000004</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="0">
+        <v>24</v>
+      </c>
+      <c r="B18" s="0">
+        <v>-0.70000000000000007</v>
+      </c>
+      <c r="C18" s="0">
+        <v>0.45000000000000001</v>
+      </c>
+      <c r="D18" s="0">
+        <v>1.05</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="0">
+        <v>25.5</v>
+      </c>
+      <c r="B19" s="0">
+        <v>-0.29999999999999999</v>
+      </c>
+      <c r="C19" s="0">
+        <v>0.15000000000000002</v>
+      </c>
+      <c r="D19" s="0">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="0">
+        <v>27</v>
+      </c>
+      <c r="B20" s="0">
+        <v>-0.60000000000000009</v>
+      </c>
+      <c r="C20" s="0">
+        <v>-0</v>
+      </c>
+      <c r="D20" s="0">
+        <v>1.05</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="0">
+        <v>28.5</v>
+      </c>
+      <c r="B21" s="0">
+        <v>-1.05</v>
+      </c>
+      <c r="C21" s="0">
+        <v>0.29999999999999999</v>
+      </c>
+      <c r="D21" s="0">
+        <v>0.80000000000000004</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="0">
+        <v>30</v>
+      </c>
+      <c r="B22" s="0">
+        <v>-1.4000000000000001</v>
+      </c>
+      <c r="C22" s="0">
+        <v>0.15000000000000002</v>
+      </c>
+      <c r="D22" s="0">
+        <v>0.75000000000000011</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="0">
+        <v>31.5</v>
+      </c>
+      <c r="B23" s="0">
+        <v>-1.2000000000000002</v>
+      </c>
+      <c r="C23" s="0">
+        <v>-0.25</v>
+      </c>
+      <c r="D23" s="0">
+        <v>1.05</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="0">
+        <v>33</v>
+      </c>
+      <c r="B24" s="0">
+        <v>-0.45000000000000001</v>
+      </c>
+      <c r="C24" s="0">
+        <v>-0.40000000000000002</v>
+      </c>
+      <c r="D24" s="0">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="0">
+        <v>34.5</v>
+      </c>
+      <c r="B25" s="0">
+        <v>-0.60000000000000009</v>
+      </c>
+      <c r="C25" s="0">
+        <v>-0.75</v>
+      </c>
+      <c r="D25" s="0">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="0">
+        <v>36</v>
+      </c>
+      <c r="B26" s="0">
+        <v>-1.1500000000000001</v>
+      </c>
+      <c r="C26" s="0">
+        <v>-0.95000000000000007</v>
+      </c>
+      <c r="D26" s="0">
+        <v>0.85000000000000009</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="0">
+        <v>37.5</v>
+      </c>
+      <c r="B27" s="0">
+        <v>-1.1500000000000001</v>
+      </c>
+      <c r="C27" s="0">
+        <v>-1.3</v>
+      </c>
+      <c r="D27" s="0">
+        <v>0.90000000000000002</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="0">
+        <v>39</v>
+      </c>
+      <c r="B28" s="0">
+        <v>-0.35000000000000003</v>
+      </c>
+      <c r="C28" s="0">
+        <v>-1.2000000000000002</v>
+      </c>
+      <c r="D28" s="0">
+        <v>1.1000000000000001</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="0">
+        <v>40.5</v>
+      </c>
+      <c r="B29" s="0">
+        <v>-0.10000000000000001</v>
+      </c>
+      <c r="C29" s="0">
+        <v>-0.80000000000000004</v>
+      </c>
+      <c r="D29" s="0">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="0">
+        <v>42</v>
+      </c>
+      <c r="B30" s="0">
+        <v>0</v>
+      </c>
+      <c r="C30" s="0">
+        <v>-0.40000000000000002</v>
+      </c>
+      <c r="D30" s="0">
+        <v>1.05</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="0">
+        <v>43.5</v>
+      </c>
+      <c r="B31" s="0">
+        <v>-0.29999999999999999</v>
+      </c>
+      <c r="C31" s="0">
+        <v>-0.15000000000000002</v>
+      </c>
+      <c r="D31" s="0">
+        <v>0.90000000000000013</v>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
 </file>
--- a/reference/functions/spline_curve/waypoint.xlsx
+++ b/reference/functions/spline_curve/waypoint.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="26924"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70D906E4-BB9E-4E58-BE7A-8F14C442A4BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2085" yWindow="2085" windowWidth="21600" windowHeight="11100" activeTab="5"/>
+    <workbookView xWindow="2085" yWindow="2085" windowWidth="21600" windowHeight="11100" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -19,15 +19,13 @@
     <sheet name="MyNewSheet" sheetId="4" r:id="rId4"/>
     <sheet name="new" sheetId="5" r:id="rId5"/>
     <sheet name="new40" sheetId="6" r:id="rId6"/>
-    <sheet name="fish" sheetId="7" r:id="rId10"/>
-    <sheet name="fish2" sheetId="8" r:id="rId11"/>
   </sheets>
-  <calcPr calcId="162913" fullCalcOnLoad="true"/>
+  <calcPr calcId="162913"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="16">
   <si>
     <t>x_wp</t>
     <phoneticPr fontId="1"/>
@@ -46,30 +44,6 @@
   </si>
   <si>
     <t>t</t>
-  </si>
-  <si>
-    <t>posi_1</t>
-  </si>
-  <si>
-    <t>posi_2</t>
-  </si>
-  <si>
-    <t>posi_3</t>
-  </si>
-  <si>
-    <t>time</t>
-  </si>
-  <si>
-    <t>posi_1</t>
-  </si>
-  <si>
-    <t>posi_2</t>
-  </si>
-  <si>
-    <t>posi_3</t>
-  </si>
-  <si>
-    <t>time</t>
   </si>
   <si>
     <t>posi_1</t>
@@ -140,7 +114,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -148,15 +122,13 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border/>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="true"/>
-    <xf numFmtId="22" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="true"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -474,7 +446,7 @@
   <dimension ref="A1:D26"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
         <v>3</v>
       </c>
@@ -488,7 +460,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:4">
       <c r="A2">
         <v>0</v>
       </c>
@@ -502,7 +474,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:4">
       <c r="A3">
         <v>1.5</v>
       </c>
@@ -516,7 +488,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:4">
       <c r="A4">
         <v>3</v>
       </c>
@@ -530,7 +502,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:4">
       <c r="A5">
         <v>4.5</v>
       </c>
@@ -544,7 +516,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:4">
       <c r="A6">
         <v>6</v>
       </c>
@@ -558,7 +530,7 @@
         <v>1.3</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:4">
       <c r="A7">
         <v>7.5</v>
       </c>
@@ -572,7 +544,7 @@
         <v>1.4000000000000001</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:4">
       <c r="A8">
         <v>9</v>
       </c>
@@ -586,7 +558,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:4">
       <c r="A9">
         <v>10.5</v>
       </c>
@@ -600,7 +572,7 @@
         <v>1.3</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:4">
       <c r="A10">
         <v>12</v>
       </c>
@@ -614,7 +586,7 @@
         <v>1.2000000000000002</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:4">
       <c r="A11">
         <v>13.5</v>
       </c>
@@ -628,7 +600,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:4">
       <c r="A12">
         <v>15</v>
       </c>
@@ -642,7 +614,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:4">
       <c r="A13">
         <v>16.5</v>
       </c>
@@ -656,7 +628,7 @@
         <v>0.70000000000000007</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:4">
       <c r="A14">
         <v>18</v>
       </c>
@@ -670,7 +642,7 @@
         <v>0.60000000000000009</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:4">
       <c r="A15">
         <v>19.5</v>
       </c>
@@ -684,7 +656,7 @@
         <v>0.70000000000000007</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:4">
       <c r="A16">
         <v>21</v>
       </c>
@@ -698,7 +670,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" spans="1:4">
       <c r="A17">
         <v>22.5</v>
       </c>
@@ -712,7 +684,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" spans="1:4">
       <c r="A18">
         <v>24</v>
       </c>
@@ -726,7 +698,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" spans="1:4">
       <c r="A19">
         <v>25.5</v>
       </c>
@@ -740,7 +712,7 @@
         <v>1.2000000000000002</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" spans="1:4">
       <c r="A20">
         <v>27</v>
       </c>
@@ -754,7 +726,7 @@
         <v>1.3</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" spans="1:4">
       <c r="A21">
         <v>28.5</v>
       </c>
@@ -768,7 +740,7 @@
         <v>1.2000000000000002</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" spans="1:4">
       <c r="A22">
         <v>30</v>
       </c>
@@ -782,7 +754,7 @@
         <v>1.3</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" spans="1:4">
       <c r="A23">
         <v>31.5</v>
       </c>
@@ -796,7 +768,7 @@
         <v>1.2000000000000002</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" spans="1:4">
       <c r="A24">
         <v>33</v>
       </c>
@@ -810,7 +782,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" spans="1:4">
       <c r="A25">
         <v>34.5</v>
       </c>
@@ -824,7 +796,7 @@
         <v>1.05</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" spans="1:4">
       <c r="A26">
         <v>36</v>
       </c>
@@ -850,7 +822,7 @@
   <dimension ref="A1:D26"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
         <v>3</v>
       </c>
@@ -864,7 +836,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:4">
       <c r="A2">
         <v>0</v>
       </c>
@@ -878,7 +850,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:4">
       <c r="A3">
         <v>2</v>
       </c>
@@ -892,7 +864,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:4">
       <c r="A4">
         <v>4</v>
       </c>
@@ -906,7 +878,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:4">
       <c r="A5">
         <v>6</v>
       </c>
@@ -920,7 +892,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:4">
       <c r="A6">
         <v>8</v>
       </c>
@@ -934,7 +906,7 @@
         <v>1.3</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:4">
       <c r="A7">
         <v>10</v>
       </c>
@@ -948,7 +920,7 @@
         <v>1.4000000000000001</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:4">
       <c r="A8">
         <v>12</v>
       </c>
@@ -962,7 +934,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:4">
       <c r="A9">
         <v>14</v>
       </c>
@@ -976,7 +948,7 @@
         <v>1.3</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:4">
       <c r="A10">
         <v>16</v>
       </c>
@@ -990,7 +962,7 @@
         <v>1.2000000000000002</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:4">
       <c r="A11">
         <v>18</v>
       </c>
@@ -1004,7 +976,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:4">
       <c r="A12">
         <v>20</v>
       </c>
@@ -1018,7 +990,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:4">
       <c r="A13">
         <v>22</v>
       </c>
@@ -1032,7 +1004,7 @@
         <v>0.70000000000000007</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:4">
       <c r="A14">
         <v>24</v>
       </c>
@@ -1046,7 +1018,7 @@
         <v>0.60000000000000009</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:4">
       <c r="A15">
         <v>26</v>
       </c>
@@ -1060,7 +1032,7 @@
         <v>0.70000000000000007</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:4">
       <c r="A16">
         <v>28</v>
       </c>
@@ -1074,7 +1046,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" spans="1:4">
       <c r="A17">
         <v>30</v>
       </c>
@@ -1088,7 +1060,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" spans="1:4">
       <c r="A18">
         <v>32</v>
       </c>
@@ -1102,7 +1074,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" spans="1:4">
       <c r="A19">
         <v>34</v>
       </c>
@@ -1116,7 +1088,7 @@
         <v>1.2000000000000002</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" spans="1:4">
       <c r="A20">
         <v>36</v>
       </c>
@@ -1130,7 +1102,7 @@
         <v>1.3</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" spans="1:4">
       <c r="A21">
         <v>38</v>
       </c>
@@ -1144,7 +1116,7 @@
         <v>1.2000000000000002</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" spans="1:4">
       <c r="A22">
         <v>40</v>
       </c>
@@ -1158,7 +1130,7 @@
         <v>1.3</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" spans="1:4">
       <c r="A23">
         <v>42</v>
       </c>
@@ -1172,7 +1144,7 @@
         <v>1.2000000000000002</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" spans="1:4">
       <c r="A24">
         <v>44</v>
       </c>
@@ -1186,7 +1158,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" spans="1:4">
       <c r="A25">
         <v>46</v>
       </c>
@@ -1200,7 +1172,7 @@
         <v>1.05</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" spans="1:4">
       <c r="A26">
         <v>48</v>
       </c>
@@ -1226,7 +1198,7 @@
   <dimension ref="A1:D26"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
         <v>3</v>
       </c>
@@ -1240,7 +1212,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:4">
       <c r="A2">
         <v>0</v>
       </c>
@@ -1254,7 +1226,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:4">
       <c r="A3">
         <v>3</v>
       </c>
@@ -1268,7 +1240,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:4">
       <c r="A4">
         <v>6</v>
       </c>
@@ -1282,7 +1254,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:4">
       <c r="A5">
         <v>9</v>
       </c>
@@ -1296,7 +1268,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:4">
       <c r="A6">
         <v>12</v>
       </c>
@@ -1310,7 +1282,7 @@
         <v>1.3</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:4">
       <c r="A7">
         <v>15</v>
       </c>
@@ -1324,7 +1296,7 @@
         <v>1.4000000000000001</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:4">
       <c r="A8">
         <v>18</v>
       </c>
@@ -1338,7 +1310,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:4">
       <c r="A9">
         <v>21</v>
       </c>
@@ -1352,7 +1324,7 @@
         <v>1.3</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:4">
       <c r="A10">
         <v>24</v>
       </c>
@@ -1366,7 +1338,7 @@
         <v>1.2000000000000002</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:4">
       <c r="A11">
         <v>27</v>
       </c>
@@ -1380,7 +1352,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:4">
       <c r="A12">
         <v>30</v>
       </c>
@@ -1394,7 +1366,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:4">
       <c r="A13">
         <v>33</v>
       </c>
@@ -1408,7 +1380,7 @@
         <v>0.70000000000000007</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:4">
       <c r="A14">
         <v>36</v>
       </c>
@@ -1422,7 +1394,7 @@
         <v>0.60000000000000009</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:4">
       <c r="A15">
         <v>39</v>
       </c>
@@ -1436,7 +1408,7 @@
         <v>0.70000000000000007</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:4">
       <c r="A16">
         <v>42</v>
       </c>
@@ -1450,7 +1422,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" spans="1:4">
       <c r="A17">
         <v>45</v>
       </c>
@@ -1464,7 +1436,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" spans="1:4">
       <c r="A18">
         <v>48</v>
       </c>
@@ -1478,7 +1450,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" spans="1:4">
       <c r="A19">
         <v>51</v>
       </c>
@@ -1492,7 +1464,7 @@
         <v>1.2000000000000002</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" spans="1:4">
       <c r="A20">
         <v>54</v>
       </c>
@@ -1506,7 +1478,7 @@
         <v>1.3</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" spans="1:4">
       <c r="A21">
         <v>57</v>
       </c>
@@ -1520,7 +1492,7 @@
         <v>1.2000000000000002</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" spans="1:4">
       <c r="A22">
         <v>60</v>
       </c>
@@ -1534,7 +1506,7 @@
         <v>1.3</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" spans="1:4">
       <c r="A23">
         <v>63</v>
       </c>
@@ -1548,7 +1520,7 @@
         <v>1.2000000000000002</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" spans="1:4">
       <c r="A24">
         <v>66</v>
       </c>
@@ -1562,7 +1534,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" spans="1:4">
       <c r="A25">
         <v>69</v>
       </c>
@@ -1576,7 +1548,7 @@
         <v>1.05</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" spans="1:4">
       <c r="A26">
         <v>72</v>
       </c>
@@ -1602,11 +1574,11 @@
   <dimension ref="A1:D3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="2.140625" customWidth="true"/>
-    <col min="2" max="4" width="6.85546875" customWidth="true"/>
+    <col min="1" max="1" width="2.140625" customWidth="1"/>
+    <col min="2" max="4" width="6.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:4">
       <c r="A1" t="s">
         <v>4</v>
       </c>
@@ -1620,7 +1592,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:4">
       <c r="A2">
         <v>0</v>
       </c>
@@ -1634,7 +1606,7 @@
         <v>0.60000000000000009</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:4">
       <c r="A3">
         <v>5</v>
       </c>
@@ -1659,11 +1631,11 @@
   <dimension ref="A1:D31"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="5.28515625" customWidth="true"/>
-    <col min="2" max="4" width="6.85546875" customWidth="true"/>
+    <col min="1" max="1" width="5.28515625" customWidth="1"/>
+    <col min="2" max="4" width="6.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:4">
       <c r="A1" t="s">
         <v>8</v>
       </c>
@@ -1677,7 +1649,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:4">
       <c r="A2">
         <v>0</v>
       </c>
@@ -1691,7 +1663,7 @@
         <v>0.45</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:4">
       <c r="A3">
         <v>3</v>
       </c>
@@ -1705,7 +1677,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:4">
       <c r="A4">
         <v>6</v>
       </c>
@@ -1719,7 +1691,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:4">
       <c r="A5">
         <v>9</v>
       </c>
@@ -1733,7 +1705,7 @@
         <v>1.35</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:4">
       <c r="A6">
         <v>12</v>
       </c>
@@ -1747,7 +1719,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:4">
       <c r="A7">
         <v>15</v>
       </c>
@@ -1761,7 +1733,7 @@
         <v>1.6500000000000001</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:4">
       <c r="A8">
         <v>18</v>
       </c>
@@ -1775,7 +1747,7 @@
         <v>1.8</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:4">
       <c r="A9">
         <v>21</v>
       </c>
@@ -1789,7 +1761,7 @@
         <v>1.7500000000000002</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:4">
       <c r="A10">
         <v>24</v>
       </c>
@@ -1803,7 +1775,7 @@
         <v>1.6500000000000001</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:4">
       <c r="A11">
         <v>27</v>
       </c>
@@ -1817,7 +1789,7 @@
         <v>1.3</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:4">
       <c r="A12">
         <v>30</v>
       </c>
@@ -1831,7 +1803,7 @@
         <v>1.55</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:4">
       <c r="A13">
         <v>33</v>
       </c>
@@ -1845,7 +1817,7 @@
         <v>1.6500000000000001</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:4">
       <c r="A14">
         <v>36</v>
       </c>
@@ -1859,7 +1831,7 @@
         <v>1.7000000000000002</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:4">
       <c r="A15">
         <v>39</v>
       </c>
@@ -1873,7 +1845,7 @@
         <v>1.4500000000000002</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:4">
       <c r="A16">
         <v>42</v>
       </c>
@@ -1887,7 +1859,7 @@
         <v>1.3</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" spans="1:4">
       <c r="A17">
         <v>45</v>
       </c>
@@ -1901,7 +1873,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" spans="1:4">
       <c r="A18">
         <v>48</v>
       </c>
@@ -1915,7 +1887,7 @@
         <v>0.85000000000000009</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" spans="1:4">
       <c r="A19">
         <v>51</v>
       </c>
@@ -1929,7 +1901,7 @@
         <v>0.60000000000000009</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" spans="1:4">
       <c r="A20">
         <v>54</v>
       </c>
@@ -1943,7 +1915,7 @@
         <v>0.35000000000000003</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" spans="1:4">
       <c r="A21">
         <v>57</v>
       </c>
@@ -1957,7 +1929,7 @@
         <v>0.15000000000000002</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" spans="1:4">
       <c r="A22">
         <v>60</v>
       </c>
@@ -1971,7 +1943,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" spans="1:4">
       <c r="A23">
         <v>63</v>
       </c>
@@ -1985,7 +1957,7 @@
         <v>0.45</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" spans="1:4">
       <c r="A24">
         <v>66</v>
       </c>
@@ -1999,7 +1971,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" spans="1:4">
       <c r="A25">
         <v>69</v>
       </c>
@@ -2013,7 +1985,7 @@
         <v>0.70000000000000007</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" spans="1:4">
       <c r="A26">
         <v>72</v>
       </c>
@@ -2027,7 +1999,7 @@
         <v>0.35000000000000003</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" spans="1:4">
       <c r="A27">
         <v>75</v>
       </c>
@@ -2041,7 +2013,7 @@
         <v>0.55000000000000004</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" spans="1:4">
       <c r="A28">
         <v>78</v>
       </c>
@@ -2055,7 +2027,7 @@
         <v>0.85000000000000009</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" spans="1:4">
       <c r="A29">
         <v>81</v>
       </c>
@@ -2069,7 +2041,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" spans="1:4">
       <c r="A30">
         <v>84</v>
       </c>
@@ -2083,7 +2055,7 @@
         <v>0.95000000000000007</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" spans="1:4">
       <c r="A31">
         <v>87</v>
       </c>
@@ -2108,11 +2080,11 @@
   <dimension ref="A1:D41"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="5.28515625" customWidth="true"/>
-    <col min="2" max="4" width="6.85546875" customWidth="true"/>
+    <col min="1" max="1" width="5.28515625" customWidth="1"/>
+    <col min="2" max="4" width="6.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:4">
       <c r="A1" t="s">
         <v>12</v>
       </c>
@@ -2126,7 +2098,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:4">
       <c r="A2">
         <v>0</v>
       </c>
@@ -2140,7 +2112,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:4">
       <c r="A3">
         <v>2</v>
       </c>
@@ -2154,7 +2126,7 @@
         <v>0.30000000000000004</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:4">
       <c r="A4">
         <v>4</v>
       </c>
@@ -2168,7 +2140,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:4">
       <c r="A5">
         <v>6</v>
       </c>
@@ -2182,7 +2154,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:4">
       <c r="A6">
         <v>8</v>
       </c>
@@ -2196,7 +2168,7 @@
         <v>0.30000000000000004</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:4">
       <c r="A7">
         <v>10</v>
       </c>
@@ -2210,7 +2182,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:4">
       <c r="A8">
         <v>12</v>
       </c>
@@ -2224,7 +2196,7 @@
         <v>1.2000000000000002</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:4">
       <c r="A9">
         <v>14</v>
       </c>
@@ -2238,7 +2210,7 @@
         <v>1.2000000000000002</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:4">
       <c r="A10">
         <v>16</v>
       </c>
@@ -2252,7 +2224,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:4">
       <c r="A11">
         <v>18</v>
       </c>
@@ -2266,7 +2238,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:4">
       <c r="A12">
         <v>20</v>
       </c>
@@ -2280,7 +2252,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:4">
       <c r="A13">
         <v>22</v>
       </c>
@@ -2294,7 +2266,7 @@
         <v>0.70000000000000007</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:4">
       <c r="A14">
         <v>24</v>
       </c>
@@ -2308,7 +2280,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:4">
       <c r="A15">
         <v>26</v>
       </c>
@@ -2322,7 +2294,7 @@
         <v>1.2000000000000002</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:4">
       <c r="A16">
         <v>28</v>
       </c>
@@ -2336,7 +2308,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" spans="1:4">
       <c r="A17">
         <v>30</v>
       </c>
@@ -2350,7 +2322,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" spans="1:4">
       <c r="A18">
         <v>32</v>
       </c>
@@ -2364,7 +2336,7 @@
         <v>1.3000000000000003</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" spans="1:4">
       <c r="A19">
         <v>34</v>
       </c>
@@ -2378,7 +2350,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" spans="1:4">
       <c r="A20">
         <v>36</v>
       </c>
@@ -2392,7 +2364,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" spans="1:4">
       <c r="A21">
         <v>38</v>
       </c>
@@ -2406,7 +2378,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" spans="1:4">
       <c r="A22">
         <v>40</v>
       </c>
@@ -2420,7 +2392,7 @@
         <v>0.70000000000000007</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" spans="1:4">
       <c r="A23">
         <v>42</v>
       </c>
@@ -2434,7 +2406,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" spans="1:4">
       <c r="A24">
         <v>44</v>
       </c>
@@ -2448,7 +2420,7 @@
         <v>1.5000000000000002</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" spans="1:4">
       <c r="A25">
         <v>46</v>
       </c>
@@ -2462,7 +2434,7 @@
         <v>1.2000000000000002</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" spans="1:4">
       <c r="A26">
         <v>48</v>
       </c>
@@ -2476,7 +2448,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" spans="1:4">
       <c r="A27">
         <v>50</v>
       </c>
@@ -2490,7 +2462,7 @@
         <v>0.70000000000000007</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" spans="1:4">
       <c r="A28">
         <v>52</v>
       </c>
@@ -2504,7 +2476,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" spans="1:4">
       <c r="A29">
         <v>54</v>
       </c>
@@ -2518,7 +2490,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" spans="1:4">
       <c r="A30">
         <v>56</v>
       </c>
@@ -2532,7 +2504,7 @@
         <v>1.4000000000000001</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" spans="1:4">
       <c r="A31">
         <v>58</v>
       </c>
@@ -2546,7 +2518,7 @@
         <v>1.4000000000000001</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" spans="1:4">
       <c r="A32">
         <v>60</v>
       </c>
@@ -2560,7 +2532,7 @@
         <v>1.6</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" spans="1:4">
       <c r="A33">
         <v>62</v>
       </c>
@@ -2574,7 +2546,7 @@
         <v>1.6</v>
       </c>
     </row>
-    <row r="34">
+    <row r="34" spans="1:4">
       <c r="A34">
         <v>64</v>
       </c>
@@ -2588,7 +2560,7 @@
         <v>1.2000000000000002</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" spans="1:4">
       <c r="A35">
         <v>66</v>
       </c>
@@ -2602,7 +2574,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="36">
+    <row r="36" spans="1:4">
       <c r="A36">
         <v>68</v>
       </c>
@@ -2616,7 +2588,7 @@
         <v>0.60000000000000009</v>
       </c>
     </row>
-    <row r="37">
+    <row r="37" spans="1:4">
       <c r="A37">
         <v>70</v>
       </c>
@@ -2630,7 +2602,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="38">
+    <row r="38" spans="1:4">
       <c r="A38">
         <v>72</v>
       </c>
@@ -2644,7 +2616,7 @@
         <v>0.60000000000000009</v>
       </c>
     </row>
-    <row r="39">
+    <row r="39" spans="1:4">
       <c r="A39">
         <v>74</v>
       </c>
@@ -2658,7 +2630,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="40">
+    <row r="40" spans="1:4">
       <c r="A40">
         <v>76</v>
       </c>
@@ -2672,7 +2644,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="41">
+    <row r="41" spans="1:4">
       <c r="A41">
         <v>78</v>
       </c>
@@ -2690,944 +2662,4 @@
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D34"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="4.89453125" customWidth="true"/>
-    <col min="2" max="2" width="6.62109375" customWidth="true"/>
-    <col min="3" max="3" width="6.62109375" customWidth="true"/>
-    <col min="4" max="4" width="6.62109375" customWidth="true"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="B1" s="0" t="s">
-        <v>17</v>
-      </c>
-      <c r="C1" s="0" t="s">
-        <v>18</v>
-      </c>
-      <c r="D1" s="0" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="0">
-        <v>0</v>
-      </c>
-      <c r="B2" s="0">
-        <v>0</v>
-      </c>
-      <c r="C2" s="0">
-        <v>-0</v>
-      </c>
-      <c r="D2" s="0">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="0">
-        <v>1.5</v>
-      </c>
-      <c r="B3" s="0">
-        <v>0.20000000000000001</v>
-      </c>
-      <c r="C3" s="0">
-        <v>0.29999999999999999</v>
-      </c>
-      <c r="D3" s="0">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="0">
-        <v>3</v>
-      </c>
-      <c r="B4" s="0">
-        <v>0.40000000000000002</v>
-      </c>
-      <c r="C4" s="0">
-        <v>0.55000000000000004</v>
-      </c>
-      <c r="D4" s="0">
-        <v>1.1000000000000001</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="0">
-        <v>4.5</v>
-      </c>
-      <c r="B5" s="0">
-        <v>0.85000000000000009</v>
-      </c>
-      <c r="C5" s="0">
-        <v>0.55000000000000004</v>
-      </c>
-      <c r="D5" s="0">
-        <v>1.1500000000000001</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="0">
-        <v>6</v>
-      </c>
-      <c r="B6" s="0">
-        <v>1.2000000000000002</v>
-      </c>
-      <c r="C6" s="0">
-        <v>0.30000000000000004</v>
-      </c>
-      <c r="D6" s="0">
-        <v>1.25</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="0">
-        <v>7.5</v>
-      </c>
-      <c r="B7" s="0">
-        <v>1.3</v>
-      </c>
-      <c r="C7" s="0">
-        <v>-0</v>
-      </c>
-      <c r="D7" s="0">
-        <v>1.3</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="0">
-        <v>9</v>
-      </c>
-      <c r="B8" s="0">
-        <v>1.2500000000000002</v>
-      </c>
-      <c r="C8" s="0">
-        <v>-0.35000000000000003</v>
-      </c>
-      <c r="D8" s="0">
-        <v>1.4000000000000001</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="0">
-        <v>10.5</v>
-      </c>
-      <c r="B9" s="0">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="C9" s="0">
-        <v>-0.60000000000000009</v>
-      </c>
-      <c r="D9" s="0">
-        <v>1.3</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="0">
-        <v>12</v>
-      </c>
-      <c r="B10" s="0">
-        <v>0.80000000000000004</v>
-      </c>
-      <c r="C10" s="0">
-        <v>-0.70000000000000007</v>
-      </c>
-      <c r="D10" s="0">
-        <v>1.2500000000000002</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="0">
-        <v>13.5</v>
-      </c>
-      <c r="B11" s="0">
-        <v>0.40000000000000002</v>
-      </c>
-      <c r="C11" s="0">
-        <v>-0.70000000000000007</v>
-      </c>
-      <c r="D11" s="0">
-        <v>1.1500000000000001</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="0">
-        <v>15</v>
-      </c>
-      <c r="B12" s="0">
-        <v>0.10000000000000001</v>
-      </c>
-      <c r="C12" s="0">
-        <v>-0.45000000000000001</v>
-      </c>
-      <c r="D12" s="0">
-        <v>1.05</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="0">
-        <v>16.5</v>
-      </c>
-      <c r="B13" s="0">
-        <v>-0.050000000000000003</v>
-      </c>
-      <c r="C13" s="0">
-        <v>-0.10000000000000001</v>
-      </c>
-      <c r="D13" s="0">
-        <v>0.95000000000000007</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="0">
-        <v>18</v>
-      </c>
-      <c r="B14" s="0">
-        <v>-0.25</v>
-      </c>
-      <c r="C14" s="0">
-        <v>0.35000000000000003</v>
-      </c>
-      <c r="D14" s="0">
-        <v>0.85000000000000009</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="0">
-        <v>19.5</v>
-      </c>
-      <c r="B15" s="0">
-        <v>-0.5</v>
-      </c>
-      <c r="C15" s="0">
-        <v>0.75000000000000011</v>
-      </c>
-      <c r="D15" s="0">
-        <v>0.80000000000000004</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="0">
-        <v>21</v>
-      </c>
-      <c r="B16" s="0">
-        <v>-0.85000000000000009</v>
-      </c>
-      <c r="C16" s="0">
-        <v>0.85000000000000009</v>
-      </c>
-      <c r="D16" s="0">
-        <v>0.75</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="0">
-        <v>22.5</v>
-      </c>
-      <c r="B17" s="0">
-        <v>-1.1500000000000001</v>
-      </c>
-      <c r="C17" s="0">
-        <v>0.75</v>
-      </c>
-      <c r="D17" s="0">
-        <v>0.70000000000000007</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="0">
-        <v>24</v>
-      </c>
-      <c r="B18" s="0">
-        <v>-1.3</v>
-      </c>
-      <c r="C18" s="0">
-        <v>0.60000000000000009</v>
-      </c>
-      <c r="D18" s="0">
-        <v>0.70000000000000007</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="0">
-        <v>25.5</v>
-      </c>
-      <c r="B19" s="0">
-        <v>-1.1000000000000001</v>
-      </c>
-      <c r="C19" s="0">
-        <v>0.35000000000000003</v>
-      </c>
-      <c r="D19" s="0">
-        <v>0.65000000000000002</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="0">
-        <v>27</v>
-      </c>
-      <c r="B20" s="0">
-        <v>-0.65000000000000013</v>
-      </c>
-      <c r="C20" s="0">
-        <v>0.29999999999999999</v>
-      </c>
-      <c r="D20" s="0">
-        <v>0.65000000000000013</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="0">
-        <v>28.5</v>
-      </c>
-      <c r="B21" s="0">
-        <v>-0.45000000000000001</v>
-      </c>
-      <c r="C21" s="0">
-        <v>0.10000000000000001</v>
-      </c>
-      <c r="D21" s="0">
-        <v>0.70000000000000007</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="0">
-        <v>30</v>
-      </c>
-      <c r="B22" s="0">
-        <v>-0.70000000000000007</v>
-      </c>
-      <c r="C22" s="0">
-        <v>0.050000000000000003</v>
-      </c>
-      <c r="D22" s="0">
-        <v>0.70000000000000007</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="0">
-        <v>31.5</v>
-      </c>
-      <c r="B23" s="0">
-        <v>-1.05</v>
-      </c>
-      <c r="C23" s="0">
-        <v>0</v>
-      </c>
-      <c r="D23" s="0">
-        <v>0.75000000000000011</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="0">
-        <v>33</v>
-      </c>
-      <c r="B24" s="0">
-        <v>-1.2500000000000002</v>
-      </c>
-      <c r="C24" s="0">
-        <v>-0.10000000000000001</v>
-      </c>
-      <c r="D24" s="0">
-        <v>0.75</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="0">
-        <v>34.5</v>
-      </c>
-      <c r="B25" s="0">
-        <v>-1.1500000000000001</v>
-      </c>
-      <c r="C25" s="0">
-        <v>-0.29999999999999999</v>
-      </c>
-      <c r="D25" s="0">
-        <v>0.80000000000000004</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="0">
-        <v>36</v>
-      </c>
-      <c r="B26" s="0">
-        <v>-0.90000000000000013</v>
-      </c>
-      <c r="C26" s="0">
-        <v>-0.35000000000000003</v>
-      </c>
-      <c r="D26" s="0">
-        <v>0.85000000000000009</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="0">
-        <v>37.5</v>
-      </c>
-      <c r="B27" s="0">
-        <v>-0.45000000000000001</v>
-      </c>
-      <c r="C27" s="0">
-        <v>-0.35000000000000003</v>
-      </c>
-      <c r="D27" s="0">
-        <v>0.85000000000000009</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="0">
-        <v>39</v>
-      </c>
-      <c r="B28" s="0">
-        <v>-0.45000000000000001</v>
-      </c>
-      <c r="C28" s="0">
-        <v>-0.5</v>
-      </c>
-      <c r="D28" s="0">
-        <v>0.90000000000000002</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="0">
-        <v>40.5</v>
-      </c>
-      <c r="B29" s="0">
-        <v>-0.70000000000000007</v>
-      </c>
-      <c r="C29" s="0">
-        <v>-0.55000000000000004</v>
-      </c>
-      <c r="D29" s="0">
-        <v>0.90000000000000002</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="0">
-        <v>42</v>
-      </c>
-      <c r="B30" s="0">
-        <v>-1.05</v>
-      </c>
-      <c r="C30" s="0">
-        <v>-0.70000000000000007</v>
-      </c>
-      <c r="D30" s="0">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="0">
-        <v>43.5</v>
-      </c>
-      <c r="B31" s="0">
-        <v>-0.95000000000000007</v>
-      </c>
-      <c r="C31" s="0">
-        <v>-0.90000000000000013</v>
-      </c>
-      <c r="D31" s="0">
-        <v>1.05</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="0">
-        <v>45</v>
-      </c>
-      <c r="B32" s="0">
-        <v>-0.60000000000000009</v>
-      </c>
-      <c r="C32" s="0">
-        <v>-1</v>
-      </c>
-      <c r="D32" s="0">
-        <v>1.1000000000000001</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="0">
-        <v>46.5</v>
-      </c>
-      <c r="B33" s="0">
-        <v>-0.20000000000000001</v>
-      </c>
-      <c r="C33" s="0">
-        <v>-0.80000000000000004</v>
-      </c>
-      <c r="D33" s="0">
-        <v>1.1000000000000001</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="0">
-        <v>48</v>
-      </c>
-      <c r="B34" s="0">
-        <v>-0</v>
-      </c>
-      <c r="C34" s="0">
-        <v>-0.45000000000000001</v>
-      </c>
-      <c r="D34" s="0">
-        <v>1.2000000000000002</v>
-      </c>
-    </row>
-  </sheetData>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D31"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="4.89453125" customWidth="true"/>
-    <col min="2" max="2" width="6.62109375" customWidth="true"/>
-    <col min="3" max="3" width="6.62109375" customWidth="true"/>
-    <col min="4" max="4" width="6.62109375" customWidth="true"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="B1" s="0" t="s">
-        <v>21</v>
-      </c>
-      <c r="C1" s="0" t="s">
-        <v>22</v>
-      </c>
-      <c r="D1" s="0" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="0">
-        <v>0</v>
-      </c>
-      <c r="B2" s="0">
-        <v>0</v>
-      </c>
-      <c r="C2" s="0">
-        <v>-0</v>
-      </c>
-      <c r="D2" s="0">
-        <v>0.95000000000000007</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="0">
-        <v>1.5</v>
-      </c>
-      <c r="B3" s="0">
-        <v>0.15000000000000002</v>
-      </c>
-      <c r="C3" s="0">
-        <v>0.40000000000000002</v>
-      </c>
-      <c r="D3" s="0">
-        <v>1.1500000000000001</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="0">
-        <v>3</v>
-      </c>
-      <c r="B4" s="0">
-        <v>0.35000000000000003</v>
-      </c>
-      <c r="C4" s="0">
-        <v>0.70000000000000007</v>
-      </c>
-      <c r="D4" s="0">
-        <v>1.2500000000000002</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="0">
-        <v>4.5</v>
-      </c>
-      <c r="B5" s="0">
-        <v>0.90000000000000013</v>
-      </c>
-      <c r="C5" s="0">
-        <v>0.80000000000000004</v>
-      </c>
-      <c r="D5" s="0">
-        <v>1.3500000000000001</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="0">
-        <v>6</v>
-      </c>
-      <c r="B6" s="0">
-        <v>1.3500000000000001</v>
-      </c>
-      <c r="C6" s="0">
-        <v>0.30000000000000004</v>
-      </c>
-      <c r="D6" s="0">
-        <v>1.2000000000000002</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="0">
-        <v>7.5</v>
-      </c>
-      <c r="B7" s="0">
-        <v>1.4500000000000002</v>
-      </c>
-      <c r="C7" s="0">
-        <v>-0.15000000000000002</v>
-      </c>
-      <c r="D7" s="0">
-        <v>1.05</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="0">
-        <v>9</v>
-      </c>
-      <c r="B8" s="0">
-        <v>1.25</v>
-      </c>
-      <c r="C8" s="0">
-        <v>-0.70000000000000007</v>
-      </c>
-      <c r="D8" s="0">
-        <v>0.90000000000000002</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="0">
-        <v>10.5</v>
-      </c>
-      <c r="B9" s="0">
-        <v>0.90000000000000013</v>
-      </c>
-      <c r="C9" s="0">
-        <v>-0.95000000000000007</v>
-      </c>
-      <c r="D9" s="0">
-        <v>0.80000000000000004</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="0">
-        <v>12</v>
-      </c>
-      <c r="B10" s="0">
-        <v>0.40000000000000002</v>
-      </c>
-      <c r="C10" s="0">
-        <v>-0.75000000000000011</v>
-      </c>
-      <c r="D10" s="0">
-        <v>0.85000000000000009</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="0">
-        <v>13.5</v>
-      </c>
-      <c r="B11" s="0">
-        <v>0</v>
-      </c>
-      <c r="C11" s="0">
-        <v>-0.15000000000000002</v>
-      </c>
-      <c r="D11" s="0">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="0">
-        <v>15</v>
-      </c>
-      <c r="B12" s="0">
-        <v>-0.10000000000000001</v>
-      </c>
-      <c r="C12" s="0">
-        <v>0.25</v>
-      </c>
-      <c r="D12" s="0">
-        <v>1.1000000000000001</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="0">
-        <v>16.5</v>
-      </c>
-      <c r="B13" s="0">
-        <v>-0.35000000000000003</v>
-      </c>
-      <c r="C13" s="0">
-        <v>0.80000000000000004</v>
-      </c>
-      <c r="D13" s="0">
-        <v>1.2500000000000002</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="0">
-        <v>18</v>
-      </c>
-      <c r="B14" s="0">
-        <v>-0.75000000000000011</v>
-      </c>
-      <c r="C14" s="0">
-        <v>1.1500000000000001</v>
-      </c>
-      <c r="D14" s="0">
-        <v>1.1500000000000001</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="0">
-        <v>19.5</v>
-      </c>
-      <c r="B15" s="0">
-        <v>-1.1500000000000001</v>
-      </c>
-      <c r="C15" s="0">
-        <v>1.2500000000000002</v>
-      </c>
-      <c r="D15" s="0">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="0">
-        <v>21</v>
-      </c>
-      <c r="B16" s="0">
-        <v>-1.3500000000000001</v>
-      </c>
-      <c r="C16" s="0">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="D16" s="0">
-        <v>0.80000000000000004</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="0">
-        <v>22.5</v>
-      </c>
-      <c r="B17" s="0">
-        <v>-1.1500000000000001</v>
-      </c>
-      <c r="C17" s="0">
-        <v>0.70000000000000007</v>
-      </c>
-      <c r="D17" s="0">
-        <v>0.80000000000000004</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="0">
-        <v>24</v>
-      </c>
-      <c r="B18" s="0">
-        <v>-0.70000000000000007</v>
-      </c>
-      <c r="C18" s="0">
-        <v>0.45000000000000001</v>
-      </c>
-      <c r="D18" s="0">
-        <v>1.05</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="0">
-        <v>25.5</v>
-      </c>
-      <c r="B19" s="0">
-        <v>-0.29999999999999999</v>
-      </c>
-      <c r="C19" s="0">
-        <v>0.15000000000000002</v>
-      </c>
-      <c r="D19" s="0">
-        <v>1.3</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="0">
-        <v>27</v>
-      </c>
-      <c r="B20" s="0">
-        <v>-0.60000000000000009</v>
-      </c>
-      <c r="C20" s="0">
-        <v>-0</v>
-      </c>
-      <c r="D20" s="0">
-        <v>1.05</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="0">
-        <v>28.5</v>
-      </c>
-      <c r="B21" s="0">
-        <v>-1.05</v>
-      </c>
-      <c r="C21" s="0">
-        <v>0.29999999999999999</v>
-      </c>
-      <c r="D21" s="0">
-        <v>0.80000000000000004</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="0">
-        <v>30</v>
-      </c>
-      <c r="B22" s="0">
-        <v>-1.4000000000000001</v>
-      </c>
-      <c r="C22" s="0">
-        <v>0.15000000000000002</v>
-      </c>
-      <c r="D22" s="0">
-        <v>0.75000000000000011</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="0">
-        <v>31.5</v>
-      </c>
-      <c r="B23" s="0">
-        <v>-1.2000000000000002</v>
-      </c>
-      <c r="C23" s="0">
-        <v>-0.25</v>
-      </c>
-      <c r="D23" s="0">
-        <v>1.05</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="0">
-        <v>33</v>
-      </c>
-      <c r="B24" s="0">
-        <v>-0.45000000000000001</v>
-      </c>
-      <c r="C24" s="0">
-        <v>-0.40000000000000002</v>
-      </c>
-      <c r="D24" s="0">
-        <v>1.25</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="0">
-        <v>34.5</v>
-      </c>
-      <c r="B25" s="0">
-        <v>-0.60000000000000009</v>
-      </c>
-      <c r="C25" s="0">
-        <v>-0.75</v>
-      </c>
-      <c r="D25" s="0">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="0">
-        <v>36</v>
-      </c>
-      <c r="B26" s="0">
-        <v>-1.1500000000000001</v>
-      </c>
-      <c r="C26" s="0">
-        <v>-0.95000000000000007</v>
-      </c>
-      <c r="D26" s="0">
-        <v>0.85000000000000009</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="0">
-        <v>37.5</v>
-      </c>
-      <c r="B27" s="0">
-        <v>-1.1500000000000001</v>
-      </c>
-      <c r="C27" s="0">
-        <v>-1.3</v>
-      </c>
-      <c r="D27" s="0">
-        <v>0.90000000000000002</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="0">
-        <v>39</v>
-      </c>
-      <c r="B28" s="0">
-        <v>-0.35000000000000003</v>
-      </c>
-      <c r="C28" s="0">
-        <v>-1.2000000000000002</v>
-      </c>
-      <c r="D28" s="0">
-        <v>1.1000000000000001</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="0">
-        <v>40.5</v>
-      </c>
-      <c r="B29" s="0">
-        <v>-0.10000000000000001</v>
-      </c>
-      <c r="C29" s="0">
-        <v>-0.80000000000000004</v>
-      </c>
-      <c r="D29" s="0">
-        <v>1.3</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="0">
-        <v>42</v>
-      </c>
-      <c r="B30" s="0">
-        <v>0</v>
-      </c>
-      <c r="C30" s="0">
-        <v>-0.40000000000000002</v>
-      </c>
-      <c r="D30" s="0">
-        <v>1.05</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="0">
-        <v>43.5</v>
-      </c>
-      <c r="B31" s="0">
-        <v>-0.29999999999999999</v>
-      </c>
-      <c r="C31" s="0">
-        <v>-0.15000000000000002</v>
-      </c>
-      <c r="D31" s="0">
-        <v>0.90000000000000013</v>
-      </c>
-    </row>
-  </sheetData>
-</worksheet>
 </file>
--- a/reference/functions/spline_curve/waypoint.xlsx
+++ b/reference/functions/spline_curve/waypoint.xlsx
@@ -1,23 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="26924"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28129"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nakat\Documents\GitHub\drone\reference\functions\spline_curve\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B35E006-822C-47B7-9D47-C096F0F3C2E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4EEAF8F-CB71-41C7-B870-B247F16DFD96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-90" yWindow="-90" windowWidth="17460" windowHeight="10260" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-2500" yWindow="-21710" windowWidth="38620" windowHeight="21100" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="MyNewSheet" sheetId="4" r:id="rId2"/>
-    <sheet name="Sheet1_15" sheetId="2" r:id="rId3"/>
-    <sheet name="Sheet1_15d3" sheetId="3" r:id="rId4"/>
-    <sheet name="new" sheetId="5" r:id="rId5"/>
+    <sheet name="origin" sheetId="4" r:id="rId2"/>
+    <sheet name="5to15" sheetId="6" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="8">
   <si>
     <t>x_wp</t>
     <phoneticPr fontId="1"/>
@@ -66,24 +64,12 @@
   <si>
     <t>posi_3</t>
   </si>
-  <si>
-    <t>time</t>
-  </si>
-  <si>
-    <t>posi_1</t>
-  </si>
-  <si>
-    <t>posi_2</t>
-  </si>
-  <si>
-    <t>posi_3</t>
-  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -98,12 +84,6 @@
       <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
-    </font>
-    <font>
-      <sz val="6"/>
-      <name val="HGGothicE"/>
-      <family val="3"/>
-      <charset val="128"/>
     </font>
   </fonts>
   <fills count="2">
@@ -147,9 +127,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office テーマ">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 テーマ">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -187,7 +167,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -293,7 +273,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -435,7 +415,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -444,9 +424,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D26"/>
-  <sheetFormatPr defaultRowHeight="14.75"/>
+  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A1" s="1" t="s">
         <v>3</v>
       </c>
@@ -460,7 +440,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A2">
         <v>0</v>
       </c>
@@ -474,7 +454,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:4">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A3">
         <v>1.5</v>
       </c>
@@ -488,7 +468,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="4" spans="1:4">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A4">
         <v>3</v>
       </c>
@@ -502,7 +482,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:4">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A5">
         <v>4.5</v>
       </c>
@@ -516,7 +496,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="6" spans="1:4">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A6">
         <v>6</v>
       </c>
@@ -530,7 +510,7 @@
         <v>1.3</v>
       </c>
     </row>
-    <row r="7" spans="1:4">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A7">
         <v>7.5</v>
       </c>
@@ -544,7 +524,7 @@
         <v>1.4000000000000001</v>
       </c>
     </row>
-    <row r="8" spans="1:4">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A8">
         <v>9</v>
       </c>
@@ -558,7 +538,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="9" spans="1:4">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A9">
         <v>10.5</v>
       </c>
@@ -572,7 +552,7 @@
         <v>1.3</v>
       </c>
     </row>
-    <row r="10" spans="1:4">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A10">
         <v>12</v>
       </c>
@@ -586,7 +566,7 @@
         <v>1.2000000000000002</v>
       </c>
     </row>
-    <row r="11" spans="1:4">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A11">
         <v>13.5</v>
       </c>
@@ -600,7 +580,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:4">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A12">
         <v>15</v>
       </c>
@@ -614,7 +594,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="13" spans="1:4">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A13">
         <v>16.5</v>
       </c>
@@ -628,7 +608,7 @@
         <v>0.70000000000000007</v>
       </c>
     </row>
-    <row r="14" spans="1:4">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A14">
         <v>18</v>
       </c>
@@ -642,7 +622,7 @@
         <v>0.60000000000000009</v>
       </c>
     </row>
-    <row r="15" spans="1:4">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A15">
         <v>19.5</v>
       </c>
@@ -656,7 +636,7 @@
         <v>0.70000000000000007</v>
       </c>
     </row>
-    <row r="16" spans="1:4">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A16">
         <v>21</v>
       </c>
@@ -670,7 +650,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="17" spans="1:4">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A17">
         <v>22.5</v>
       </c>
@@ -684,7 +664,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:4">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A18">
         <v>24</v>
       </c>
@@ -698,7 +678,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="19" spans="1:4">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A19">
         <v>25.5</v>
       </c>
@@ -712,7 +692,7 @@
         <v>1.2000000000000002</v>
       </c>
     </row>
-    <row r="20" spans="1:4">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A20">
         <v>27</v>
       </c>
@@ -726,7 +706,7 @@
         <v>1.3</v>
       </c>
     </row>
-    <row r="21" spans="1:4">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A21">
         <v>28.5</v>
       </c>
@@ -740,7 +720,7 @@
         <v>1.2000000000000002</v>
       </c>
     </row>
-    <row r="22" spans="1:4">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A22">
         <v>30</v>
       </c>
@@ -754,7 +734,7 @@
         <v>1.3</v>
       </c>
     </row>
-    <row r="23" spans="1:4">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A23">
         <v>31.5</v>
       </c>
@@ -768,7 +748,7 @@
         <v>1.2000000000000002</v>
       </c>
     </row>
-    <row r="24" spans="1:4">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A24">
         <v>33</v>
       </c>
@@ -782,7 +762,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="25" spans="1:4">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A25">
         <v>34.5</v>
       </c>
@@ -796,7 +776,7 @@
         <v>1.05</v>
       </c>
     </row>
-    <row r="26" spans="1:4">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A26">
         <v>36</v>
       </c>
@@ -820,13 +800,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:D132"/>
-  <sheetFormatPr defaultRowHeight="14.75"/>
+  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
   <cols>
     <col min="1" max="1" width="5.90625" customWidth="1"/>
     <col min="2" max="4" width="6.86328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A1" t="s">
         <v>4</v>
       </c>
@@ -840,7 +820,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A2">
         <v>0</v>
       </c>
@@ -854,7 +834,7 @@
         <v>2.5143889596457303E-3</v>
       </c>
     </row>
-    <row r="3" spans="1:4">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A3">
         <v>5</v>
       </c>
@@ -868,7 +848,7 @@
         <v>-1.5923376176110715</v>
       </c>
     </row>
-    <row r="4" spans="1:4">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A4">
         <v>10</v>
       </c>
@@ -882,7 +862,7 @@
         <v>1.6129946190549993</v>
       </c>
     </row>
-    <row r="5" spans="1:4">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A5">
         <v>15</v>
       </c>
@@ -896,7 +876,7 @@
         <v>0.83740062219910261</v>
       </c>
     </row>
-    <row r="6" spans="1:4">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A6">
         <v>20</v>
       </c>
@@ -910,7 +890,7 @@
         <v>0.31680918265487801</v>
       </c>
     </row>
-    <row r="7" spans="1:4">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A7">
         <v>25</v>
       </c>
@@ -924,7 +904,7 @@
         <v>1.2764408752063083</v>
       </c>
     </row>
-    <row r="8" spans="1:4">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A8">
         <v>30</v>
       </c>
@@ -938,7 +918,7 @@
         <v>1.5118664306624763</v>
       </c>
     </row>
-    <row r="9" spans="1:4">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A9">
         <v>35</v>
       </c>
@@ -952,7 +932,7 @@
         <v>-4.7307536154024357</v>
       </c>
     </row>
-    <row r="10" spans="1:4">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A10">
         <v>40</v>
       </c>
@@ -966,7 +946,7 @@
         <v>2.0098215069291472</v>
       </c>
     </row>
-    <row r="11" spans="1:4">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A11">
         <v>45</v>
       </c>
@@ -980,7 +960,7 @@
         <v>2.2459930027101969</v>
       </c>
     </row>
-    <row r="12" spans="1:4">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A12">
         <v>50</v>
       </c>
@@ -994,7 +974,7 @@
         <v>-0.71427041847938133</v>
       </c>
     </row>
-    <row r="13" spans="1:4">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A13">
         <v>55</v>
       </c>
@@ -1008,7 +988,7 @@
         <v>0.87411558151694102</v>
       </c>
     </row>
-    <row r="14" spans="1:4">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A14">
         <v>60</v>
       </c>
@@ -1022,7 +1002,7 @@
         <v>0.50678709178415882</v>
       </c>
     </row>
-    <row r="15" spans="1:4">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A15">
         <v>65</v>
       </c>
@@ -1036,7 +1016,7 @@
         <v>-0.30624051417129095</v>
       </c>
     </row>
-    <row r="16" spans="1:4">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A16">
         <v>70</v>
       </c>
@@ -1050,7 +1030,7 @@
         <v>-3.9146105313087345</v>
       </c>
     </row>
-    <row r="17" spans="1:4">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A17">
         <v>75</v>
       </c>
@@ -1064,7 +1044,7 @@
         <v>4.7602624075810045</v>
       </c>
     </row>
-    <row r="18" spans="1:4">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A18">
         <v>80</v>
       </c>
@@ -1078,7 +1058,7 @@
         <v>-1.3399947978837368</v>
       </c>
     </row>
-    <row r="19" spans="1:4">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A19">
         <v>85</v>
       </c>
@@ -1092,7 +1072,7 @@
         <v>-4.215366851019021</v>
       </c>
     </row>
-    <row r="20" spans="1:4">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A20">
         <v>90</v>
       </c>
@@ -1106,7 +1086,7 @@
         <v>-4.4653950180761024</v>
       </c>
     </row>
-    <row r="21" spans="1:4">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A21">
         <v>95</v>
       </c>
@@ -1120,7 +1100,7 @@
         <v>2.3174510546711211</v>
       </c>
     </row>
-    <row r="22" spans="1:4">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A22">
         <v>100</v>
       </c>
@@ -1134,7 +1114,7 @@
         <v>-2.4469565685518155</v>
       </c>
     </row>
-    <row r="23" spans="1:4">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A23">
         <v>105</v>
       </c>
@@ -1148,7 +1128,7 @@
         <v>-2.5539097033394507</v>
       </c>
     </row>
-    <row r="24" spans="1:4">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A24">
         <v>110</v>
       </c>
@@ -1162,7 +1142,7 @@
         <v>-1.4459965599407432</v>
       </c>
     </row>
-    <row r="25" spans="1:4">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A25">
         <v>115</v>
       </c>
@@ -1176,7 +1156,7 @@
         <v>1.0008415884716482</v>
       </c>
     </row>
-    <row r="26" spans="1:4">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A26">
         <v>120</v>
       </c>
@@ -1190,7 +1170,7 @@
         <v>2.2443406250490772</v>
       </c>
     </row>
-    <row r="27" spans="1:4">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A27">
         <v>125</v>
       </c>
@@ -1204,7 +1184,7 @@
         <v>-4.0960986361258698</v>
       </c>
     </row>
-    <row r="28" spans="1:4">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A28">
         <v>130</v>
       </c>
@@ -1218,7 +1198,7 @@
         <v>4.6934286332964223</v>
       </c>
     </row>
-    <row r="29" spans="1:4">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A29">
         <v>135</v>
       </c>
@@ -1232,7 +1212,7 @@
         <v>-4.3769391712908945</v>
       </c>
     </row>
-    <row r="30" spans="1:4">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A30">
         <v>140</v>
       </c>
@@ -1246,7 +1226,7 @@
         <v>4.3936324237126261</v>
       </c>
     </row>
-    <row r="31" spans="1:4">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A31">
         <v>145</v>
       </c>
@@ -1260,7 +1240,7 @@
         <v>-0.17059200732076563</v>
       </c>
     </row>
-    <row r="32" spans="1:4">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A32">
         <v>150</v>
       </c>
@@ -1274,7 +1254,7 @@
         <v>3.3104073633841615</v>
       </c>
     </row>
-    <row r="33" spans="1:4">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A33">
         <v>155</v>
       </c>
@@ -1288,7 +1268,7 @@
         <v>-1.1286388991793495</v>
       </c>
     </row>
-    <row r="34" spans="1:4">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A34">
         <v>160</v>
       </c>
@@ -1302,7 +1282,7 @@
         <v>1.6923601147740586</v>
       </c>
     </row>
-    <row r="35" spans="1:4">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A35">
         <v>165</v>
       </c>
@@ -1316,7 +1296,7 @@
         <v>1.9493721341731607</v>
       </c>
     </row>
-    <row r="36" spans="1:4">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A36">
         <v>170</v>
       </c>
@@ -1330,7 +1310,7 @@
         <v>-3.5731428814234665</v>
       </c>
     </row>
-    <row r="37" spans="1:4">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A37">
         <v>175</v>
       </c>
@@ -1344,7 +1324,7 @@
         <v>-0.16824547684147206</v>
       </c>
     </row>
-    <row r="38" spans="1:4">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A38">
         <v>180</v>
       </c>
@@ -1358,7 +1338,7 @@
         <v>3.7545109810478063</v>
       </c>
     </row>
-    <row r="39" spans="1:4">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A39">
         <v>185</v>
       </c>
@@ -1372,7 +1352,7 @@
         <v>0.54078060347251378</v>
       </c>
     </row>
-    <row r="40" spans="1:4">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A40">
         <v>190</v>
       </c>
@@ -1386,7 +1366,7 @@
         <v>-3.5212793126992183</v>
       </c>
     </row>
-    <row r="41" spans="1:4">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A41">
         <v>195</v>
       </c>
@@ -1400,7 +1380,7 @@
         <v>-3.8327216751578455</v>
       </c>
     </row>
-    <row r="42" spans="1:4">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A42">
         <v>200</v>
       </c>
@@ -1414,7 +1394,7 @@
         <v>-1.4043363221400995</v>
       </c>
     </row>
-    <row r="43" spans="1:4">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A43">
         <v>205</v>
       </c>
@@ -1428,7 +1408,7 @@
         <v>-0.30766453615983513</v>
       </c>
     </row>
-    <row r="44" spans="1:4">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A44">
         <v>210</v>
       </c>
@@ -1442,7 +1422,7 @@
         <v>-2.2974788731457716</v>
       </c>
     </row>
-    <row r="45" spans="1:4">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A45">
         <v>215</v>
       </c>
@@ -1456,7 +1436,7 @@
         <v>-2.6040236745237264</v>
       </c>
     </row>
-    <row r="46" spans="1:4">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A46">
         <v>220</v>
       </c>
@@ -1470,7 +1450,7 @@
         <v>-1.6267749651982433</v>
       </c>
     </row>
-    <row r="47" spans="1:4">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A47">
         <v>225</v>
       </c>
@@ -1484,7 +1464,7 @@
         <v>-2.7558778901116519</v>
       </c>
     </row>
-    <row r="48" spans="1:4">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A48">
         <v>230</v>
       </c>
@@ -1498,7 +1478,7 @@
         <v>-3.3307752325489925</v>
       </c>
     </row>
-    <row r="49" spans="1:4">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A49">
         <v>235</v>
       </c>
@@ -1512,7 +1492,7 @@
         <v>-3.788865812315485</v>
       </c>
     </row>
-    <row r="50" spans="1:4">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A50">
         <v>240</v>
       </c>
@@ -1526,7 +1506,7 @@
         <v>1.9163100448142745</v>
       </c>
     </row>
-    <row r="51" spans="1:4">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A51">
         <v>245</v>
       </c>
@@ -1540,7 +1520,7 @@
         <v>-0.45171651463562945</v>
       </c>
     </row>
-    <row r="52" spans="1:4">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A52">
         <v>250</v>
       </c>
@@ -1554,7 +1534,7 @@
         <v>1.1204968011208316</v>
       </c>
     </row>
-    <row r="53" spans="1:4">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A53">
         <v>255</v>
       </c>
@@ -1568,7 +1548,7 @@
         <v>0.18901859959311484</v>
       </c>
     </row>
-    <row r="54" spans="1:4">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A54">
         <v>260</v>
       </c>
@@ -1582,7 +1562,7 @@
         <v>-4.8986444451687134</v>
       </c>
     </row>
-    <row r="55" spans="1:4">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A55">
         <v>265</v>
       </c>
@@ -1596,7 +1576,7 @@
         <v>-1.9404129043036511</v>
       </c>
     </row>
-    <row r="56" spans="1:4">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A56">
         <v>270</v>
       </c>
@@ -1610,7 +1590,7 @@
         <v>0.94956400116934403</v>
       </c>
     </row>
-    <row r="57" spans="1:4">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A57">
         <v>275</v>
       </c>
@@ -1624,7 +1604,7 @@
         <v>-2.4333099525699255</v>
       </c>
     </row>
-    <row r="58" spans="1:4">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A58">
         <v>280</v>
       </c>
@@ -1638,7 +1618,7 @@
         <v>2.3275889108562451</v>
       </c>
     </row>
-    <row r="59" spans="1:4">
+    <row r="59" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A59">
         <v>285</v>
       </c>
@@ -1652,7 +1632,7 @@
         <v>-1.247873095563059</v>
       </c>
     </row>
-    <row r="60" spans="1:4">
+    <row r="60" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A60">
         <v>290</v>
       </c>
@@ -1666,7 +1646,7 @@
         <v>3.5941810445347855</v>
       </c>
     </row>
-    <row r="61" spans="1:4">
+    <row r="61" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A61">
         <v>295</v>
       </c>
@@ -1680,7 +1660,7 @@
         <v>-3.8291408115260084</v>
       </c>
     </row>
-    <row r="62" spans="1:4">
+    <row r="62" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A62">
         <v>300</v>
       </c>
@@ -1694,7 +1674,7 @@
         <v>-0.7527211830211511</v>
       </c>
     </row>
-    <row r="63" spans="1:4">
+    <row r="63" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A63">
         <v>310</v>
       </c>
@@ -1708,7 +1688,7 @@
         <v>-4.3029135987555609</v>
       </c>
     </row>
-    <row r="64" spans="1:4">
+    <row r="64" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A64">
         <v>320</v>
       </c>
@@ -1722,7 +1702,7 @@
         <v>-1.7068382992475528</v>
       </c>
     </row>
-    <row r="65" spans="1:4">
+    <row r="65" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A65">
         <v>330</v>
       </c>
@@ -1736,7 +1716,7 @@
         <v>3.3938672732647945</v>
       </c>
     </row>
-    <row r="66" spans="1:4">
+    <row r="66" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A66">
         <v>340</v>
       </c>
@@ -1750,7 +1730,7 @@
         <v>-0.68286055830592107</v>
       </c>
     </row>
-    <row r="67" spans="1:4">
+    <row r="67" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A67">
         <v>350</v>
       </c>
@@ -1764,7 +1744,7 @@
         <v>-6.5438526761227855E-2</v>
       </c>
     </row>
-    <row r="68" spans="1:4">
+    <row r="68" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A68">
         <v>360</v>
       </c>
@@ -1778,7 +1758,7 @@
         <v>-1.7199525526209858</v>
       </c>
     </row>
-    <row r="69" spans="1:4">
+    <row r="69" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A69">
         <v>370</v>
       </c>
@@ -1792,7 +1772,7 @@
         <v>0.56093253872197213</v>
       </c>
     </row>
-    <row r="70" spans="1:4">
+    <row r="70" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A70">
         <v>380</v>
       </c>
@@ -1806,7 +1786,7 @@
         <v>-4.6334289050480502</v>
       </c>
     </row>
-    <row r="71" spans="1:4">
+    <row r="71" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A71">
         <v>390</v>
       </c>
@@ -1820,7 +1800,7 @@
         <v>-1.3612034211029878</v>
       </c>
     </row>
-    <row r="72" spans="1:4">
+    <row r="72" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A72">
         <v>400</v>
       </c>
@@ -1834,7 +1814,7 @@
         <v>4.6054352008508728</v>
       </c>
     </row>
-    <row r="73" spans="1:4">
+    <row r="73" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A73">
         <v>410</v>
       </c>
@@ -1848,7 +1828,7 @@
         <v>3.9964315753945767</v>
       </c>
     </row>
-    <row r="74" spans="1:4">
+    <row r="74" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A74">
         <v>420</v>
       </c>
@@ -1862,7 +1842,7 @@
         <v>4.4863012889615996</v>
       </c>
     </row>
-    <row r="75" spans="1:4">
+    <row r="75" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A75">
         <v>430</v>
       </c>
@@ -1876,7 +1856,7 @@
         <v>0.41246301658184548</v>
       </c>
     </row>
-    <row r="76" spans="1:4">
+    <row r="76" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A76">
         <v>440</v>
       </c>
@@ -1890,7 +1870,7 @@
         <v>3.3701019276245638</v>
       </c>
     </row>
-    <row r="77" spans="1:4">
+    <row r="77" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A77">
         <v>450</v>
       </c>
@@ -1904,7 +1884,7 @@
         <v>3.5927992962940012</v>
       </c>
     </row>
-    <row r="78" spans="1:4">
+    <row r="78" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A78">
         <v>460</v>
       </c>
@@ -1918,7 +1898,7 @@
         <v>-1.7419939426058739</v>
       </c>
     </row>
-    <row r="79" spans="1:4">
+    <row r="79" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A79">
         <v>470</v>
       </c>
@@ -1932,7 +1912,7 @@
         <v>3.394090790320432</v>
       </c>
     </row>
-    <row r="80" spans="1:4">
+    <row r="80" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A80">
         <v>480</v>
       </c>
@@ -1946,7 +1926,7 @@
         <v>-0.19505225160462603</v>
       </c>
     </row>
-    <row r="81" spans="1:4">
+    <row r="81" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A81">
         <v>490</v>
       </c>
@@ -1960,7 +1940,7 @@
         <v>2.3867688422087441</v>
       </c>
     </row>
-    <row r="82" spans="1:4">
+    <row r="82" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A82">
         <v>500</v>
       </c>
@@ -1974,7 +1954,7 @@
         <v>-2.8741223271239527</v>
       </c>
     </row>
-    <row r="83" spans="1:4">
+    <row r="83" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A83">
         <v>510</v>
       </c>
@@ -1988,7 +1968,7 @@
         <v>0.91745675309284236</v>
       </c>
     </row>
-    <row r="84" spans="1:4">
+    <row r="84" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A84">
         <v>520</v>
       </c>
@@ -2002,7 +1982,7 @@
         <v>3.9527780819638081</v>
       </c>
     </row>
-    <row r="85" spans="1:4">
+    <row r="85" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A85">
         <v>530</v>
       </c>
@@ -2016,7 +1996,7 @@
         <v>0.48329068692591459</v>
       </c>
     </row>
-    <row r="86" spans="1:4">
+    <row r="86" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A86">
         <v>540</v>
       </c>
@@ -2030,7 +2010,7 @@
         <v>-2.3925259518518893</v>
       </c>
     </row>
-    <row r="87" spans="1:4">
+    <row r="87" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A87">
         <v>550</v>
       </c>
@@ -2044,7 +2024,7 @@
         <v>1.8123264178816179</v>
       </c>
     </row>
-    <row r="88" spans="1:4">
+    <row r="88" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A88">
         <v>560</v>
       </c>
@@ -2058,7 +2038,7 @@
         <v>2.1571167913917586</v>
       </c>
     </row>
-    <row r="89" spans="1:4">
+    <row r="89" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A89">
         <v>570</v>
       </c>
@@ -2072,7 +2052,7 @@
         <v>-0.11800833430770208</v>
       </c>
     </row>
-    <row r="90" spans="1:4">
+    <row r="90" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A90">
         <v>580</v>
       </c>
@@ -2086,7 +2066,7 @@
         <v>-4.0635166761945127</v>
       </c>
     </row>
-    <row r="91" spans="1:4">
+    <row r="91" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A91">
         <v>595</v>
       </c>
@@ -2100,7 +2080,7 @@
         <v>-1.5272825471461937</v>
       </c>
     </row>
-    <row r="92" spans="1:4">
+    <row r="92" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A92">
         <v>610</v>
       </c>
@@ -2114,7 +2094,7 @@
         <v>1.0927134953255813E-2</v>
       </c>
     </row>
-    <row r="93" spans="1:4">
+    <row r="93" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A93">
         <v>625</v>
       </c>
@@ -2128,7 +2108,7 @@
         <v>1.5402994571295059</v>
       </c>
     </row>
-    <row r="94" spans="1:4">
+    <row r="94" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A94">
         <v>640</v>
       </c>
@@ -2142,7 +2122,7 @@
         <v>4.2483983236790213</v>
       </c>
     </row>
-    <row r="95" spans="1:4">
+    <row r="95" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A95">
         <v>655</v>
       </c>
@@ -2156,7 +2136,7 @@
         <v>4.2867624084882285</v>
       </c>
     </row>
-    <row r="96" spans="1:4">
+    <row r="96" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A96">
         <v>670</v>
       </c>
@@ -2170,7 +2150,7 @@
         <v>-1.3446264576145028</v>
       </c>
     </row>
-    <row r="97" spans="1:4">
+    <row r="97" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A97">
         <v>685</v>
       </c>
@@ -2184,7 +2164,7 @@
         <v>-0.4194043693088545</v>
       </c>
     </row>
-    <row r="98" spans="1:4">
+    <row r="98" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A98">
         <v>700</v>
       </c>
@@ -2198,7 +2178,7 @@
         <v>4.0888939258471666</v>
       </c>
     </row>
-    <row r="99" spans="1:4">
+    <row r="99" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A99">
         <v>715</v>
       </c>
@@ -2212,7 +2192,7 @@
         <v>2.5930996787243545</v>
       </c>
     </row>
-    <row r="100" spans="1:4">
+    <row r="100" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A100">
         <v>730</v>
       </c>
@@ -2226,7 +2206,7 @@
         <v>-2.8048482978831202</v>
       </c>
     </row>
-    <row r="101" spans="1:4">
+    <row r="101" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A101">
         <v>745</v>
       </c>
@@ -2240,7 +2220,7 @@
         <v>-1.7776562109683391</v>
       </c>
     </row>
-    <row r="102" spans="1:4">
+    <row r="102" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A102">
         <v>760</v>
       </c>
@@ -2254,7 +2234,7 @@
         <v>3.3955029994805139</v>
       </c>
     </row>
-    <row r="103" spans="1:4">
+    <row r="103" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A103">
         <v>775</v>
       </c>
@@ -2268,7 +2248,7 @@
         <v>-4.8258234804074762</v>
       </c>
     </row>
-    <row r="104" spans="1:4">
+    <row r="104" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A104">
         <v>790</v>
       </c>
@@ -2282,7 +2262,7 @@
         <v>4.2173923432814897</v>
       </c>
     </row>
-    <row r="105" spans="1:4">
+    <row r="105" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A105">
         <v>805</v>
       </c>
@@ -2296,7 +2276,7 @@
         <v>1.6221113895410877</v>
       </c>
     </row>
-    <row r="106" spans="1:4">
+    <row r="106" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A106">
         <v>820</v>
       </c>
@@ -2310,7 +2290,7 @@
         <v>-1.8969917044986195</v>
       </c>
     </row>
-    <row r="107" spans="1:4">
+    <row r="107" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A107">
         <v>835</v>
       </c>
@@ -2324,7 +2304,7 @@
         <v>-1.0217480698132586</v>
       </c>
     </row>
-    <row r="108" spans="1:4">
+    <row r="108" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A108">
         <v>850</v>
       </c>
@@ -2338,7 +2318,7 @@
         <v>1.4569720227085992</v>
       </c>
     </row>
-    <row r="109" spans="1:4">
+    <row r="109" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A109">
         <v>865</v>
       </c>
@@ -2352,7 +2332,7 @@
         <v>-1.5967531597427365</v>
       </c>
     </row>
-    <row r="110" spans="1:4">
+    <row r="110" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A110">
         <v>880</v>
       </c>
@@ -2366,7 +2346,7 @@
         <v>3.0809422581490811</v>
       </c>
     </row>
-    <row r="111" spans="1:4">
+    <row r="111" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A111">
         <v>895</v>
       </c>
@@ -2380,7 +2360,7 @@
         <v>-2.9775758775475856</v>
       </c>
     </row>
-    <row r="112" spans="1:4">
+    <row r="112" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A112">
         <v>910</v>
       </c>
@@ -2394,7 +2374,7 @@
         <v>2.2056100851896163</v>
       </c>
     </row>
-    <row r="113" spans="1:4">
+    <row r="113" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A113">
         <v>925</v>
       </c>
@@ -2408,7 +2388,7 @@
         <v>4.4293783830987934</v>
       </c>
     </row>
-    <row r="114" spans="1:4">
+    <row r="114" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A114">
         <v>940</v>
       </c>
@@ -2422,7 +2402,7 @@
         <v>3.5274759449709214</v>
       </c>
     </row>
-    <row r="115" spans="1:4">
+    <row r="115" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A115">
         <v>955</v>
       </c>
@@ -2436,7 +2416,7 @@
         <v>-1.7043559373445594</v>
       </c>
     </row>
-    <row r="116" spans="1:4">
+    <row r="116" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A116">
         <v>970</v>
       </c>
@@ -2450,7 +2430,7 @@
         <v>-2.9064141141066568</v>
       </c>
     </row>
-    <row r="117" spans="1:4">
+    <row r="117" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A117">
         <v>985</v>
       </c>
@@ -2464,7 +2444,7 @@
         <v>3.4614174938740359</v>
       </c>
     </row>
-    <row r="118" spans="1:4">
+    <row r="118" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A118">
         <v>1000</v>
       </c>
@@ -2478,7 +2458,7 @@
         <v>-1.7887499853489119</v>
       </c>
     </row>
-    <row r="119" spans="1:4">
+    <row r="119" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A119">
         <v>1015</v>
       </c>
@@ -2492,7 +2472,7 @@
         <v>-3.0245303812850577</v>
       </c>
     </row>
-    <row r="120" spans="1:4">
+    <row r="120" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A120">
         <v>1030</v>
       </c>
@@ -2506,7 +2486,7 @@
         <v>0.24071602899060074</v>
       </c>
     </row>
-    <row r="121" spans="1:4">
+    <row r="121" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A121">
         <v>1045</v>
       </c>
@@ -2520,7 +2500,7 @@
         <v>-1.0485681083140996</v>
       </c>
     </row>
-    <row r="122" spans="1:4">
+    <row r="122" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A122">
         <v>1060</v>
       </c>
@@ -2534,7 +2514,7 @@
         <v>0.12568295209392955</v>
       </c>
     </row>
-    <row r="123" spans="1:4">
+    <row r="123" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A123">
         <v>1075</v>
       </c>
@@ -2548,7 +2528,7 @@
         <v>-4.8138871856405929</v>
       </c>
     </row>
-    <row r="124" spans="1:4">
+    <row r="124" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A124">
         <v>1090</v>
       </c>
@@ -2562,7 +2542,7 @@
         <v>3.3723983243154034</v>
       </c>
     </row>
-    <row r="125" spans="1:4">
+    <row r="125" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A125">
         <v>1105</v>
       </c>
@@ -2576,7 +2556,7 @@
         <v>-4.2884924541841842</v>
       </c>
     </row>
-    <row r="126" spans="1:4">
+    <row r="126" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A126">
         <v>1120</v>
       </c>
@@ -2590,7 +2570,7 @@
         <v>4.2347790302627732</v>
       </c>
     </row>
-    <row r="127" spans="1:4">
+    <row r="127" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A127">
         <v>1135</v>
       </c>
@@ -2604,7 +2584,7 @@
         <v>-2.7741450737202946</v>
       </c>
     </row>
-    <row r="128" spans="1:4">
+    <row r="128" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A128">
         <v>1150</v>
       </c>
@@ -2618,7 +2598,7 @@
         <v>2.7230188137295164</v>
       </c>
     </row>
-    <row r="129" spans="1:4">
+    <row r="129" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A129">
         <v>1165</v>
       </c>
@@ -2632,7 +2612,7 @@
         <v>-4.3497530897306653</v>
       </c>
     </row>
-    <row r="130" spans="1:4">
+    <row r="130" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A130">
         <v>1180</v>
       </c>
@@ -2646,7 +2626,7 @@
         <v>-4.806178953054081</v>
       </c>
     </row>
-    <row r="131" spans="1:4">
+    <row r="131" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A131">
         <v>1195</v>
       </c>
@@ -2660,7 +2640,7 @@
         <v>3.2450264301798537</v>
       </c>
     </row>
-    <row r="132" spans="1:4">
+    <row r="132" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A132">
         <v>1210</v>
       </c>
@@ -2681,1058 +2661,1860 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:D26"/>
-  <sheetFormatPr defaultRowHeight="14.75"/>
-  <sheetData>
-    <row r="1" spans="1:4">
-      <c r="A1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4">
-      <c r="A2">
-        <v>0</v>
-      </c>
-      <c r="B2">
-        <v>0</v>
-      </c>
-      <c r="C2">
-        <v>0</v>
-      </c>
-      <c r="D2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
-      <c r="A3">
-        <v>2</v>
-      </c>
-      <c r="B3">
-        <v>-0.15000000000000002</v>
-      </c>
-      <c r="C3">
-        <v>0.30000000000000004</v>
-      </c>
-      <c r="D3">
-        <v>0.9</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
-      <c r="A4">
-        <v>4</v>
-      </c>
-      <c r="B4">
-        <v>0.30000000000000004</v>
-      </c>
-      <c r="C4">
-        <v>0.60000000000000009</v>
-      </c>
-      <c r="D4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4">
-      <c r="A5">
-        <v>6</v>
-      </c>
-      <c r="B5">
-        <v>0.44999999999999996</v>
-      </c>
-      <c r="C5">
-        <v>0.90000000000000013</v>
-      </c>
-      <c r="D5">
-        <v>1.1000000000000001</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4">
-      <c r="A6">
-        <v>8</v>
-      </c>
-      <c r="B6">
-        <v>0.90000000000000013</v>
-      </c>
-      <c r="C6">
-        <v>1.2000000000000002</v>
-      </c>
-      <c r="D6">
-        <v>1.3</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4">
-      <c r="A7">
-        <v>10</v>
-      </c>
-      <c r="B7">
-        <v>1.35</v>
-      </c>
-      <c r="C7">
-        <v>1.05</v>
-      </c>
-      <c r="D7">
-        <v>1.4000000000000001</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4">
-      <c r="A8">
-        <v>12</v>
-      </c>
-      <c r="B8">
-        <v>1.6500000000000001</v>
-      </c>
-      <c r="C8">
-        <v>0.60000000000000009</v>
-      </c>
-      <c r="D8">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4">
-      <c r="A9">
-        <v>14</v>
-      </c>
-      <c r="B9">
-        <v>1.5</v>
-      </c>
-      <c r="C9">
-        <v>0</v>
-      </c>
-      <c r="D9">
-        <v>1.3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4">
-      <c r="A10">
-        <v>16</v>
-      </c>
-      <c r="B10">
-        <v>1.2000000000000002</v>
-      </c>
-      <c r="C10">
-        <v>-0.60000000000000009</v>
-      </c>
-      <c r="D10">
-        <v>1.2000000000000002</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4">
-      <c r="A11">
-        <v>18</v>
-      </c>
-      <c r="B11">
-        <v>0.45000000000000007</v>
-      </c>
-      <c r="C11">
-        <v>-1.2000000000000002</v>
-      </c>
-      <c r="D11">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4">
-      <c r="A12">
-        <v>20</v>
-      </c>
-      <c r="B12">
-        <v>-0.30000000000000004</v>
-      </c>
-      <c r="C12">
-        <v>-1.35</v>
-      </c>
-      <c r="D12">
-        <v>0.8</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4">
-      <c r="A13">
-        <v>22</v>
-      </c>
-      <c r="B13">
-        <v>-0.45000000000000007</v>
-      </c>
-      <c r="C13">
-        <v>-1.05</v>
-      </c>
-      <c r="D13">
-        <v>0.70000000000000007</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4">
-      <c r="A14">
-        <v>24</v>
-      </c>
-      <c r="B14">
-        <v>0</v>
-      </c>
-      <c r="C14">
-        <v>-0.75</v>
-      </c>
-      <c r="D14">
-        <v>0.60000000000000009</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4">
-      <c r="A15">
-        <v>26</v>
-      </c>
-      <c r="B15">
-        <v>0.60000000000000009</v>
-      </c>
-      <c r="C15">
-        <v>-0.90000000000000013</v>
-      </c>
-      <c r="D15">
-        <v>0.70000000000000007</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4">
-      <c r="A16">
-        <v>28</v>
-      </c>
-      <c r="B16">
-        <v>1.5</v>
-      </c>
-      <c r="C16">
-        <v>-0.90000000000000013</v>
-      </c>
-      <c r="D16">
-        <v>0.9</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4">
-      <c r="A17">
-        <v>30</v>
-      </c>
-      <c r="B17">
-        <v>1.8000000000000003</v>
-      </c>
-      <c r="C17">
-        <v>-0.30000000000000004</v>
-      </c>
-      <c r="D17">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4">
-      <c r="A18">
-        <v>32</v>
-      </c>
-      <c r="B18">
-        <v>1.2000000000000002</v>
-      </c>
-      <c r="C18">
-        <v>0.60000000000000009</v>
-      </c>
-      <c r="D18">
-        <v>1.1000000000000001</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4">
-      <c r="A19">
-        <v>34</v>
-      </c>
-      <c r="B19">
-        <v>0.45000000000000007</v>
-      </c>
-      <c r="C19">
-        <v>0.90000000000000013</v>
-      </c>
-      <c r="D19">
-        <v>1.2000000000000002</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4">
-      <c r="A20">
-        <v>36</v>
-      </c>
-      <c r="B20">
-        <v>-0.30000000000000004</v>
-      </c>
-      <c r="C20">
-        <v>1.05</v>
-      </c>
-      <c r="D20">
-        <v>1.3</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4">
-      <c r="A21">
-        <v>38</v>
-      </c>
-      <c r="B21">
-        <v>-1.05</v>
-      </c>
-      <c r="C21">
-        <v>0.30000000000000004</v>
-      </c>
-      <c r="D21">
-        <v>1.2000000000000002</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4">
-      <c r="A22">
-        <v>40</v>
-      </c>
-      <c r="B22">
-        <v>-0.90000000000000013</v>
-      </c>
-      <c r="C22">
-        <v>-0.90000000000000013</v>
-      </c>
-      <c r="D22">
-        <v>1.3</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4">
-      <c r="A23">
-        <v>42</v>
-      </c>
-      <c r="B23">
-        <v>-0.60000000000000009</v>
-      </c>
-      <c r="C23">
-        <v>-0.89999999999999991</v>
-      </c>
-      <c r="D23">
-        <v>1.2000000000000002</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4">
-      <c r="A24">
-        <v>44</v>
-      </c>
-      <c r="B24">
-        <v>-0.44999999999999996</v>
-      </c>
-      <c r="C24">
-        <v>-0.60000000000000009</v>
-      </c>
-      <c r="D24">
-        <v>1.1000000000000001</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4">
-      <c r="A25">
-        <v>46</v>
-      </c>
-      <c r="B25">
-        <v>0.15000000000000002</v>
-      </c>
-      <c r="C25">
-        <v>-0.30000000000000004</v>
-      </c>
-      <c r="D25">
-        <v>1.05</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4">
-      <c r="A26">
-        <v>48</v>
-      </c>
-      <c r="B26">
-        <v>0</v>
-      </c>
-      <c r="C26">
-        <v>0</v>
-      </c>
-      <c r="D26">
-        <v>1</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="3"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="262" orientation="landscape" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:D26"/>
-  <sheetFormatPr defaultRowHeight="14.75"/>
-  <sheetData>
-    <row r="1" spans="1:4">
-      <c r="A1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4">
-      <c r="A2">
-        <v>0</v>
-      </c>
-      <c r="B2">
-        <v>0</v>
-      </c>
-      <c r="C2">
-        <v>0</v>
-      </c>
-      <c r="D2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
-      <c r="A3">
-        <v>3</v>
-      </c>
-      <c r="B3">
-        <v>-0.15000000000000002</v>
-      </c>
-      <c r="C3">
-        <v>0.30000000000000004</v>
-      </c>
-      <c r="D3">
-        <v>0.9</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
-      <c r="A4">
-        <v>6</v>
-      </c>
-      <c r="B4">
-        <v>0.30000000000000004</v>
-      </c>
-      <c r="C4">
-        <v>0.60000000000000009</v>
-      </c>
-      <c r="D4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4">
-      <c r="A5">
-        <v>9</v>
-      </c>
-      <c r="B5">
-        <v>0.44999999999999996</v>
-      </c>
-      <c r="C5">
-        <v>0.90000000000000013</v>
-      </c>
-      <c r="D5">
-        <v>1.1000000000000001</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4">
-      <c r="A6">
-        <v>12</v>
-      </c>
-      <c r="B6">
-        <v>0.90000000000000013</v>
-      </c>
-      <c r="C6">
-        <v>1.2000000000000002</v>
-      </c>
-      <c r="D6">
-        <v>1.3</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4">
-      <c r="A7">
-        <v>15</v>
-      </c>
-      <c r="B7">
-        <v>1.35</v>
-      </c>
-      <c r="C7">
-        <v>1.05</v>
-      </c>
-      <c r="D7">
-        <v>1.4000000000000001</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4">
-      <c r="A8">
-        <v>18</v>
-      </c>
-      <c r="B8">
-        <v>1.6500000000000001</v>
-      </c>
-      <c r="C8">
-        <v>0.60000000000000009</v>
-      </c>
-      <c r="D8">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4">
-      <c r="A9">
-        <v>21</v>
-      </c>
-      <c r="B9">
-        <v>1.5</v>
-      </c>
-      <c r="C9">
-        <v>0</v>
-      </c>
-      <c r="D9">
-        <v>1.3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4">
-      <c r="A10">
-        <v>24</v>
-      </c>
-      <c r="B10">
-        <v>1.2000000000000002</v>
-      </c>
-      <c r="C10">
-        <v>-0.60000000000000009</v>
-      </c>
-      <c r="D10">
-        <v>1.2000000000000002</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4">
-      <c r="A11">
-        <v>27</v>
-      </c>
-      <c r="B11">
-        <v>0.45000000000000007</v>
-      </c>
-      <c r="C11">
-        <v>-1.2000000000000002</v>
-      </c>
-      <c r="D11">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4">
-      <c r="A12">
-        <v>30</v>
-      </c>
-      <c r="B12">
-        <v>-0.30000000000000004</v>
-      </c>
-      <c r="C12">
-        <v>-1.35</v>
-      </c>
-      <c r="D12">
-        <v>0.8</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4">
-      <c r="A13">
-        <v>33</v>
-      </c>
-      <c r="B13">
-        <v>-0.45000000000000007</v>
-      </c>
-      <c r="C13">
-        <v>-1.05</v>
-      </c>
-      <c r="D13">
-        <v>0.70000000000000007</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4">
-      <c r="A14">
-        <v>36</v>
-      </c>
-      <c r="B14">
-        <v>0</v>
-      </c>
-      <c r="C14">
-        <v>-0.75</v>
-      </c>
-      <c r="D14">
-        <v>0.60000000000000009</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4">
-      <c r="A15">
-        <v>39</v>
-      </c>
-      <c r="B15">
-        <v>0.60000000000000009</v>
-      </c>
-      <c r="C15">
-        <v>-0.90000000000000013</v>
-      </c>
-      <c r="D15">
-        <v>0.70000000000000007</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4">
-      <c r="A16">
-        <v>42</v>
-      </c>
-      <c r="B16">
-        <v>1.5</v>
-      </c>
-      <c r="C16">
-        <v>-0.90000000000000013</v>
-      </c>
-      <c r="D16">
-        <v>0.9</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4">
-      <c r="A17">
-        <v>45</v>
-      </c>
-      <c r="B17">
-        <v>1.8000000000000003</v>
-      </c>
-      <c r="C17">
-        <v>-0.30000000000000004</v>
-      </c>
-      <c r="D17">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4">
-      <c r="A18">
-        <v>48</v>
-      </c>
-      <c r="B18">
-        <v>1.2000000000000002</v>
-      </c>
-      <c r="C18">
-        <v>0.60000000000000009</v>
-      </c>
-      <c r="D18">
-        <v>1.1000000000000001</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4">
-      <c r="A19">
-        <v>51</v>
-      </c>
-      <c r="B19">
-        <v>0.45000000000000007</v>
-      </c>
-      <c r="C19">
-        <v>0.90000000000000013</v>
-      </c>
-      <c r="D19">
-        <v>1.2000000000000002</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4">
-      <c r="A20">
-        <v>54</v>
-      </c>
-      <c r="B20">
-        <v>-0.30000000000000004</v>
-      </c>
-      <c r="C20">
-        <v>1.05</v>
-      </c>
-      <c r="D20">
-        <v>1.3</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4">
-      <c r="A21">
-        <v>57</v>
-      </c>
-      <c r="B21">
-        <v>-1.05</v>
-      </c>
-      <c r="C21">
-        <v>0.30000000000000004</v>
-      </c>
-      <c r="D21">
-        <v>1.2000000000000002</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4">
-      <c r="A22">
-        <v>60</v>
-      </c>
-      <c r="B22">
-        <v>-0.90000000000000013</v>
-      </c>
-      <c r="C22">
-        <v>-0.90000000000000013</v>
-      </c>
-      <c r="D22">
-        <v>1.3</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4">
-      <c r="A23">
-        <v>63</v>
-      </c>
-      <c r="B23">
-        <v>-0.60000000000000009</v>
-      </c>
-      <c r="C23">
-        <v>-0.89999999999999991</v>
-      </c>
-      <c r="D23">
-        <v>1.2000000000000002</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4">
-      <c r="A24">
-        <v>66</v>
-      </c>
-      <c r="B24">
-        <v>-0.44999999999999996</v>
-      </c>
-      <c r="C24">
-        <v>-0.60000000000000009</v>
-      </c>
-      <c r="D24">
-        <v>1.1000000000000001</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4">
-      <c r="A25">
-        <v>69</v>
-      </c>
-      <c r="B25">
-        <v>0.15000000000000002</v>
-      </c>
-      <c r="C25">
-        <v>-0.30000000000000004</v>
-      </c>
-      <c r="D25">
-        <v>1.05</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4">
-      <c r="A26">
-        <v>72</v>
-      </c>
-      <c r="B26">
-        <v>0</v>
-      </c>
-      <c r="C26">
-        <v>0</v>
-      </c>
-      <c r="D26">
-        <v>1</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="3"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="262" orientation="landscape" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:D21"/>
-  <sheetFormatPr defaultRowHeight="14.75"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{56A987FB-6A42-4432-9068-D3F18FDE7F8F}">
+  <dimension ref="A1:D132"/>
+  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
   <cols>
-    <col min="1" max="1" width="5.26953125" customWidth="1"/>
+    <col min="1" max="1" width="5.90625" customWidth="1"/>
     <col min="2" max="4" width="6.86328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="B1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C1" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A2">
         <v>0</v>
       </c>
       <c r="B2">
-        <v>0</v>
+        <v>-4.8813534815012529</v>
       </c>
       <c r="C2">
-        <v>0</v>
+        <v>-3.8673993938224838</v>
       </c>
       <c r="D2">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
+        <v>2.5143889596457303E-3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A3">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="B3">
-        <v>0.2</v>
+        <v>-2.0602062718800074</v>
       </c>
       <c r="C3">
-        <v>0.2</v>
+        <v>-0.94277766920159767</v>
       </c>
       <c r="D3">
-        <v>0.70000000000000007</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
+        <v>-1.5923376176110715</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A4">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="B4">
-        <v>-0.2</v>
+        <v>3.5019112961812828</v>
       </c>
       <c r="C4">
-        <v>0.4</v>
+        <v>-4.2437069668487677</v>
       </c>
       <c r="D4">
-        <v>0.9</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4">
+        <v>1.6129946190549993</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A5">
-        <v>9</v>
+        <v>45</v>
       </c>
       <c r="B5">
-        <v>-0.30000000000000004</v>
+        <v>-2.6817263093778698</v>
       </c>
       <c r="C5">
-        <v>0.60000000000000009</v>
+        <v>2.6505132387305608</v>
       </c>
       <c r="D5">
-        <v>1.1000000000000001</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4">
+        <v>0.83740062219910261</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A6">
-        <v>12</v>
+        <v>60</v>
       </c>
       <c r="B6">
-        <v>-0.1</v>
+        <v>2.5407217361544108</v>
       </c>
       <c r="C6">
-        <v>0.9</v>
+        <v>-2.3460881293480984</v>
       </c>
       <c r="D6">
-        <v>1.2000000000000002</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4">
+        <v>0.31680918265487801</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A7">
-        <v>15</v>
+        <v>75</v>
       </c>
       <c r="B7">
-        <v>0.30000000000000004</v>
+        <v>1.8915240555160584</v>
       </c>
       <c r="C7">
-        <v>1</v>
+        <v>0.84691238471568453</v>
       </c>
       <c r="D7">
-        <v>1.4000000000000001</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4">
+        <v>1.2764408752063083</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A8">
-        <v>18</v>
+        <v>90</v>
       </c>
       <c r="B8">
-        <v>0.60000000000000009</v>
+        <v>-0.27169456756774513</v>
       </c>
       <c r="C8">
-        <v>0.8</v>
+        <v>2.6857563237049731</v>
       </c>
       <c r="D8">
-        <v>1.2000000000000002</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4">
+        <v>1.5118664306624763</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A9">
-        <v>21</v>
+        <v>105</v>
       </c>
       <c r="B9">
-        <v>0.70000000000000007</v>
+        <v>-2.2178776983275519</v>
       </c>
       <c r="C9">
-        <v>0.4</v>
+        <v>1.1673627186491209</v>
       </c>
       <c r="D9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4">
+        <v>-4.7307536154024357</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A10">
-        <v>24</v>
+        <v>120</v>
       </c>
       <c r="B10">
-        <v>0.8</v>
+        <v>1.0721479615677432</v>
       </c>
       <c r="C10">
-        <v>0</v>
+        <v>-3.5214842798093535</v>
       </c>
       <c r="D10">
-        <v>1.1000000000000001</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4">
+        <v>2.0098215069291472</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A11">
-        <v>27</v>
+        <v>135</v>
       </c>
       <c r="B11">
-        <v>0.9</v>
+        <v>4.8921835582064643</v>
       </c>
       <c r="C11">
-        <v>-0.30000000000000004</v>
+        <v>3.2599786450223425</v>
       </c>
       <c r="D11">
-        <v>1.3000000000000003</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4">
+        <v>2.2459930027101969</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A12">
-        <v>30</v>
+        <v>150</v>
       </c>
       <c r="B12">
-        <v>0.9</v>
+        <v>-4.74591588350264</v>
       </c>
       <c r="C12">
-        <v>-0.60000000000000009</v>
+        <v>-2.831942346179491</v>
       </c>
       <c r="D12">
-        <v>1.1000000000000001</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4">
+        <v>-0.71427041847938133</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A13">
-        <v>33</v>
+        <v>165</v>
       </c>
       <c r="B13">
-        <v>0.6</v>
+        <v>-3.8827915697349278</v>
       </c>
       <c r="C13">
-        <v>-0.8</v>
+        <v>-1.5094547143303716</v>
       </c>
       <c r="D13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4">
+        <v>0.87411558151694102</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A14">
-        <v>36</v>
+        <v>180</v>
       </c>
       <c r="B14">
-        <v>0.1</v>
+        <v>1.6294329515630712</v>
       </c>
       <c r="C14">
-        <v>-0.9</v>
+        <v>-2.9688559791560443</v>
       </c>
       <c r="D14">
-        <v>0.8</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4">
+        <v>0.50678709178415882</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A15">
-        <v>39</v>
+        <v>195</v>
       </c>
       <c r="B15">
-        <v>-0.2</v>
+        <v>-1.3704979855447175</v>
       </c>
       <c r="C15">
-        <v>-0.9</v>
+        <v>-2.7947981773155361</v>
       </c>
       <c r="D15">
-        <v>0.70000000000000007</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4">
+        <v>-0.30624051417129095</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A16">
-        <v>42</v>
+        <v>210</v>
       </c>
       <c r="B16">
-        <v>-0.5</v>
+        <v>4.5702315141919927</v>
       </c>
       <c r="C16">
-        <v>-0.70000000000000007</v>
+        <v>3.8710976753359185</v>
       </c>
       <c r="D16">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4">
+        <v>-3.9146105313087345</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A17">
-        <v>45</v>
+        <v>225</v>
       </c>
       <c r="B17">
-        <v>-0.5</v>
+        <v>-2.2165518621442146</v>
       </c>
       <c r="C17">
-        <v>-0.30000000000000004</v>
+        <v>-0.7447979455173559</v>
       </c>
       <c r="D17">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4">
+        <v>4.7602624075810045</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A18">
-        <v>48</v>
+        <v>240</v>
       </c>
       <c r="B18">
-        <v>-0.60000000000000009</v>
+        <v>1.4688548050695927</v>
       </c>
       <c r="C18">
-        <v>0</v>
+        <v>0.47317837588559009</v>
       </c>
       <c r="D18">
-        <v>0.70000000000000007</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4">
+        <v>-1.3399947978837368</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A19">
-        <v>51</v>
+        <v>255</v>
       </c>
       <c r="B19">
-        <v>-0.9</v>
+        <v>3.9447910925374394</v>
       </c>
       <c r="C19">
-        <v>0.2</v>
+        <v>1.7643154495019142</v>
       </c>
       <c r="D19">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4">
+        <v>-4.215366851019021</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A20">
-        <v>54</v>
+        <v>270</v>
       </c>
       <c r="B20">
-        <v>-1.2000000000000002</v>
+        <v>-2.0942642611540094</v>
       </c>
       <c r="C20">
-        <v>0.5</v>
+        <v>3.7123799349961697</v>
       </c>
       <c r="D20">
-        <v>1.3</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4">
+        <v>-4.4653950180761024</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A21">
-        <v>57</v>
+        <v>285</v>
       </c>
       <c r="B21">
-        <v>-0.70000000000000007</v>
+        <v>-0.97096386865342499</v>
       </c>
       <c r="C21">
-        <v>1.1000000000000001</v>
+        <v>4.4730814032884378</v>
       </c>
       <c r="D21">
-        <v>1.5</v>
+        <v>2.3174510546711211</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A22">
+        <v>300</v>
+      </c>
+      <c r="B22">
+        <v>3.9898342512186344</v>
+      </c>
+      <c r="C22">
+        <v>0.97739136892693868</v>
+      </c>
+      <c r="D22">
+        <v>-2.4469565685518155</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A23">
+        <v>315</v>
+      </c>
+      <c r="B23">
+        <v>-0.81417950602545086</v>
+      </c>
+      <c r="C23">
+        <v>-2.0801503557505843</v>
+      </c>
+      <c r="D23">
+        <v>-2.5539097033394507</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A24">
+        <v>330</v>
+      </c>
+      <c r="B24">
+        <v>-0.93424293384985924</v>
+      </c>
+      <c r="C24">
+        <v>0.92326235920522248</v>
+      </c>
+      <c r="D24">
+        <v>-1.4459965599407432</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A25">
+        <v>345</v>
+      </c>
+      <c r="B25">
+        <v>-4.6792358728595742</v>
+      </c>
+      <c r="C25">
+        <v>4.934049225181381</v>
+      </c>
+      <c r="D25">
+        <v>1.0008415884716482</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A26">
+        <v>360</v>
+      </c>
+      <c r="B26">
+        <v>-4.2436047352558415</v>
+      </c>
+      <c r="C26">
+        <v>-0.45942761759381057</v>
+      </c>
+      <c r="D26">
+        <v>2.2443406250490772</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A27">
+        <v>375</v>
+      </c>
+      <c r="B27">
+        <v>-0.36047817813442462</v>
+      </c>
+      <c r="C27">
+        <v>-2.5090264350269598</v>
+      </c>
+      <c r="D27">
+        <v>-4.0960986361258698</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A28">
+        <v>390</v>
+      </c>
+      <c r="B28">
+        <v>-0.67576797264878086</v>
+      </c>
+      <c r="C28">
+        <v>-1.1837551605264862</v>
+      </c>
+      <c r="D28">
+        <v>4.6934286332964223</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A29">
+        <v>405</v>
+      </c>
+      <c r="B29">
+        <v>-0.6019186430811263</v>
+      </c>
+      <c r="C29">
+        <v>1.3661269341432813</v>
+      </c>
+      <c r="D29">
+        <v>-4.3769391712908945</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A30">
+        <v>420</v>
+      </c>
+      <c r="B30">
+        <v>1.433163547676094</v>
+      </c>
+      <c r="C30">
+        <v>-4.6152538955823195</v>
+      </c>
+      <c r="D30">
+        <v>4.3936324237126261</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A31">
+        <v>435</v>
+      </c>
+      <c r="B31">
+        <v>-1.38569602342556</v>
+      </c>
+      <c r="C31">
+        <v>-2.2173010102656345</v>
+      </c>
+      <c r="D31">
+        <v>-0.17059200732076563</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A32">
+        <v>450</v>
+      </c>
+      <c r="B32">
+        <v>-0.28443319938492584</v>
+      </c>
+      <c r="C32">
+        <v>0.46291187348874829</v>
+      </c>
+      <c r="D32">
+        <v>3.3104073633841615</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A33">
+        <v>465</v>
+      </c>
+      <c r="B33">
+        <v>0.90734273354822093</v>
+      </c>
+      <c r="C33">
+        <v>-2.1023101036883074</v>
+      </c>
+      <c r="D33">
+        <v>-1.1286388991793495</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A34">
+        <v>480</v>
+      </c>
+      <c r="B34">
+        <v>0.92939808667390267</v>
+      </c>
+      <c r="C34">
+        <v>-0.43938645369899221</v>
+      </c>
+      <c r="D34">
+        <v>1.6923601147740586</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A35">
+        <v>495</v>
+      </c>
+      <c r="B35">
+        <v>2.6563729888972198</v>
+      </c>
+      <c r="C35">
+        <v>-4.3469967459118664</v>
+      </c>
+      <c r="D35">
+        <v>1.9493721341731607</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A36">
+        <v>510</v>
+      </c>
+      <c r="B36">
+        <v>-4.8616822245528457</v>
+      </c>
+      <c r="C36">
+        <v>2.8255431815904473</v>
+      </c>
+      <c r="D36">
+        <v>-3.5731428814234665</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A37">
+        <v>525</v>
+      </c>
+      <c r="B37">
+        <v>1.2213868186149923</v>
+      </c>
+      <c r="C37">
+        <v>4.2221700253778298</v>
+      </c>
+      <c r="D37">
+        <v>-0.16824547684147206</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A38">
+        <v>540</v>
+      </c>
+      <c r="B38">
+        <v>-0.62076403981803141</v>
+      </c>
+      <c r="C38">
+        <v>-2.6237990327379257</v>
+      </c>
+      <c r="D38">
+        <v>3.7545109810478063</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A39">
+        <v>555</v>
+      </c>
+      <c r="B39">
+        <v>-4.0952812130328056</v>
+      </c>
+      <c r="C39">
+        <v>2.867656174086787</v>
+      </c>
+      <c r="D39">
+        <v>0.54078060347251378</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A40">
+        <v>570</v>
+      </c>
+      <c r="B40">
+        <v>3.4071331708232511</v>
+      </c>
+      <c r="C40">
+        <v>-0.97155530944262991</v>
+      </c>
+      <c r="D40">
+        <v>-3.5212793126992183</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A41">
+        <v>585</v>
+      </c>
+      <c r="B41">
+        <v>4.5013978377255146</v>
+      </c>
+      <c r="C41">
+        <v>4.4576030628111294</v>
+      </c>
+      <c r="D41">
+        <v>-3.8327216751578455</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A42">
+        <v>600</v>
+      </c>
+      <c r="B42">
+        <v>-0.93929512402725623</v>
+      </c>
+      <c r="C42">
+        <v>1.129152093139848</v>
+      </c>
+      <c r="D42">
+        <v>-1.4043363221400995</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A43">
+        <v>615</v>
+      </c>
+      <c r="B43">
+        <v>4.7998974020323404</v>
+      </c>
+      <c r="C43">
+        <v>2.8231358328103004</v>
+      </c>
+      <c r="D43">
+        <v>-0.30766453615983513</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A44">
+        <v>630</v>
+      </c>
+      <c r="B44">
+        <v>-4.89252447113667</v>
+      </c>
+      <c r="C44">
+        <v>-2.3708854385833544</v>
+      </c>
+      <c r="D44">
+        <v>-2.2974788731457716</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A45">
+        <v>645</v>
+      </c>
+      <c r="B45">
+        <v>2.5306529641266007</v>
+      </c>
+      <c r="C45">
+        <v>4.082743062422467</v>
+      </c>
+      <c r="D45">
+        <v>-2.6040236745237264</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A46">
+        <v>660</v>
+      </c>
+      <c r="B46">
+        <v>-4.9196881340079548</v>
+      </c>
+      <c r="C46">
+        <v>4.2611085427489712</v>
+      </c>
+      <c r="D46">
+        <v>-1.6267749651982433</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A47">
+        <v>675</v>
+      </c>
+      <c r="B47">
+        <v>4.8656432084729886</v>
+      </c>
+      <c r="C47">
+        <v>-2.6560895153567419</v>
+      </c>
+      <c r="D47">
+        <v>-2.7558778901116519</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A48">
+        <v>690</v>
+      </c>
+      <c r="B48">
+        <v>-2.7256058217560675</v>
+      </c>
+      <c r="C48">
+        <v>-2.6742117742992164</v>
+      </c>
+      <c r="D48">
+        <v>-3.3307752325489925</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A49">
+        <v>705</v>
+      </c>
+      <c r="B49">
+        <v>3.3859690257313222</v>
+      </c>
+      <c r="C49">
+        <v>-3.5209423133789821</v>
+      </c>
+      <c r="D49">
+        <v>-3.788865812315485</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A50">
+        <v>720</v>
+      </c>
+      <c r="B50">
+        <v>-2.0239290627620701</v>
+      </c>
+      <c r="C50">
+        <v>-2.9899328266432246</v>
+      </c>
+      <c r="D50">
+        <v>1.9163100448142745</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A51">
+        <v>735</v>
+      </c>
+      <c r="B51">
+        <v>-4.4515573250968572</v>
+      </c>
+      <c r="C51">
+        <v>-1.1594434350692973</v>
+      </c>
+      <c r="D51">
+        <v>-0.45171651463562945</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A52">
+        <v>750</v>
+      </c>
+      <c r="B52">
+        <v>1.3261736814678737</v>
+      </c>
+      <c r="C52">
+        <v>-0.11706339357034468</v>
+      </c>
+      <c r="D52">
+        <v>1.1204968011208316</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A53">
+        <v>765</v>
+      </c>
+      <c r="B53">
+        <v>4.8058299386193104</v>
+      </c>
+      <c r="C53">
+        <v>1.7200741589290802</v>
+      </c>
+      <c r="D53">
+        <v>0.18901859959311484</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A54">
+        <v>780</v>
+      </c>
+      <c r="B54">
+        <v>3.2640992749855591</v>
+      </c>
+      <c r="C54">
+        <v>1.2409631160851486</v>
+      </c>
+      <c r="D54">
+        <v>-4.8986444451687134</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A55">
+        <v>795</v>
+      </c>
+      <c r="B55">
+        <v>-0.54949878867694313</v>
+      </c>
+      <c r="C55">
+        <v>4.8336780584555399</v>
+      </c>
+      <c r="D55">
+        <v>-1.9404129043036511</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A56">
+        <v>810</v>
+      </c>
+      <c r="B56">
+        <v>3.9766342698996668</v>
+      </c>
+      <c r="C56">
+        <v>-0.96813789951125329</v>
+      </c>
+      <c r="D56">
+        <v>0.94956400116934403</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A57">
+        <v>825</v>
+      </c>
+      <c r="B57">
+        <v>-0.68141613263433376</v>
+      </c>
+      <c r="C57">
+        <v>-1.5193604879797995</v>
+      </c>
+      <c r="D57">
+        <v>-2.4333099525699255</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A58">
+        <v>840</v>
+      </c>
+      <c r="B58">
+        <v>0.76809773677195436</v>
+      </c>
+      <c r="C58">
+        <v>-4.8865735268898147E-2</v>
+      </c>
+      <c r="D58">
+        <v>2.3275889108562451</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A59">
+        <v>855</v>
+      </c>
+      <c r="B59">
+        <v>2.9507776312637288</v>
+      </c>
+      <c r="C59">
+        <v>3.4228136114799899</v>
+      </c>
+      <c r="D59">
+        <v>-1.247873095563059</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A60">
+        <v>870</v>
+      </c>
+      <c r="B60">
+        <v>4.9816973602366907</v>
+      </c>
+      <c r="C60">
+        <v>-3.8847865163494877</v>
+      </c>
+      <c r="D60">
+        <v>3.5941810445347855</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A61">
+        <v>885</v>
+      </c>
+      <c r="B61">
+        <v>2.8933774615437837</v>
+      </c>
+      <c r="C61">
+        <v>-0.24054304717668673</v>
+      </c>
+      <c r="D61">
+        <v>-3.8291408115260084</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A62">
+        <v>900</v>
+      </c>
+      <c r="B62">
+        <v>-2.893184559805678</v>
+      </c>
+      <c r="C62">
+        <v>2.1460721928727011</v>
+      </c>
+      <c r="D62">
+        <v>-0.7527211830211511</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A63">
+        <v>915</v>
+      </c>
+      <c r="B63">
+        <v>4.1835142785279702</v>
+      </c>
+      <c r="C63">
+        <v>-2.2894057795653353</v>
+      </c>
+      <c r="D63">
+        <v>-4.3029135987555609</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A64">
+        <v>930</v>
+      </c>
+      <c r="B64">
+        <v>0.43293936160694102</v>
+      </c>
+      <c r="C64">
+        <v>-4.0501598174717701</v>
+      </c>
+      <c r="D64">
+        <v>-1.7068382992475528</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A65">
+        <v>945</v>
+      </c>
+      <c r="B65">
+        <v>4.0661941778569952</v>
+      </c>
+      <c r="C65">
+        <v>-4.9576798289062776</v>
+      </c>
+      <c r="D65">
+        <v>3.3938672732647945</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A66">
+        <v>960</v>
+      </c>
+      <c r="B66">
+        <v>-2.8613251032492859</v>
+      </c>
+      <c r="C66">
+        <v>-2.2164433304328846</v>
+      </c>
+      <c r="D66">
+        <v>-0.68286055830592107</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A67">
+        <v>975</v>
+      </c>
+      <c r="B67">
+        <v>-2.0003409552530238</v>
+      </c>
+      <c r="C67">
+        <v>-1.3249510085924587</v>
+      </c>
+      <c r="D67">
+        <v>-6.5438526761227855E-2</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A68">
+        <v>990</v>
+      </c>
+      <c r="B68">
+        <v>-4.488988535255281</v>
+      </c>
+      <c r="C68">
+        <v>-4.6163617324152746</v>
+      </c>
+      <c r="D68">
+        <v>-1.7199525526209858</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A69">
+        <v>1005</v>
+      </c>
+      <c r="B69">
+        <v>-2.433048363300383E-2</v>
+      </c>
+      <c r="C69">
+        <v>-2.1971638192486309</v>
+      </c>
+      <c r="D69">
+        <v>0.56093253872197213</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A70">
+        <v>1020</v>
+      </c>
+      <c r="B70">
+        <v>-0.19776177870766021</v>
+      </c>
+      <c r="C70">
+        <v>-2.8512007671570307</v>
+      </c>
+      <c r="D70">
+        <v>-4.6334289050480502</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A71">
+        <v>1035</v>
+      </c>
+      <c r="B71">
+        <v>1.8708629648525466</v>
+      </c>
+      <c r="C71">
+        <v>-1.9820020347219058</v>
+      </c>
+      <c r="D71">
+        <v>-1.3612034211029878</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A72">
+        <v>1050</v>
+      </c>
+      <c r="B72">
+        <v>-3.9324741293504073</v>
+      </c>
+      <c r="C72">
+        <v>2.0632309186963504</v>
+      </c>
+      <c r="D72">
+        <v>4.6054352008508728</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A73">
+        <v>1065</v>
+      </c>
+      <c r="B73">
+        <v>-0.87850174677119197</v>
+      </c>
+      <c r="C73">
+        <v>1.2411398342469537</v>
+      </c>
+      <c r="D73">
+        <v>3.9964315753945767</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A74">
+        <v>1080</v>
+      </c>
+      <c r="B74">
+        <v>-1.1641307916664534</v>
+      </c>
+      <c r="C74">
+        <v>4.3989994804157684</v>
+      </c>
+      <c r="D74">
+        <v>4.4863012889615996</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A75">
+        <v>1095</v>
+      </c>
+      <c r="B75">
+        <v>0.62118701714698799</v>
+      </c>
+      <c r="C75">
+        <v>-4.5357705439657261</v>
+      </c>
+      <c r="D75">
+        <v>0.41246301658184548</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A76">
+        <v>1110</v>
+      </c>
+      <c r="B76">
+        <v>-4.924377848972604</v>
+      </c>
+      <c r="C76">
+        <v>3.5956994769481163</v>
+      </c>
+      <c r="D76">
+        <v>3.3701019276245638</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A77">
+        <v>1125</v>
+      </c>
+      <c r="B77">
+        <v>-1.7406083981738074</v>
+      </c>
+      <c r="C77">
+        <v>-4.028982550593768</v>
+      </c>
+      <c r="D77">
+        <v>3.5927992962940012</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A78">
+        <v>1140</v>
+      </c>
+      <c r="B78">
+        <v>1.0157053465247257</v>
+      </c>
+      <c r="C78">
+        <v>2.593172739209443</v>
+      </c>
+      <c r="D78">
+        <v>-1.7419939426058739</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A79">
+        <v>1155</v>
+      </c>
+      <c r="B79">
+        <v>0.35020159828259456</v>
+      </c>
+      <c r="C79">
+        <v>-4.2418968821045402</v>
+      </c>
+      <c r="D79">
+        <v>3.394090790320432</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A80">
+        <v>1170</v>
+      </c>
+      <c r="B80">
+        <v>3.1810938166725999</v>
+      </c>
+      <c r="C80">
+        <v>3.5377366385570852</v>
+      </c>
+      <c r="D80">
+        <v>-0.19505225160462603</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A81">
+        <v>1185</v>
+      </c>
+      <c r="B81">
+        <v>-2.9525564121572909</v>
+      </c>
+      <c r="C81">
+        <v>2.4502889479219747</v>
+      </c>
+      <c r="D81">
+        <v>2.3867688422087441</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A82">
+        <v>1200</v>
+      </c>
+      <c r="B82">
+        <v>-4.2841889826134336</v>
+      </c>
+      <c r="C82">
+        <v>-3.2497098008334788</v>
+      </c>
+      <c r="D82">
+        <v>-2.8741223271239527</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A83">
+        <v>1215</v>
+      </c>
+      <c r="B83">
+        <v>-4.3023430959363509</v>
+      </c>
+      <c r="C83">
+        <v>1.3469711079959545</v>
+      </c>
+      <c r="D83">
+        <v>0.91745675309284236</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A84">
+        <v>1230</v>
+      </c>
+      <c r="B84">
+        <v>-1.3723078276724976</v>
+      </c>
+      <c r="C84">
+        <v>2.2880276936581625</v>
+      </c>
+      <c r="D84">
+        <v>3.9527780819638081</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A85">
+        <v>1245</v>
+      </c>
+      <c r="B85">
+        <v>0.61384410005318135</v>
+      </c>
+      <c r="C85">
+        <v>-1.9523399984628953</v>
+      </c>
+      <c r="D85">
+        <v>0.48329068692591459</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A86">
+        <v>1260</v>
+      </c>
+      <c r="B86">
+        <v>-4.1446289258943931</v>
+      </c>
+      <c r="C86">
+        <v>-0.62833651884691033</v>
+      </c>
+      <c r="D86">
+        <v>-2.3925259518518893</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A87">
+        <v>1275</v>
+      </c>
+      <c r="B87">
+        <v>-3.8421284601302608</v>
+      </c>
+      <c r="C87">
+        <v>-2.631853643534714</v>
+      </c>
+      <c r="D87">
+        <v>1.8123264178816179</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A88">
+        <v>1290</v>
+      </c>
+      <c r="B88">
+        <v>-1.2878430377367223</v>
+      </c>
+      <c r="C88">
+        <v>1.9866344066500563</v>
+      </c>
+      <c r="D88">
+        <v>2.1571167913917586</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A89">
+        <v>1305</v>
+      </c>
+      <c r="B89">
+        <v>3.4596335403331335</v>
+      </c>
+      <c r="C89">
+        <v>0.21185400240273045</v>
+      </c>
+      <c r="D89">
+        <v>-0.11800833430770208</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A90">
+        <v>1320</v>
+      </c>
+      <c r="B90">
+        <v>-1.5799160138907209</v>
+      </c>
+      <c r="C90">
+        <v>1.8960852154630337</v>
+      </c>
+      <c r="D90">
+        <v>-4.0635166761945127</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A91">
+        <v>1335</v>
+      </c>
+      <c r="B91">
+        <v>-4.7764443707733681</v>
+      </c>
+      <c r="C91">
+        <v>-0.26138461783975497</v>
+      </c>
+      <c r="D91">
+        <v>-1.5272825471461937</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A92">
+        <v>1350</v>
+      </c>
+      <c r="B92">
+        <v>-4.3228847998194304</v>
+      </c>
+      <c r="C92">
+        <v>-0.87634539862270211</v>
+      </c>
+      <c r="D92">
+        <v>1.0927134953255813E-2</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A93">
+        <v>1365</v>
+      </c>
+      <c r="B93">
+        <v>4.0776404284715531</v>
+      </c>
+      <c r="C93">
+        <v>-1.3684933237821428</v>
+      </c>
+      <c r="D93">
+        <v>1.5402994571295059</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A94">
+        <v>1380</v>
+      </c>
+      <c r="B94">
+        <v>1.8079354837491246</v>
+      </c>
+      <c r="C94">
+        <v>0.62852511969122005</v>
+      </c>
+      <c r="D94">
+        <v>4.2483983236790213</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A95">
+        <v>1395</v>
+      </c>
+      <c r="B95">
+        <v>-3.7046710784525305</v>
+      </c>
+      <c r="C95">
+        <v>4.9837135923872804</v>
+      </c>
+      <c r="D95">
+        <v>4.2867624084882285</v>
+      </c>
+    </row>
+    <row r="96" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A96">
+        <v>1410</v>
+      </c>
+      <c r="B96">
+        <v>-2.8461624810754582</v>
+      </c>
+      <c r="C96">
+        <v>3.9527976334120538</v>
+      </c>
+      <c r="D96">
+        <v>-1.3446264576145028</v>
+      </c>
+    </row>
+    <row r="97" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A97">
+        <v>1425</v>
+      </c>
+      <c r="B97">
+        <v>-2.0104093894753197</v>
+      </c>
+      <c r="C97">
+        <v>1.4072015311211938</v>
+      </c>
+      <c r="D97">
+        <v>-0.4194043693088545</v>
+      </c>
+    </row>
+    <row r="98" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A98">
+        <v>1440</v>
+      </c>
+      <c r="B98">
+        <v>0.61691340606465417</v>
+      </c>
+      <c r="C98">
+        <v>-2.3511722008040223</v>
+      </c>
+      <c r="D98">
+        <v>4.0888939258471666</v>
+      </c>
+    </row>
+    <row r="99" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A99">
+        <v>1455</v>
+      </c>
+      <c r="B99">
+        <v>2.1941317275804662</v>
+      </c>
+      <c r="C99">
+        <v>-4.3974520327352291</v>
+      </c>
+      <c r="D99">
+        <v>2.5930996787243545</v>
+      </c>
+    </row>
+    <row r="100" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A100">
+        <v>1470</v>
+      </c>
+      <c r="B100">
+        <v>-4.7494681666739522</v>
+      </c>
+      <c r="C100">
+        <v>-3.4416305544286252</v>
+      </c>
+      <c r="D100">
+        <v>-2.8048482978831202</v>
+      </c>
+    </row>
+    <row r="101" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A101">
+        <v>1485</v>
+      </c>
+      <c r="B101">
+        <v>3.064505732487274</v>
+      </c>
+      <c r="C101">
+        <v>3.7318636388210624</v>
+      </c>
+      <c r="D101">
+        <v>-1.7776562109683391</v>
+      </c>
+    </row>
+    <row r="102" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A102">
+        <v>1500</v>
+      </c>
+      <c r="B102">
+        <v>1.0117659574376836</v>
+      </c>
+      <c r="C102">
+        <v>0.56584157448082539</v>
+      </c>
+      <c r="D102">
+        <v>3.3955029994805139</v>
+      </c>
+    </row>
+    <row r="103" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A103">
+        <v>1515</v>
+      </c>
+      <c r="B103">
+        <v>3.1167453127746194</v>
+      </c>
+      <c r="C103">
+        <v>-0.41585255240951802</v>
+      </c>
+      <c r="D103">
+        <v>-4.8258234804074762</v>
+      </c>
+    </row>
+    <row r="104" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A104">
+        <v>1530</v>
+      </c>
+      <c r="B104">
+        <v>0.81366767755840175</v>
+      </c>
+      <c r="C104">
+        <v>2.5083560394375426</v>
+      </c>
+      <c r="D104">
+        <v>4.2173923432814897</v>
+      </c>
+    </row>
+    <row r="105" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A105">
+        <v>1545</v>
+      </c>
+      <c r="B105">
+        <v>-2.6516235879374204</v>
+      </c>
+      <c r="C105">
+        <v>-1.8241294582819956</v>
+      </c>
+      <c r="D105">
+        <v>1.6221113895410877</v>
+      </c>
+    </row>
+    <row r="106" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A106">
+        <v>1560</v>
+      </c>
+      <c r="B106">
+        <v>-3.6149494706867982</v>
+      </c>
+      <c r="C106">
+        <v>-1.5194556502430279</v>
+      </c>
+      <c r="D106">
+        <v>-1.8969917044986195</v>
+      </c>
+    </row>
+    <row r="107" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A107">
+        <v>1575</v>
+      </c>
+      <c r="B107">
+        <v>-3.8512415089475227</v>
+      </c>
+      <c r="C107">
+        <v>0.79648931064807749</v>
+      </c>
+      <c r="D107">
+        <v>-1.0217480698132586</v>
+      </c>
+    </row>
+    <row r="108" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A108">
+        <v>1590</v>
+      </c>
+      <c r="B108">
+        <v>-4.4131771756663536</v>
+      </c>
+      <c r="C108">
+        <v>3.2603868840373131</v>
+      </c>
+      <c r="D108">
+        <v>1.4569720227085992</v>
+      </c>
+    </row>
+    <row r="109" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A109">
+        <v>1605</v>
+      </c>
+      <c r="B109">
+        <v>-1.0354742141511786</v>
+      </c>
+      <c r="C109">
+        <v>1.4288948270699031</v>
+      </c>
+      <c r="D109">
+        <v>-1.5967531597427365</v>
+      </c>
+    </row>
+    <row r="110" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A110">
+        <v>1620</v>
+      </c>
+      <c r="B110">
+        <v>4.044390634434011</v>
+      </c>
+      <c r="C110">
+        <v>1.2885543236570807</v>
+      </c>
+      <c r="D110">
+        <v>3.0809422581490811</v>
+      </c>
+    </row>
+    <row r="111" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A111">
+        <v>1635</v>
+      </c>
+      <c r="B111">
+        <v>-0.81603281637400715</v>
+      </c>
+      <c r="C111">
+        <v>-1.2934924152829663</v>
+      </c>
+      <c r="D111">
+        <v>-2.9775758775475856</v>
+      </c>
+    </row>
+    <row r="112" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A112">
+        <v>1650</v>
+      </c>
+      <c r="B112">
+        <v>3.3760181711262325</v>
+      </c>
+      <c r="C112">
+        <v>-1.8384228859091956</v>
+      </c>
+      <c r="D112">
+        <v>2.2056100851896163</v>
+      </c>
+    </row>
+    <row r="113" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A113">
+        <v>1665</v>
+      </c>
+      <c r="B113">
+        <v>-1.096314194401159</v>
+      </c>
+      <c r="C113">
+        <v>0.23531444701986426</v>
+      </c>
+      <c r="D113">
+        <v>4.4293783830987934</v>
+      </c>
+    </row>
+    <row r="114" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A114">
+        <v>1680</v>
+      </c>
+      <c r="B114">
+        <v>-0.7500514059977248</v>
+      </c>
+      <c r="C114">
+        <v>-0.63461129713092257</v>
+      </c>
+      <c r="D114">
+        <v>3.5274759449709214</v>
+      </c>
+    </row>
+    <row r="115" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A115">
+        <v>1695</v>
+      </c>
+      <c r="B115">
+        <v>3.103497969738469</v>
+      </c>
+      <c r="C115">
+        <v>3.503719425120341</v>
+      </c>
+      <c r="D115">
+        <v>-1.7043559373445594</v>
+      </c>
+    </row>
+    <row r="116" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A116">
+        <v>1710</v>
+      </c>
+      <c r="B116">
+        <v>-4.0447049773633275</v>
+      </c>
+      <c r="C116">
+        <v>-4.0655960824014734</v>
+      </c>
+      <c r="D116">
+        <v>-2.9064141141066568</v>
+      </c>
+    </row>
+    <row r="117" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A117">
+        <v>1725</v>
+      </c>
+      <c r="B117">
+        <v>-0.77094337338949659</v>
+      </c>
+      <c r="C117">
+        <v>1.5842274749283314</v>
+      </c>
+      <c r="D117">
+        <v>3.4614174938740359</v>
+      </c>
+    </row>
+    <row r="118" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A118">
+        <v>1740</v>
+      </c>
+      <c r="B118">
+        <v>-0.53688258825629109</v>
+      </c>
+      <c r="C118">
+        <v>1.407755171826246</v>
+      </c>
+      <c r="D118">
+        <v>-1.7887499853489119</v>
+      </c>
+    </row>
+    <row r="119" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A119">
+        <v>1755</v>
+      </c>
+      <c r="B119">
+        <v>0.83042981782377678</v>
+      </c>
+      <c r="C119">
+        <v>-4.4488070403614248</v>
+      </c>
+      <c r="D119">
+        <v>-3.0245303812850577</v>
+      </c>
+    </row>
+    <row r="120" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A120">
+        <v>1770</v>
+      </c>
+      <c r="B120">
+        <v>-1.3799395867498798</v>
+      </c>
+      <c r="C120">
+        <v>3.3948313582956779</v>
+      </c>
+      <c r="D120">
+        <v>0.24071602899060074</v>
+      </c>
+    </row>
+    <row r="121" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A121">
+        <v>1785</v>
+      </c>
+      <c r="B121">
+        <v>-4.7394526273263402</v>
+      </c>
+      <c r="C121">
+        <v>-4.0336956062692844</v>
+      </c>
+      <c r="D121">
+        <v>-1.0485681083140996</v>
+      </c>
+    </row>
+    <row r="122" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A122">
+        <v>1800</v>
+      </c>
+      <c r="B122">
+        <v>-4.0445738251805956</v>
+      </c>
+      <c r="C122">
+        <v>1.2361190839278446</v>
+      </c>
+      <c r="D122">
+        <v>0.12568295209392955</v>
+      </c>
+    </row>
+    <row r="123" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A123">
+        <v>1815</v>
+      </c>
+      <c r="B123">
+        <v>-2.2291210437297404</v>
+      </c>
+      <c r="C123">
+        <v>1.6737233400797802</v>
+      </c>
+      <c r="D123">
+        <v>-4.8138871856405929</v>
+      </c>
+    </row>
+    <row r="124" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A124">
+        <v>1830</v>
+      </c>
+      <c r="B124">
+        <v>-2.853118676654228</v>
+      </c>
+      <c r="C124">
+        <v>-2.1472855089718124</v>
+      </c>
+      <c r="D124">
+        <v>3.3723983243154034</v>
+      </c>
+    </row>
+    <row r="125" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A125">
+        <v>1845</v>
+      </c>
+      <c r="B125">
+        <v>-0.24882100304299826</v>
+      </c>
+      <c r="C125">
+        <v>1.8033363964076921</v>
+      </c>
+      <c r="D125">
+        <v>-4.2884924541841842</v>
+      </c>
+    </row>
+    <row r="126" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A126">
+        <v>1860</v>
+      </c>
+      <c r="B126">
+        <v>-2.2445194295065543</v>
+      </c>
+      <c r="C126">
+        <v>-3.2500729664089256</v>
+      </c>
+      <c r="D126">
+        <v>4.2347790302627732</v>
+      </c>
+    </row>
+    <row r="127" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A127">
+        <v>1875</v>
+      </c>
+      <c r="B127">
+        <v>-2.450669341096102</v>
+      </c>
+      <c r="C127">
+        <v>-4.6896077737500841</v>
+      </c>
+      <c r="D127">
+        <v>-2.7741450737202946</v>
+      </c>
+    </row>
+    <row r="128" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A128">
+        <v>1890</v>
+      </c>
+      <c r="B128">
+        <v>-1.9867994555348123</v>
+      </c>
+      <c r="C128">
+        <v>-1.9981246073140779E-2</v>
+      </c>
+      <c r="D128">
+        <v>2.7230188137295164</v>
+      </c>
+    </row>
+    <row r="129" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A129">
+        <v>1905</v>
+      </c>
+      <c r="B129">
+        <v>-3.5727034087965404</v>
+      </c>
+      <c r="C129">
+        <v>-2.5623548310283226</v>
+      </c>
+      <c r="D129">
+        <v>-4.3497530897306653</v>
+      </c>
+    </row>
+    <row r="130" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A130">
+        <v>1920</v>
+      </c>
+      <c r="B130">
+        <v>0.5566715052606408</v>
+      </c>
+      <c r="C130">
+        <v>4.6873498063994958</v>
+      </c>
+      <c r="D130">
+        <v>-4.806178953054081</v>
+      </c>
+    </row>
+    <row r="131" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A131">
+        <v>1935</v>
+      </c>
+      <c r="B131">
+        <v>4.7614075948617245</v>
+      </c>
+      <c r="C131">
+        <v>4.0560638762975945</v>
+      </c>
+      <c r="D131">
+        <v>3.2450264301798537</v>
+      </c>
+    </row>
+    <row r="132" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A132">
+        <v>1950</v>
+      </c>
+      <c r="B132">
+        <v>4.20009574202055</v>
+      </c>
+      <c r="C132">
+        <v>-4.1979965081471535</v>
+      </c>
+      <c r="D132">
+        <v>4.6532756701806548</v>
       </c>
     </row>
   </sheetData>

--- a/reference/functions/spline_curve/waypoint.xlsx
+++ b/reference/functions/spline_curve/waypoint.xlsx
@@ -1,21 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28129"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nakat\Documents\GitHub\drone\reference\functions\spline_curve\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\acsl_students\Documents\GitHub_subfolder\drone\reference\functions\spline_curve\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4EEAF8F-CB71-41C7-B870-B247F16DFD96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{360EDF50-C1A7-49D4-B5B9-8A981B3C0726}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-2500" yWindow="-21710" windowWidth="38620" windowHeight="21100" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="origin" sheetId="4" r:id="rId2"/>
     <sheet name="5to15" sheetId="6" r:id="rId3"/>
+    <sheet name="forMEC" sheetId="7" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -35,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="8">
   <si>
     <t>x_wp</t>
     <phoneticPr fontId="1"/>
@@ -424,9 +425,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D26"/>
-  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>3</v>
       </c>
@@ -440,7 +441,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>0</v>
       </c>
@@ -454,7 +455,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>1.5</v>
       </c>
@@ -468,7 +469,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>3</v>
       </c>
@@ -482,7 +483,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>4.5</v>
       </c>
@@ -496,7 +497,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>6</v>
       </c>
@@ -510,7 +511,7 @@
         <v>1.3</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>7.5</v>
       </c>
@@ -524,7 +525,7 @@
         <v>1.4000000000000001</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>9</v>
       </c>
@@ -538,7 +539,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>10.5</v>
       </c>
@@ -552,7 +553,7 @@
         <v>1.3</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>12</v>
       </c>
@@ -566,7 +567,7 @@
         <v>1.2000000000000002</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>13.5</v>
       </c>
@@ -580,7 +581,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>15</v>
       </c>
@@ -594,7 +595,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>16.5</v>
       </c>
@@ -608,7 +609,7 @@
         <v>0.70000000000000007</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>18</v>
       </c>
@@ -622,7 +623,7 @@
         <v>0.60000000000000009</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>19.5</v>
       </c>
@@ -636,7 +637,7 @@
         <v>0.70000000000000007</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>21</v>
       </c>
@@ -650,7 +651,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>22.5</v>
       </c>
@@ -664,7 +665,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>24</v>
       </c>
@@ -678,7 +679,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>25.5</v>
       </c>
@@ -692,7 +693,7 @@
         <v>1.2000000000000002</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>27</v>
       </c>
@@ -706,7 +707,7 @@
         <v>1.3</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A21">
         <v>28.5</v>
       </c>
@@ -720,7 +721,7 @@
         <v>1.2000000000000002</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A22">
         <v>30</v>
       </c>
@@ -734,7 +735,7 @@
         <v>1.3</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A23">
         <v>31.5</v>
       </c>
@@ -748,7 +749,7 @@
         <v>1.2000000000000002</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A24">
         <v>33</v>
       </c>
@@ -762,7 +763,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A25">
         <v>34.5</v>
       </c>
@@ -776,7 +777,7 @@
         <v>1.05</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A26">
         <v>36</v>
       </c>
@@ -800,13 +801,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:D132"/>
-  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="5.90625" customWidth="1"/>
-    <col min="2" max="4" width="6.86328125" customWidth="1"/>
+    <col min="2" max="4" width="6.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>4</v>
       </c>
@@ -820,7 +821,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>0</v>
       </c>
@@ -834,7 +835,7 @@
         <v>2.5143889596457303E-3</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>5</v>
       </c>
@@ -848,7 +849,7 @@
         <v>-1.5923376176110715</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>10</v>
       </c>
@@ -862,7 +863,7 @@
         <v>1.6129946190549993</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>15</v>
       </c>
@@ -876,7 +877,7 @@
         <v>0.83740062219910261</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>20</v>
       </c>
@@ -890,7 +891,7 @@
         <v>0.31680918265487801</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>25</v>
       </c>
@@ -904,7 +905,7 @@
         <v>1.2764408752063083</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>30</v>
       </c>
@@ -918,7 +919,7 @@
         <v>1.5118664306624763</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>35</v>
       </c>
@@ -932,7 +933,7 @@
         <v>-4.7307536154024357</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>40</v>
       </c>
@@ -946,7 +947,7 @@
         <v>2.0098215069291472</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>45</v>
       </c>
@@ -960,7 +961,7 @@
         <v>2.2459930027101969</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>50</v>
       </c>
@@ -974,7 +975,7 @@
         <v>-0.71427041847938133</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>55</v>
       </c>
@@ -988,7 +989,7 @@
         <v>0.87411558151694102</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>60</v>
       </c>
@@ -1002,7 +1003,7 @@
         <v>0.50678709178415882</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>65</v>
       </c>
@@ -1016,7 +1017,7 @@
         <v>-0.30624051417129095</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>70</v>
       </c>
@@ -1030,7 +1031,7 @@
         <v>-3.9146105313087345</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>75</v>
       </c>
@@ -1044,7 +1045,7 @@
         <v>4.7602624075810045</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>80</v>
       </c>
@@ -1058,7 +1059,7 @@
         <v>-1.3399947978837368</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>85</v>
       </c>
@@ -1072,7 +1073,7 @@
         <v>-4.215366851019021</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>90</v>
       </c>
@@ -1086,7 +1087,7 @@
         <v>-4.4653950180761024</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A21">
         <v>95</v>
       </c>
@@ -1100,7 +1101,7 @@
         <v>2.3174510546711211</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A22">
         <v>100</v>
       </c>
@@ -1114,7 +1115,7 @@
         <v>-2.4469565685518155</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A23">
         <v>105</v>
       </c>
@@ -1128,7 +1129,7 @@
         <v>-2.5539097033394507</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A24">
         <v>110</v>
       </c>
@@ -1142,7 +1143,7 @@
         <v>-1.4459965599407432</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A25">
         <v>115</v>
       </c>
@@ -1156,7 +1157,7 @@
         <v>1.0008415884716482</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A26">
         <v>120</v>
       </c>
@@ -1170,7 +1171,7 @@
         <v>2.2443406250490772</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A27">
         <v>125</v>
       </c>
@@ -1184,7 +1185,7 @@
         <v>-4.0960986361258698</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A28">
         <v>130</v>
       </c>
@@ -1198,7 +1199,7 @@
         <v>4.6934286332964223</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A29">
         <v>135</v>
       </c>
@@ -1212,7 +1213,7 @@
         <v>-4.3769391712908945</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A30">
         <v>140</v>
       </c>
@@ -1226,7 +1227,7 @@
         <v>4.3936324237126261</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A31">
         <v>145</v>
       </c>
@@ -1240,7 +1241,7 @@
         <v>-0.17059200732076563</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A32">
         <v>150</v>
       </c>
@@ -1254,7 +1255,7 @@
         <v>3.3104073633841615</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A33">
         <v>155</v>
       </c>
@@ -1268,7 +1269,7 @@
         <v>-1.1286388991793495</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A34">
         <v>160</v>
       </c>
@@ -1282,7 +1283,7 @@
         <v>1.6923601147740586</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A35">
         <v>165</v>
       </c>
@@ -1296,7 +1297,7 @@
         <v>1.9493721341731607</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A36">
         <v>170</v>
       </c>
@@ -1310,7 +1311,7 @@
         <v>-3.5731428814234665</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A37">
         <v>175</v>
       </c>
@@ -1324,7 +1325,7 @@
         <v>-0.16824547684147206</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A38">
         <v>180</v>
       </c>
@@ -1338,7 +1339,7 @@
         <v>3.7545109810478063</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A39">
         <v>185</v>
       </c>
@@ -1352,7 +1353,7 @@
         <v>0.54078060347251378</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A40">
         <v>190</v>
       </c>
@@ -1366,7 +1367,7 @@
         <v>-3.5212793126992183</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A41">
         <v>195</v>
       </c>
@@ -1380,7 +1381,7 @@
         <v>-3.8327216751578455</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A42">
         <v>200</v>
       </c>
@@ -1394,7 +1395,7 @@
         <v>-1.4043363221400995</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A43">
         <v>205</v>
       </c>
@@ -1408,7 +1409,7 @@
         <v>-0.30766453615983513</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A44">
         <v>210</v>
       </c>
@@ -1422,7 +1423,7 @@
         <v>-2.2974788731457716</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A45">
         <v>215</v>
       </c>
@@ -1436,7 +1437,7 @@
         <v>-2.6040236745237264</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A46">
         <v>220</v>
       </c>
@@ -1450,7 +1451,7 @@
         <v>-1.6267749651982433</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A47">
         <v>225</v>
       </c>
@@ -1464,7 +1465,7 @@
         <v>-2.7558778901116519</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A48">
         <v>230</v>
       </c>
@@ -1478,7 +1479,7 @@
         <v>-3.3307752325489925</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A49">
         <v>235</v>
       </c>
@@ -1492,7 +1493,7 @@
         <v>-3.788865812315485</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A50">
         <v>240</v>
       </c>
@@ -1506,7 +1507,7 @@
         <v>1.9163100448142745</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A51">
         <v>245</v>
       </c>
@@ -1520,7 +1521,7 @@
         <v>-0.45171651463562945</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A52">
         <v>250</v>
       </c>
@@ -1534,7 +1535,7 @@
         <v>1.1204968011208316</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A53">
         <v>255</v>
       </c>
@@ -1548,7 +1549,7 @@
         <v>0.18901859959311484</v>
       </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A54">
         <v>260</v>
       </c>
@@ -1562,7 +1563,7 @@
         <v>-4.8986444451687134</v>
       </c>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A55">
         <v>265</v>
       </c>
@@ -1576,7 +1577,7 @@
         <v>-1.9404129043036511</v>
       </c>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A56">
         <v>270</v>
       </c>
@@ -1590,7 +1591,7 @@
         <v>0.94956400116934403</v>
       </c>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A57">
         <v>275</v>
       </c>
@@ -1604,7 +1605,7 @@
         <v>-2.4333099525699255</v>
       </c>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A58">
         <v>280</v>
       </c>
@@ -1618,7 +1619,7 @@
         <v>2.3275889108562451</v>
       </c>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="59" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A59">
         <v>285</v>
       </c>
@@ -1632,7 +1633,7 @@
         <v>-1.247873095563059</v>
       </c>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="60" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A60">
         <v>290</v>
       </c>
@@ -1646,7 +1647,7 @@
         <v>3.5941810445347855</v>
       </c>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="61" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A61">
         <v>295</v>
       </c>
@@ -1660,7 +1661,7 @@
         <v>-3.8291408115260084</v>
       </c>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="62" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A62">
         <v>300</v>
       </c>
@@ -1674,7 +1675,7 @@
         <v>-0.7527211830211511</v>
       </c>
     </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="63" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A63">
         <v>310</v>
       </c>
@@ -1688,7 +1689,7 @@
         <v>-4.3029135987555609</v>
       </c>
     </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="64" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A64">
         <v>320</v>
       </c>
@@ -1702,7 +1703,7 @@
         <v>-1.7068382992475528</v>
       </c>
     </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="65" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A65">
         <v>330</v>
       </c>
@@ -1716,7 +1717,7 @@
         <v>3.3938672732647945</v>
       </c>
     </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="66" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A66">
         <v>340</v>
       </c>
@@ -1730,7 +1731,7 @@
         <v>-0.68286055830592107</v>
       </c>
     </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="67" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A67">
         <v>350</v>
       </c>
@@ -1744,7 +1745,7 @@
         <v>-6.5438526761227855E-2</v>
       </c>
     </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="68" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A68">
         <v>360</v>
       </c>
@@ -1758,7 +1759,7 @@
         <v>-1.7199525526209858</v>
       </c>
     </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="69" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A69">
         <v>370</v>
       </c>
@@ -1772,7 +1773,7 @@
         <v>0.56093253872197213</v>
       </c>
     </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="70" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A70">
         <v>380</v>
       </c>
@@ -1786,7 +1787,7 @@
         <v>-4.6334289050480502</v>
       </c>
     </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="71" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A71">
         <v>390</v>
       </c>
@@ -1800,7 +1801,7 @@
         <v>-1.3612034211029878</v>
       </c>
     </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="72" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A72">
         <v>400</v>
       </c>
@@ -1814,7 +1815,7 @@
         <v>4.6054352008508728</v>
       </c>
     </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="73" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A73">
         <v>410</v>
       </c>
@@ -1828,7 +1829,7 @@
         <v>3.9964315753945767</v>
       </c>
     </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="74" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A74">
         <v>420</v>
       </c>
@@ -1842,7 +1843,7 @@
         <v>4.4863012889615996</v>
       </c>
     </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="75" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A75">
         <v>430</v>
       </c>
@@ -1856,7 +1857,7 @@
         <v>0.41246301658184548</v>
       </c>
     </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="76" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A76">
         <v>440</v>
       </c>
@@ -1870,7 +1871,7 @@
         <v>3.3701019276245638</v>
       </c>
     </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="77" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A77">
         <v>450</v>
       </c>
@@ -1884,7 +1885,7 @@
         <v>3.5927992962940012</v>
       </c>
     </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="78" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A78">
         <v>460</v>
       </c>
@@ -1898,7 +1899,7 @@
         <v>-1.7419939426058739</v>
       </c>
     </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="79" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A79">
         <v>470</v>
       </c>
@@ -1912,7 +1913,7 @@
         <v>3.394090790320432</v>
       </c>
     </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="80" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A80">
         <v>480</v>
       </c>
@@ -1926,7 +1927,7 @@
         <v>-0.19505225160462603</v>
       </c>
     </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="81" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A81">
         <v>490</v>
       </c>
@@ -1940,7 +1941,7 @@
         <v>2.3867688422087441</v>
       </c>
     </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="82" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A82">
         <v>500</v>
       </c>
@@ -1954,7 +1955,7 @@
         <v>-2.8741223271239527</v>
       </c>
     </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="83" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A83">
         <v>510</v>
       </c>
@@ -1968,7 +1969,7 @@
         <v>0.91745675309284236</v>
       </c>
     </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="84" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A84">
         <v>520</v>
       </c>
@@ -1982,7 +1983,7 @@
         <v>3.9527780819638081</v>
       </c>
     </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="85" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A85">
         <v>530</v>
       </c>
@@ -1996,7 +1997,7 @@
         <v>0.48329068692591459</v>
       </c>
     </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="86" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A86">
         <v>540</v>
       </c>
@@ -2010,7 +2011,7 @@
         <v>-2.3925259518518893</v>
       </c>
     </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="87" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A87">
         <v>550</v>
       </c>
@@ -2024,7 +2025,7 @@
         <v>1.8123264178816179</v>
       </c>
     </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="88" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A88">
         <v>560</v>
       </c>
@@ -2038,7 +2039,7 @@
         <v>2.1571167913917586</v>
       </c>
     </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="89" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A89">
         <v>570</v>
       </c>
@@ -2052,7 +2053,7 @@
         <v>-0.11800833430770208</v>
       </c>
     </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="90" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A90">
         <v>580</v>
       </c>
@@ -2066,7 +2067,7 @@
         <v>-4.0635166761945127</v>
       </c>
     </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="91" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A91">
         <v>595</v>
       </c>
@@ -2080,7 +2081,7 @@
         <v>-1.5272825471461937</v>
       </c>
     </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="92" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A92">
         <v>610</v>
       </c>
@@ -2094,7 +2095,7 @@
         <v>1.0927134953255813E-2</v>
       </c>
     </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="93" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A93">
         <v>625</v>
       </c>
@@ -2108,7 +2109,7 @@
         <v>1.5402994571295059</v>
       </c>
     </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="94" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A94">
         <v>640</v>
       </c>
@@ -2122,7 +2123,7 @@
         <v>4.2483983236790213</v>
       </c>
     </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="95" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A95">
         <v>655</v>
       </c>
@@ -2136,7 +2137,7 @@
         <v>4.2867624084882285</v>
       </c>
     </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="96" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A96">
         <v>670</v>
       </c>
@@ -2150,7 +2151,7 @@
         <v>-1.3446264576145028</v>
       </c>
     </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="97" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A97">
         <v>685</v>
       </c>
@@ -2164,7 +2165,7 @@
         <v>-0.4194043693088545</v>
       </c>
     </row>
-    <row r="98" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="98" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A98">
         <v>700</v>
       </c>
@@ -2178,7 +2179,7 @@
         <v>4.0888939258471666</v>
       </c>
     </row>
-    <row r="99" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="99" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A99">
         <v>715</v>
       </c>
@@ -2192,7 +2193,7 @@
         <v>2.5930996787243545</v>
       </c>
     </row>
-    <row r="100" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="100" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A100">
         <v>730</v>
       </c>
@@ -2206,7 +2207,7 @@
         <v>-2.8048482978831202</v>
       </c>
     </row>
-    <row r="101" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="101" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A101">
         <v>745</v>
       </c>
@@ -2220,7 +2221,7 @@
         <v>-1.7776562109683391</v>
       </c>
     </row>
-    <row r="102" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="102" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A102">
         <v>760</v>
       </c>
@@ -2234,7 +2235,7 @@
         <v>3.3955029994805139</v>
       </c>
     </row>
-    <row r="103" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="103" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A103">
         <v>775</v>
       </c>
@@ -2248,7 +2249,7 @@
         <v>-4.8258234804074762</v>
       </c>
     </row>
-    <row r="104" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="104" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A104">
         <v>790</v>
       </c>
@@ -2262,7 +2263,7 @@
         <v>4.2173923432814897</v>
       </c>
     </row>
-    <row r="105" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="105" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A105">
         <v>805</v>
       </c>
@@ -2276,7 +2277,7 @@
         <v>1.6221113895410877</v>
       </c>
     </row>
-    <row r="106" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="106" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A106">
         <v>820</v>
       </c>
@@ -2290,7 +2291,7 @@
         <v>-1.8969917044986195</v>
       </c>
     </row>
-    <row r="107" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="107" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A107">
         <v>835</v>
       </c>
@@ -2304,7 +2305,7 @@
         <v>-1.0217480698132586</v>
       </c>
     </row>
-    <row r="108" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="108" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A108">
         <v>850</v>
       </c>
@@ -2318,7 +2319,7 @@
         <v>1.4569720227085992</v>
       </c>
     </row>
-    <row r="109" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="109" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A109">
         <v>865</v>
       </c>
@@ -2332,7 +2333,7 @@
         <v>-1.5967531597427365</v>
       </c>
     </row>
-    <row r="110" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="110" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A110">
         <v>880</v>
       </c>
@@ -2346,7 +2347,7 @@
         <v>3.0809422581490811</v>
       </c>
     </row>
-    <row r="111" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="111" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A111">
         <v>895</v>
       </c>
@@ -2360,7 +2361,7 @@
         <v>-2.9775758775475856</v>
       </c>
     </row>
-    <row r="112" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="112" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A112">
         <v>910</v>
       </c>
@@ -2374,7 +2375,7 @@
         <v>2.2056100851896163</v>
       </c>
     </row>
-    <row r="113" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="113" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A113">
         <v>925</v>
       </c>
@@ -2388,7 +2389,7 @@
         <v>4.4293783830987934</v>
       </c>
     </row>
-    <row r="114" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="114" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A114">
         <v>940</v>
       </c>
@@ -2402,7 +2403,7 @@
         <v>3.5274759449709214</v>
       </c>
     </row>
-    <row r="115" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="115" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A115">
         <v>955</v>
       </c>
@@ -2416,7 +2417,7 @@
         <v>-1.7043559373445594</v>
       </c>
     </row>
-    <row r="116" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="116" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A116">
         <v>970</v>
       </c>
@@ -2430,7 +2431,7 @@
         <v>-2.9064141141066568</v>
       </c>
     </row>
-    <row r="117" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="117" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A117">
         <v>985</v>
       </c>
@@ -2444,7 +2445,7 @@
         <v>3.4614174938740359</v>
       </c>
     </row>
-    <row r="118" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="118" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A118">
         <v>1000</v>
       </c>
@@ -2458,7 +2459,7 @@
         <v>-1.7887499853489119</v>
       </c>
     </row>
-    <row r="119" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="119" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A119">
         <v>1015</v>
       </c>
@@ -2472,7 +2473,7 @@
         <v>-3.0245303812850577</v>
       </c>
     </row>
-    <row r="120" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="120" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A120">
         <v>1030</v>
       </c>
@@ -2486,7 +2487,7 @@
         <v>0.24071602899060074</v>
       </c>
     </row>
-    <row r="121" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="121" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A121">
         <v>1045</v>
       </c>
@@ -2500,7 +2501,7 @@
         <v>-1.0485681083140996</v>
       </c>
     </row>
-    <row r="122" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="122" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A122">
         <v>1060</v>
       </c>
@@ -2514,7 +2515,7 @@
         <v>0.12568295209392955</v>
       </c>
     </row>
-    <row r="123" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="123" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A123">
         <v>1075</v>
       </c>
@@ -2528,7 +2529,7 @@
         <v>-4.8138871856405929</v>
       </c>
     </row>
-    <row r="124" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="124" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A124">
         <v>1090</v>
       </c>
@@ -2542,7 +2543,7 @@
         <v>3.3723983243154034</v>
       </c>
     </row>
-    <row r="125" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="125" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A125">
         <v>1105</v>
       </c>
@@ -2556,7 +2557,7 @@
         <v>-4.2884924541841842</v>
       </c>
     </row>
-    <row r="126" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="126" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A126">
         <v>1120</v>
       </c>
@@ -2570,7 +2571,7 @@
         <v>4.2347790302627732</v>
       </c>
     </row>
-    <row r="127" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="127" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A127">
         <v>1135</v>
       </c>
@@ -2584,7 +2585,7 @@
         <v>-2.7741450737202946</v>
       </c>
     </row>
-    <row r="128" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="128" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A128">
         <v>1150</v>
       </c>
@@ -2598,7 +2599,7 @@
         <v>2.7230188137295164</v>
       </c>
     </row>
-    <row r="129" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="129" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A129">
         <v>1165</v>
       </c>
@@ -2612,7 +2613,7 @@
         <v>-4.3497530897306653</v>
       </c>
     </row>
-    <row r="130" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="130" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A130">
         <v>1180</v>
       </c>
@@ -2626,7 +2627,7 @@
         <v>-4.806178953054081</v>
       </c>
     </row>
-    <row r="131" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="131" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A131">
         <v>1195</v>
       </c>
@@ -2640,7 +2641,7 @@
         <v>3.2450264301798537</v>
       </c>
     </row>
-    <row r="132" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="132" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A132">
         <v>1210</v>
       </c>
@@ -2663,13 +2664,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{56A987FB-6A42-4432-9068-D3F18FDE7F8F}">
   <dimension ref="A1:D132"/>
-  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="5.90625" customWidth="1"/>
-    <col min="2" max="4" width="6.86328125" customWidth="1"/>
+    <col min="2" max="4" width="6.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>4</v>
       </c>
@@ -2683,7 +2684,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>0</v>
       </c>
@@ -2697,7 +2698,7 @@
         <v>2.5143889596457303E-3</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>15</v>
       </c>
@@ -2711,7 +2712,7 @@
         <v>-1.5923376176110715</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>30</v>
       </c>
@@ -2725,7 +2726,7 @@
         <v>1.6129946190549993</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>45</v>
       </c>
@@ -2739,7 +2740,7 @@
         <v>0.83740062219910261</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>60</v>
       </c>
@@ -2753,7 +2754,7 @@
         <v>0.31680918265487801</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>75</v>
       </c>
@@ -2767,7 +2768,7 @@
         <v>1.2764408752063083</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>90</v>
       </c>
@@ -2781,7 +2782,7 @@
         <v>1.5118664306624763</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>105</v>
       </c>
@@ -2795,7 +2796,7 @@
         <v>-4.7307536154024357</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>120</v>
       </c>
@@ -2809,7 +2810,7 @@
         <v>2.0098215069291472</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>135</v>
       </c>
@@ -2823,7 +2824,7 @@
         <v>2.2459930027101969</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>150</v>
       </c>
@@ -2837,7 +2838,7 @@
         <v>-0.71427041847938133</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>165</v>
       </c>
@@ -2851,7 +2852,7 @@
         <v>0.87411558151694102</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>180</v>
       </c>
@@ -2865,7 +2866,7 @@
         <v>0.50678709178415882</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>195</v>
       </c>
@@ -2879,7 +2880,7 @@
         <v>-0.30624051417129095</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>210</v>
       </c>
@@ -2893,7 +2894,7 @@
         <v>-3.9146105313087345</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>225</v>
       </c>
@@ -2907,7 +2908,7 @@
         <v>4.7602624075810045</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>240</v>
       </c>
@@ -2921,7 +2922,7 @@
         <v>-1.3399947978837368</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>255</v>
       </c>
@@ -2935,7 +2936,7 @@
         <v>-4.215366851019021</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>270</v>
       </c>
@@ -2949,7 +2950,7 @@
         <v>-4.4653950180761024</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A21">
         <v>285</v>
       </c>
@@ -2963,7 +2964,7 @@
         <v>2.3174510546711211</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A22">
         <v>300</v>
       </c>
@@ -2977,7 +2978,7 @@
         <v>-2.4469565685518155</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A23">
         <v>315</v>
       </c>
@@ -2991,7 +2992,7 @@
         <v>-2.5539097033394507</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A24">
         <v>330</v>
       </c>
@@ -3005,7 +3006,7 @@
         <v>-1.4459965599407432</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A25">
         <v>345</v>
       </c>
@@ -3019,7 +3020,7 @@
         <v>1.0008415884716482</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A26">
         <v>360</v>
       </c>
@@ -3033,7 +3034,7 @@
         <v>2.2443406250490772</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A27">
         <v>375</v>
       </c>
@@ -3047,7 +3048,7 @@
         <v>-4.0960986361258698</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A28">
         <v>390</v>
       </c>
@@ -3061,7 +3062,7 @@
         <v>4.6934286332964223</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A29">
         <v>405</v>
       </c>
@@ -3075,7 +3076,7 @@
         <v>-4.3769391712908945</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A30">
         <v>420</v>
       </c>
@@ -3089,7 +3090,7 @@
         <v>4.3936324237126261</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A31">
         <v>435</v>
       </c>
@@ -3103,7 +3104,7 @@
         <v>-0.17059200732076563</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A32">
         <v>450</v>
       </c>
@@ -3117,7 +3118,7 @@
         <v>3.3104073633841615</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A33">
         <v>465</v>
       </c>
@@ -3131,7 +3132,7 @@
         <v>-1.1286388991793495</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A34">
         <v>480</v>
       </c>
@@ -3145,7 +3146,7 @@
         <v>1.6923601147740586</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A35">
         <v>495</v>
       </c>
@@ -3159,7 +3160,7 @@
         <v>1.9493721341731607</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A36">
         <v>510</v>
       </c>
@@ -3173,7 +3174,7 @@
         <v>-3.5731428814234665</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A37">
         <v>525</v>
       </c>
@@ -3187,7 +3188,7 @@
         <v>-0.16824547684147206</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A38">
         <v>540</v>
       </c>
@@ -3201,7 +3202,7 @@
         <v>3.7545109810478063</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A39">
         <v>555</v>
       </c>
@@ -3215,7 +3216,7 @@
         <v>0.54078060347251378</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A40">
         <v>570</v>
       </c>
@@ -3229,7 +3230,7 @@
         <v>-3.5212793126992183</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A41">
         <v>585</v>
       </c>
@@ -3243,7 +3244,7 @@
         <v>-3.8327216751578455</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A42">
         <v>600</v>
       </c>
@@ -3257,7 +3258,7 @@
         <v>-1.4043363221400995</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A43">
         <v>615</v>
       </c>
@@ -3271,7 +3272,7 @@
         <v>-0.30766453615983513</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A44">
         <v>630</v>
       </c>
@@ -3285,7 +3286,7 @@
         <v>-2.2974788731457716</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A45">
         <v>645</v>
       </c>
@@ -3299,7 +3300,7 @@
         <v>-2.6040236745237264</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A46">
         <v>660</v>
       </c>
@@ -3313,7 +3314,7 @@
         <v>-1.6267749651982433</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A47">
         <v>675</v>
       </c>
@@ -3327,7 +3328,7 @@
         <v>-2.7558778901116519</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A48">
         <v>690</v>
       </c>
@@ -3341,7 +3342,7 @@
         <v>-3.3307752325489925</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A49">
         <v>705</v>
       </c>
@@ -3355,7 +3356,7 @@
         <v>-3.788865812315485</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A50">
         <v>720</v>
       </c>
@@ -3369,7 +3370,7 @@
         <v>1.9163100448142745</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A51">
         <v>735</v>
       </c>
@@ -3383,7 +3384,7 @@
         <v>-0.45171651463562945</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A52">
         <v>750</v>
       </c>
@@ -3397,7 +3398,7 @@
         <v>1.1204968011208316</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A53">
         <v>765</v>
       </c>
@@ -3411,7 +3412,7 @@
         <v>0.18901859959311484</v>
       </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A54">
         <v>780</v>
       </c>
@@ -3425,7 +3426,7 @@
         <v>-4.8986444451687134</v>
       </c>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A55">
         <v>795</v>
       </c>
@@ -3439,7 +3440,7 @@
         <v>-1.9404129043036511</v>
       </c>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A56">
         <v>810</v>
       </c>
@@ -3453,7 +3454,7 @@
         <v>0.94956400116934403</v>
       </c>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A57">
         <v>825</v>
       </c>
@@ -3467,7 +3468,7 @@
         <v>-2.4333099525699255</v>
       </c>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A58">
         <v>840</v>
       </c>
@@ -3481,7 +3482,7 @@
         <v>2.3275889108562451</v>
       </c>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="59" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A59">
         <v>855</v>
       </c>
@@ -3495,7 +3496,7 @@
         <v>-1.247873095563059</v>
       </c>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="60" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A60">
         <v>870</v>
       </c>
@@ -3509,7 +3510,7 @@
         <v>3.5941810445347855</v>
       </c>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="61" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A61">
         <v>885</v>
       </c>
@@ -3523,7 +3524,7 @@
         <v>-3.8291408115260084</v>
       </c>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="62" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A62">
         <v>900</v>
       </c>
@@ -3537,7 +3538,7 @@
         <v>-0.7527211830211511</v>
       </c>
     </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="63" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A63">
         <v>915</v>
       </c>
@@ -3551,7 +3552,7 @@
         <v>-4.3029135987555609</v>
       </c>
     </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="64" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A64">
         <v>930</v>
       </c>
@@ -3565,7 +3566,7 @@
         <v>-1.7068382992475528</v>
       </c>
     </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="65" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A65">
         <v>945</v>
       </c>
@@ -3579,7 +3580,7 @@
         <v>3.3938672732647945</v>
       </c>
     </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="66" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A66">
         <v>960</v>
       </c>
@@ -3593,7 +3594,7 @@
         <v>-0.68286055830592107</v>
       </c>
     </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="67" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A67">
         <v>975</v>
       </c>
@@ -3607,7 +3608,7 @@
         <v>-6.5438526761227855E-2</v>
       </c>
     </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="68" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A68">
         <v>990</v>
       </c>
@@ -3621,7 +3622,7 @@
         <v>-1.7199525526209858</v>
       </c>
     </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="69" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A69">
         <v>1005</v>
       </c>
@@ -3635,7 +3636,7 @@
         <v>0.56093253872197213</v>
       </c>
     </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="70" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A70">
         <v>1020</v>
       </c>
@@ -3649,7 +3650,7 @@
         <v>-4.6334289050480502</v>
       </c>
     </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="71" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A71">
         <v>1035</v>
       </c>
@@ -3663,7 +3664,7 @@
         <v>-1.3612034211029878</v>
       </c>
     </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="72" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A72">
         <v>1050</v>
       </c>
@@ -3677,7 +3678,7 @@
         <v>4.6054352008508728</v>
       </c>
     </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="73" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A73">
         <v>1065</v>
       </c>
@@ -3691,7 +3692,7 @@
         <v>3.9964315753945767</v>
       </c>
     </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="74" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A74">
         <v>1080</v>
       </c>
@@ -3705,7 +3706,7 @@
         <v>4.4863012889615996</v>
       </c>
     </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="75" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A75">
         <v>1095</v>
       </c>
@@ -3719,7 +3720,7 @@
         <v>0.41246301658184548</v>
       </c>
     </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="76" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A76">
         <v>1110</v>
       </c>
@@ -3733,7 +3734,7 @@
         <v>3.3701019276245638</v>
       </c>
     </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="77" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A77">
         <v>1125</v>
       </c>
@@ -3747,7 +3748,7 @@
         <v>3.5927992962940012</v>
       </c>
     </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="78" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A78">
         <v>1140</v>
       </c>
@@ -3761,7 +3762,7 @@
         <v>-1.7419939426058739</v>
       </c>
     </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="79" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A79">
         <v>1155</v>
       </c>
@@ -3775,7 +3776,7 @@
         <v>3.394090790320432</v>
       </c>
     </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="80" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A80">
         <v>1170</v>
       </c>
@@ -3789,7 +3790,7 @@
         <v>-0.19505225160462603</v>
       </c>
     </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="81" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A81">
         <v>1185</v>
       </c>
@@ -3803,7 +3804,7 @@
         <v>2.3867688422087441</v>
       </c>
     </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="82" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A82">
         <v>1200</v>
       </c>
@@ -3817,7 +3818,7 @@
         <v>-2.8741223271239527</v>
       </c>
     </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="83" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A83">
         <v>1215</v>
       </c>
@@ -3831,7 +3832,7 @@
         <v>0.91745675309284236</v>
       </c>
     </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="84" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A84">
         <v>1230</v>
       </c>
@@ -3845,7 +3846,7 @@
         <v>3.9527780819638081</v>
       </c>
     </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="85" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A85">
         <v>1245</v>
       </c>
@@ -3859,7 +3860,7 @@
         <v>0.48329068692591459</v>
       </c>
     </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="86" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A86">
         <v>1260</v>
       </c>
@@ -3873,7 +3874,7 @@
         <v>-2.3925259518518893</v>
       </c>
     </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="87" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A87">
         <v>1275</v>
       </c>
@@ -3887,7 +3888,7 @@
         <v>1.8123264178816179</v>
       </c>
     </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="88" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A88">
         <v>1290</v>
       </c>
@@ -3901,7 +3902,7 @@
         <v>2.1571167913917586</v>
       </c>
     </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="89" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A89">
         <v>1305</v>
       </c>
@@ -3915,7 +3916,7 @@
         <v>-0.11800833430770208</v>
       </c>
     </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="90" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A90">
         <v>1320</v>
       </c>
@@ -3929,7 +3930,7 @@
         <v>-4.0635166761945127</v>
       </c>
     </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="91" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A91">
         <v>1335</v>
       </c>
@@ -3943,7 +3944,7 @@
         <v>-1.5272825471461937</v>
       </c>
     </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="92" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A92">
         <v>1350</v>
       </c>
@@ -3957,7 +3958,7 @@
         <v>1.0927134953255813E-2</v>
       </c>
     </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="93" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A93">
         <v>1365</v>
       </c>
@@ -3971,7 +3972,7 @@
         <v>1.5402994571295059</v>
       </c>
     </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="94" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A94">
         <v>1380</v>
       </c>
@@ -3985,7 +3986,7 @@
         <v>4.2483983236790213</v>
       </c>
     </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="95" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A95">
         <v>1395</v>
       </c>
@@ -3999,7 +4000,7 @@
         <v>4.2867624084882285</v>
       </c>
     </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="96" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A96">
         <v>1410</v>
       </c>
@@ -4013,7 +4014,7 @@
         <v>-1.3446264576145028</v>
       </c>
     </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="97" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A97">
         <v>1425</v>
       </c>
@@ -4027,7 +4028,7 @@
         <v>-0.4194043693088545</v>
       </c>
     </row>
-    <row r="98" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="98" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A98">
         <v>1440</v>
       </c>
@@ -4041,7 +4042,7 @@
         <v>4.0888939258471666</v>
       </c>
     </row>
-    <row r="99" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="99" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A99">
         <v>1455</v>
       </c>
@@ -4055,7 +4056,7 @@
         <v>2.5930996787243545</v>
       </c>
     </row>
-    <row r="100" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="100" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A100">
         <v>1470</v>
       </c>
@@ -4069,7 +4070,7 @@
         <v>-2.8048482978831202</v>
       </c>
     </row>
-    <row r="101" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="101" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A101">
         <v>1485</v>
       </c>
@@ -4083,7 +4084,7 @@
         <v>-1.7776562109683391</v>
       </c>
     </row>
-    <row r="102" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="102" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A102">
         <v>1500</v>
       </c>
@@ -4097,7 +4098,7 @@
         <v>3.3955029994805139</v>
       </c>
     </row>
-    <row r="103" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="103" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A103">
         <v>1515</v>
       </c>
@@ -4111,7 +4112,7 @@
         <v>-4.8258234804074762</v>
       </c>
     </row>
-    <row r="104" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="104" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A104">
         <v>1530</v>
       </c>
@@ -4125,7 +4126,7 @@
         <v>4.2173923432814897</v>
       </c>
     </row>
-    <row r="105" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="105" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A105">
         <v>1545</v>
       </c>
@@ -4139,7 +4140,7 @@
         <v>1.6221113895410877</v>
       </c>
     </row>
-    <row r="106" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="106" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A106">
         <v>1560</v>
       </c>
@@ -4153,7 +4154,7 @@
         <v>-1.8969917044986195</v>
       </c>
     </row>
-    <row r="107" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="107" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A107">
         <v>1575</v>
       </c>
@@ -4167,7 +4168,7 @@
         <v>-1.0217480698132586</v>
       </c>
     </row>
-    <row r="108" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="108" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A108">
         <v>1590</v>
       </c>
@@ -4181,7 +4182,7 @@
         <v>1.4569720227085992</v>
       </c>
     </row>
-    <row r="109" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="109" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A109">
         <v>1605</v>
       </c>
@@ -4195,7 +4196,7 @@
         <v>-1.5967531597427365</v>
       </c>
     </row>
-    <row r="110" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="110" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A110">
         <v>1620</v>
       </c>
@@ -4209,7 +4210,7 @@
         <v>3.0809422581490811</v>
       </c>
     </row>
-    <row r="111" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="111" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A111">
         <v>1635</v>
       </c>
@@ -4223,7 +4224,7 @@
         <v>-2.9775758775475856</v>
       </c>
     </row>
-    <row r="112" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="112" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A112">
         <v>1650</v>
       </c>
@@ -4237,7 +4238,7 @@
         <v>2.2056100851896163</v>
       </c>
     </row>
-    <row r="113" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="113" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A113">
         <v>1665</v>
       </c>
@@ -4251,7 +4252,7 @@
         <v>4.4293783830987934</v>
       </c>
     </row>
-    <row r="114" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="114" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A114">
         <v>1680</v>
       </c>
@@ -4265,7 +4266,7 @@
         <v>3.5274759449709214</v>
       </c>
     </row>
-    <row r="115" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="115" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A115">
         <v>1695</v>
       </c>
@@ -4279,7 +4280,7 @@
         <v>-1.7043559373445594</v>
       </c>
     </row>
-    <row r="116" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="116" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A116">
         <v>1710</v>
       </c>
@@ -4293,7 +4294,7 @@
         <v>-2.9064141141066568</v>
       </c>
     </row>
-    <row r="117" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="117" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A117">
         <v>1725</v>
       </c>
@@ -4307,7 +4308,7 @@
         <v>3.4614174938740359</v>
       </c>
     </row>
-    <row r="118" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="118" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A118">
         <v>1740</v>
       </c>
@@ -4321,7 +4322,7 @@
         <v>-1.7887499853489119</v>
       </c>
     </row>
-    <row r="119" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="119" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A119">
         <v>1755</v>
       </c>
@@ -4335,7 +4336,7 @@
         <v>-3.0245303812850577</v>
       </c>
     </row>
-    <row r="120" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="120" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A120">
         <v>1770</v>
       </c>
@@ -4349,7 +4350,7 @@
         <v>0.24071602899060074</v>
       </c>
     </row>
-    <row r="121" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="121" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A121">
         <v>1785</v>
       </c>
@@ -4363,7 +4364,7 @@
         <v>-1.0485681083140996</v>
       </c>
     </row>
-    <row r="122" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="122" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A122">
         <v>1800</v>
       </c>
@@ -4377,7 +4378,7 @@
         <v>0.12568295209392955</v>
       </c>
     </row>
-    <row r="123" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="123" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A123">
         <v>1815</v>
       </c>
@@ -4391,7 +4392,7 @@
         <v>-4.8138871856405929</v>
       </c>
     </row>
-    <row r="124" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="124" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A124">
         <v>1830</v>
       </c>
@@ -4405,7 +4406,7 @@
         <v>3.3723983243154034</v>
       </c>
     </row>
-    <row r="125" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="125" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A125">
         <v>1845</v>
       </c>
@@ -4419,7 +4420,7 @@
         <v>-4.2884924541841842</v>
       </c>
     </row>
-    <row r="126" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="126" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A126">
         <v>1860</v>
       </c>
@@ -4433,7 +4434,7 @@
         <v>4.2347790302627732</v>
       </c>
     </row>
-    <row r="127" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="127" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A127">
         <v>1875</v>
       </c>
@@ -4447,7 +4448,7 @@
         <v>-2.7741450737202946</v>
       </c>
     </row>
-    <row r="128" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="128" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A128">
         <v>1890</v>
       </c>
@@ -4461,7 +4462,7 @@
         <v>2.7230188137295164</v>
       </c>
     </row>
-    <row r="129" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="129" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A129">
         <v>1905</v>
       </c>
@@ -4475,7 +4476,7 @@
         <v>-4.3497530897306653</v>
       </c>
     </row>
-    <row r="130" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="130" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A130">
         <v>1920</v>
       </c>
@@ -4489,7 +4490,7 @@
         <v>-4.806178953054081</v>
       </c>
     </row>
-    <row r="131" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="131" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A131">
         <v>1935</v>
       </c>
@@ -4503,7 +4504,7 @@
         <v>3.2450264301798537</v>
       </c>
     </row>
-    <row r="132" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="132" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A132">
         <v>1950</v>
       </c>
@@ -4521,4 +4522,387 @@
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{97B39A8F-3377-4121-B7E5-7B859139780C}">
+  <dimension ref="A1:D22"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2" s="1">
+        <f ca="1">3*RAND()-1.5</f>
+        <v>-0.20656972819168029</v>
+      </c>
+      <c r="C2" s="1">
+        <f ca="1">3*RAND()-1.5</f>
+        <v>-1.3406136721002575</v>
+      </c>
+      <c r="D2" s="1">
+        <f ca="1">1*RAND()+0.5</f>
+        <v>1.3236859624598352</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A3">
+        <v>5</v>
+      </c>
+      <c r="B3" s="1">
+        <f t="shared" ref="B3:C22" ca="1" si="0">3*RAND()-1.5</f>
+        <v>0.69046559120738937</v>
+      </c>
+      <c r="C3" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>-0.37813340773252868</v>
+      </c>
+      <c r="D3" s="1">
+        <f t="shared" ref="D3:D22" ca="1" si="1">1*RAND()+0.5</f>
+        <v>0.93113882592089958</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A4">
+        <v>10</v>
+      </c>
+      <c r="B4" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>-9.9281512507298997E-2</v>
+      </c>
+      <c r="C4" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>0.49890140332731003</v>
+      </c>
+      <c r="D4" s="1">
+        <f t="shared" ca="1" si="1"/>
+        <v>1.0595296453461147</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A5">
+        <v>15</v>
+      </c>
+      <c r="B5" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>0.70072717940230245</v>
+      </c>
+      <c r="C5" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>-0.10958936881962056</v>
+      </c>
+      <c r="D5" s="1">
+        <f t="shared" ca="1" si="1"/>
+        <v>1.4931645300892842</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A6">
+        <v>20</v>
+      </c>
+      <c r="B6" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>-1.341385866675983</v>
+      </c>
+      <c r="C6" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>-0.14774989826127483</v>
+      </c>
+      <c r="D6" s="1">
+        <f t="shared" ca="1" si="1"/>
+        <v>1.1853255523027879</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A7">
+        <v>25</v>
+      </c>
+      <c r="B7" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>-2.5341526267728121E-3</v>
+      </c>
+      <c r="C7" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>-1.148482722290229</v>
+      </c>
+      <c r="D7" s="1">
+        <f t="shared" ca="1" si="1"/>
+        <v>0.83442493911182292</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A8">
+        <v>30</v>
+      </c>
+      <c r="B8" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>-0.46937016035644286</v>
+      </c>
+      <c r="C8" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>0.2104030065164666</v>
+      </c>
+      <c r="D8" s="1">
+        <f t="shared" ca="1" si="1"/>
+        <v>1.4710128090833836</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A9">
+        <v>35</v>
+      </c>
+      <c r="B9" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>-0.43597953674111589</v>
+      </c>
+      <c r="C9" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>0.14806541251177618</v>
+      </c>
+      <c r="D9" s="1">
+        <f t="shared" ca="1" si="1"/>
+        <v>1.4848310816606305</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A10">
+        <v>40</v>
+      </c>
+      <c r="B10" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>0.42464854552823583</v>
+      </c>
+      <c r="C10" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>-0.37112855252038468</v>
+      </c>
+      <c r="D10" s="1">
+        <f t="shared" ca="1" si="1"/>
+        <v>0.79763825507779373</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A11">
+        <v>45</v>
+      </c>
+      <c r="B11" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>-1.4239798053678439</v>
+      </c>
+      <c r="C11" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>-0.43765359911835189</v>
+      </c>
+      <c r="D11" s="1">
+        <f t="shared" ca="1" si="1"/>
+        <v>1.2938600084404528</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A12">
+        <v>50</v>
+      </c>
+      <c r="B12" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>-1.2469504098075188</v>
+      </c>
+      <c r="C12" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>1.4708233054126985</v>
+      </c>
+      <c r="D12" s="1">
+        <f t="shared" ca="1" si="1"/>
+        <v>0.57196823818749809</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A13">
+        <v>55</v>
+      </c>
+      <c r="B13" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>1.3450520623942142E-2</v>
+      </c>
+      <c r="C13" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>-0.25696254819741648</v>
+      </c>
+      <c r="D13" s="1">
+        <f t="shared" ca="1" si="1"/>
+        <v>1.3686052126367914</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A14">
+        <v>60</v>
+      </c>
+      <c r="B14" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>0.92572118608364828</v>
+      </c>
+      <c r="C14" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>-0.72809678822133206</v>
+      </c>
+      <c r="D14" s="1">
+        <f t="shared" ca="1" si="1"/>
+        <v>1.4893857173715077</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A15">
+        <v>65</v>
+      </c>
+      <c r="B15" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>0.72200755259222626</v>
+      </c>
+      <c r="C15" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>-0.44393409822588126</v>
+      </c>
+      <c r="D15" s="1">
+        <f t="shared" ca="1" si="1"/>
+        <v>0.74817338681577905</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A16">
+        <v>70</v>
+      </c>
+      <c r="B16" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>3.1391741141383989E-2</v>
+      </c>
+      <c r="C16" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>0.42750792592823172</v>
+      </c>
+      <c r="D16" s="1">
+        <f t="shared" ca="1" si="1"/>
+        <v>1.4672744086126546</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A17">
+        <v>75</v>
+      </c>
+      <c r="B17" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>0.2382846859507386</v>
+      </c>
+      <c r="C17" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>0.44604660049662792</v>
+      </c>
+      <c r="D17" s="1">
+        <f t="shared" ca="1" si="1"/>
+        <v>1.0153545478915063</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A18">
+        <v>80</v>
+      </c>
+      <c r="B18" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>-1.1709593586659048</v>
+      </c>
+      <c r="C18" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>-1.166043018120567</v>
+      </c>
+      <c r="D18" s="1">
+        <f t="shared" ca="1" si="1"/>
+        <v>0.75979551352582397</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A19">
+        <v>85</v>
+      </c>
+      <c r="B19" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>-0.38900694480548847</v>
+      </c>
+      <c r="C19" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>-1.1270511604476803</v>
+      </c>
+      <c r="D19" s="1">
+        <f t="shared" ca="1" si="1"/>
+        <v>0.54328500429812132</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A20">
+        <v>90</v>
+      </c>
+      <c r="B20" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>0.63459610785923593</v>
+      </c>
+      <c r="C20" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>-1.2797201586700422</v>
+      </c>
+      <c r="D20" s="1">
+        <f t="shared" ca="1" si="1"/>
+        <v>1.4006413056104883</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A21">
+        <v>95</v>
+      </c>
+      <c r="B21" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>-1.2513291338282762</v>
+      </c>
+      <c r="C21" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>0.60820401152442871</v>
+      </c>
+      <c r="D21" s="1">
+        <f t="shared" ca="1" si="1"/>
+        <v>1.0022116915064334</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A22">
+        <v>100</v>
+      </c>
+      <c r="B22" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>-0.991046082985517</v>
+      </c>
+      <c r="C22" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>-0.66079057445648914</v>
+      </c>
+      <c r="D22" s="1">
+        <f t="shared" ca="1" si="1"/>
+        <v>1.3431885384415967</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
 </file>
--- a/reference/functions/spline_curve/waypoint.xlsx
+++ b/reference/functions/spline_curve/waypoint.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\acsl_students\Documents\GitHub_subfolder\drone\reference\functions\spline_curve\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{360EDF50-C1A7-49D4-B5B9-8A981B3C0726}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2827643A-ACF6-4883-93E0-7DD306A82401}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5350" yWindow="3480" windowWidth="28800" windowHeight="15370" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -4526,7 +4526,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{97B39A8F-3377-4121-B7E5-7B859139780C}">
-  <dimension ref="A1:D22"/>
+  <dimension ref="A1:D44"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.35">
@@ -4548,357 +4548,663 @@
         <v>0</v>
       </c>
       <c r="B2" s="1">
-        <f ca="1">3*RAND()-1.5</f>
-        <v>-0.20656972819168029</v>
+        <f ca="1">3*RAND()-1</f>
+        <v>0.79514260040494111</v>
       </c>
       <c r="C2" s="1">
         <f ca="1">3*RAND()-1.5</f>
-        <v>-1.3406136721002575</v>
+        <v>0.28839355208060891</v>
       </c>
       <c r="D2" s="1">
-        <f ca="1">1*RAND()+0.5</f>
-        <v>1.3236859624598352</v>
+        <f ca="1">1.5*RAND()+0.3</f>
+        <v>0.71374418136454543</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="B3" s="1">
-        <f t="shared" ref="B3:C22" ca="1" si="0">3*RAND()-1.5</f>
-        <v>0.69046559120738937</v>
+        <f t="shared" ref="B3:B42" ca="1" si="0">3*RAND()-1</f>
+        <v>0.69244334459946311</v>
       </c>
       <c r="C3" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>-0.37813340773252868</v>
+        <f t="shared" ref="C3:C42" ca="1" si="1">3*RAND()-1.5</f>
+        <v>-0.53866880311789633</v>
       </c>
       <c r="D3" s="1">
-        <f t="shared" ref="D3:D22" ca="1" si="1">1*RAND()+0.5</f>
-        <v>0.93113882592089958</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="B4" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>-9.9281512507298997E-2</v>
+        <v>1.2569341820190751</v>
       </c>
       <c r="C4" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>0.49890140332731003</v>
+        <f t="shared" ca="1" si="1"/>
+        <v>-1.1432583419225413</v>
       </c>
       <c r="D4" s="1">
-        <f t="shared" ca="1" si="1"/>
-        <v>1.0595296453461147</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5">
-        <v>15</v>
+        <v>7.5</v>
       </c>
       <c r="B5" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>0.70072717940230245</v>
+        <v>0.98660399518649777</v>
       </c>
       <c r="C5" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>-0.10958936881962056</v>
+        <f t="shared" ca="1" si="1"/>
+        <v>-1.4353254447099326</v>
       </c>
       <c r="D5" s="1">
-        <f t="shared" ca="1" si="1"/>
-        <v>1.4931645300892842</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="B6" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>-1.341385866675983</v>
+        <v>0.45802509789825563</v>
       </c>
       <c r="C6" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>-0.14774989826127483</v>
+        <f t="shared" ca="1" si="1"/>
+        <v>-0.61033153717600308</v>
       </c>
       <c r="D6" s="1">
-        <f t="shared" ca="1" si="1"/>
-        <v>1.1853255523027879</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A7">
-        <v>25</v>
+        <v>12.5</v>
       </c>
       <c r="B7" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>-2.5341526267728121E-3</v>
+        <v>-0.4686101167112926</v>
       </c>
       <c r="C7" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>-1.148482722290229</v>
+        <f t="shared" ca="1" si="1"/>
+        <v>2.9868346262313494E-2</v>
       </c>
       <c r="D7" s="1">
-        <f t="shared" ca="1" si="1"/>
-        <v>0.83442493911182292</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A8">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="B8" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>-0.46937016035644286</v>
+        <v>0.53522586248548465</v>
       </c>
       <c r="C8" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>0.2104030065164666</v>
+        <f t="shared" ca="1" si="1"/>
+        <v>0.31438033538939303</v>
       </c>
       <c r="D8" s="1">
-        <f t="shared" ca="1" si="1"/>
-        <v>1.4710128090833836</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A9">
-        <v>35</v>
+        <v>17.5</v>
       </c>
       <c r="B9" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>-0.43597953674111589</v>
+        <v>5.6892264278400884E-2</v>
       </c>
       <c r="C9" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>0.14806541251177618</v>
+        <f t="shared" ca="1" si="1"/>
+        <v>0.43783989072272078</v>
       </c>
       <c r="D9" s="1">
-        <f t="shared" ca="1" si="1"/>
-        <v>1.4848310816606305</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A10">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="B10" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>0.42464854552823583</v>
+        <v>7.1195321538141343E-2</v>
       </c>
       <c r="C10" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>-0.37112855252038468</v>
+        <f t="shared" ca="1" si="1"/>
+        <v>0.1926492178871213</v>
       </c>
       <c r="D10" s="1">
-        <f t="shared" ca="1" si="1"/>
-        <v>0.79763825507779373</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A11">
-        <v>45</v>
+        <v>22.5</v>
       </c>
       <c r="B11" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>-1.4239798053678439</v>
+        <v>0.7174969547919996</v>
       </c>
       <c r="C11" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>-0.43765359911835189</v>
+        <f t="shared" ca="1" si="1"/>
+        <v>0.50146421929380747</v>
       </c>
       <c r="D11" s="1">
-        <f t="shared" ca="1" si="1"/>
-        <v>1.2938600084404528</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A12">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="B12" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>-1.2469504098075188</v>
+        <v>0.76379489834499426</v>
       </c>
       <c r="C12" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>1.4708233054126985</v>
+        <f t="shared" ca="1" si="1"/>
+        <v>1.2947332050364255</v>
       </c>
       <c r="D12" s="1">
-        <f t="shared" ca="1" si="1"/>
-        <v>0.57196823818749809</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A13">
-        <v>55</v>
+        <v>27.5</v>
       </c>
       <c r="B13" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>1.3450520623942142E-2</v>
+        <v>0.95851693019514039</v>
       </c>
       <c r="C13" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>-0.25696254819741648</v>
+        <f t="shared" ca="1" si="1"/>
+        <v>0.87080061904923767</v>
       </c>
       <c r="D13" s="1">
-        <f t="shared" ca="1" si="1"/>
-        <v>1.3686052126367914</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A14">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="B14" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>0.92572118608364828</v>
+        <v>1.0357759961119064</v>
       </c>
       <c r="C14" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>-0.72809678822133206</v>
+        <f t="shared" ca="1" si="1"/>
+        <v>-0.28900261996549315</v>
       </c>
       <c r="D14" s="1">
-        <f t="shared" ca="1" si="1"/>
-        <v>1.4893857173715077</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A15">
-        <v>65</v>
+        <v>32.5</v>
       </c>
       <c r="B15" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>0.72200755259222626</v>
+        <v>1.4471223969292377</v>
       </c>
       <c r="C15" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>-0.44393409822588126</v>
+        <f t="shared" ca="1" si="1"/>
+        <v>7.0045820680657345E-2</v>
       </c>
       <c r="D15" s="1">
-        <f t="shared" ca="1" si="1"/>
-        <v>0.74817338681577905</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A16">
-        <v>70</v>
+        <v>35</v>
       </c>
       <c r="B16" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>3.1391741141383989E-2</v>
+        <v>1.1708305072784069</v>
       </c>
       <c r="C16" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>0.42750792592823172</v>
+        <f t="shared" ca="1" si="1"/>
+        <v>-0.84083446292879904</v>
       </c>
       <c r="D16" s="1">
-        <f t="shared" ca="1" si="1"/>
-        <v>1.4672744086126546</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A17">
-        <v>75</v>
+        <v>37.5</v>
       </c>
       <c r="B17" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>0.2382846859507386</v>
+        <v>0.61312677940697968</v>
       </c>
       <c r="C17" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>0.44604660049662792</v>
+        <f t="shared" ca="1" si="1"/>
+        <v>-0.3895606123480313</v>
       </c>
       <c r="D17" s="1">
-        <f t="shared" ca="1" si="1"/>
-        <v>1.0153545478915063</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A18">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="B18" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>-1.1709593586659048</v>
+        <v>1.038448490717748</v>
       </c>
       <c r="C18" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>-1.166043018120567</v>
+        <f t="shared" ca="1" si="1"/>
+        <v>0.85468578171283127</v>
       </c>
       <c r="D18" s="1">
-        <f t="shared" ca="1" si="1"/>
-        <v>0.75979551352582397</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A19">
-        <v>85</v>
+        <v>42.5</v>
       </c>
       <c r="B19" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>-0.38900694480548847</v>
+        <v>-0.40664929446432185</v>
       </c>
       <c r="C19" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>-1.1270511604476803</v>
+        <f t="shared" ca="1" si="1"/>
+        <v>0.24483243431539781</v>
       </c>
       <c r="D19" s="1">
-        <f t="shared" ca="1" si="1"/>
-        <v>0.54328500429812132</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A20">
-        <v>90</v>
+        <v>45</v>
       </c>
       <c r="B20" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>0.63459610785923593</v>
+        <v>-0.43287833195767078</v>
       </c>
       <c r="C20" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>-1.2797201586700422</v>
+        <f t="shared" ca="1" si="1"/>
+        <v>-0.41950736047213422</v>
       </c>
       <c r="D20" s="1">
-        <f t="shared" ca="1" si="1"/>
-        <v>1.4006413056104883</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A21">
-        <v>95</v>
+        <v>47.5</v>
       </c>
       <c r="B21" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>-1.2513291338282762</v>
+        <v>1.308712205127982</v>
       </c>
       <c r="C21" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>0.60820401152442871</v>
+        <f t="shared" ca="1" si="1"/>
+        <v>-1.3183711776036593</v>
       </c>
       <c r="D21" s="1">
-        <f t="shared" ca="1" si="1"/>
-        <v>1.0022116915064334</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A22">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="B22" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>-0.991046082985517</v>
+        <v>-0.75150849713559753</v>
       </c>
       <c r="C22" s="1">
+        <f t="shared" ca="1" si="1"/>
+        <v>-0.76544003416511497</v>
+      </c>
+      <c r="D22" s="1">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A23">
+        <v>52.5</v>
+      </c>
+      <c r="B23" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>-0.66079057445648914</v>
-      </c>
-      <c r="D22" s="1">
+        <v>1.2352648758627773</v>
+      </c>
+      <c r="C23" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>1.3431885384415967</v>
-      </c>
+        <v>-0.62146488119173704</v>
+      </c>
+      <c r="D23" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A24">
+        <v>55</v>
+      </c>
+      <c r="B24" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>0.89587189832200509</v>
+      </c>
+      <c r="C24" s="1">
+        <f t="shared" ca="1" si="1"/>
+        <v>-0.39791984038247041</v>
+      </c>
+      <c r="D24" s="1">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A25">
+        <v>57.5</v>
+      </c>
+      <c r="B25" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>0.59229831901169971</v>
+      </c>
+      <c r="C25" s="1">
+        <f t="shared" ca="1" si="1"/>
+        <v>-0.81644197776365779</v>
+      </c>
+      <c r="D25" s="1">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A26">
+        <v>60</v>
+      </c>
+      <c r="B26" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>-0.79404955840331115</v>
+      </c>
+      <c r="C26" s="1">
+        <f t="shared" ca="1" si="1"/>
+        <v>-0.17702106599498668</v>
+      </c>
+      <c r="D26" s="1">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A27">
+        <v>62.5</v>
+      </c>
+      <c r="B27" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>-0.50575979403399429</v>
+      </c>
+      <c r="C27" s="1">
+        <f t="shared" ca="1" si="1"/>
+        <v>1.2124442313583383</v>
+      </c>
+      <c r="D27" s="1">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A28">
+        <v>65</v>
+      </c>
+      <c r="B28" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>1.5804886278953556</v>
+      </c>
+      <c r="C28" s="1">
+        <f t="shared" ca="1" si="1"/>
+        <v>-1.3296398441606727</v>
+      </c>
+      <c r="D28" s="1">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A29">
+        <v>67.5</v>
+      </c>
+      <c r="B29" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>0.25591750899825816</v>
+      </c>
+      <c r="C29" s="1">
+        <f t="shared" ca="1" si="1"/>
+        <v>0.5744033305578311</v>
+      </c>
+      <c r="D29" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A30">
+        <v>70</v>
+      </c>
+      <c r="B30" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>0.56539596868405573</v>
+      </c>
+      <c r="C30" s="1">
+        <f t="shared" ca="1" si="1"/>
+        <v>-2.2430049319156264E-2</v>
+      </c>
+      <c r="D30" s="1">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A31">
+        <v>72.5</v>
+      </c>
+      <c r="B31" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>0.71470378955272418</v>
+      </c>
+      <c r="C31" s="1">
+        <f t="shared" ca="1" si="1"/>
+        <v>1.3432974264984763</v>
+      </c>
+      <c r="D31" s="1">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A32">
+        <v>75</v>
+      </c>
+      <c r="B32" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>-0.23686939455264033</v>
+      </c>
+      <c r="C32" s="1">
+        <f t="shared" ca="1" si="1"/>
+        <v>0.65945987951427476</v>
+      </c>
+      <c r="D32" s="1">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A33">
+        <v>77.5</v>
+      </c>
+      <c r="B33" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>-0.48674691052005536</v>
+      </c>
+      <c r="C33" s="1">
+        <f t="shared" ca="1" si="1"/>
+        <v>-0.93081348490575211</v>
+      </c>
+      <c r="D33" s="1">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A34">
+        <v>80</v>
+      </c>
+      <c r="B34" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>-4.9583502910854671E-2</v>
+      </c>
+      <c r="C34" s="1">
+        <f t="shared" ca="1" si="1"/>
+        <v>1.2156521056323508</v>
+      </c>
+      <c r="D34" s="1">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A35">
+        <v>82.5</v>
+      </c>
+      <c r="B35" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>1.7021276506631766E-2</v>
+      </c>
+      <c r="C35" s="1">
+        <f t="shared" ca="1" si="1"/>
+        <v>-0.52224461837489589</v>
+      </c>
+      <c r="D35" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A36">
+        <v>85</v>
+      </c>
+      <c r="B36" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>0.17643470572080622</v>
+      </c>
+      <c r="C36" s="1">
+        <f t="shared" ca="1" si="1"/>
+        <v>-0.63495180660013983</v>
+      </c>
+      <c r="D36" s="1">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A37">
+        <v>87.5</v>
+      </c>
+      <c r="B37" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>1.8005860323732645</v>
+      </c>
+      <c r="C37" s="1">
+        <f t="shared" ca="1" si="1"/>
+        <v>-1.3769233710833411</v>
+      </c>
+      <c r="D37" s="1">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A38">
+        <v>90</v>
+      </c>
+      <c r="B38" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>0.38665916581585158</v>
+      </c>
+      <c r="C38" s="1">
+        <f t="shared" ca="1" si="1"/>
+        <v>-0.43809888782331963</v>
+      </c>
+      <c r="D38" s="1">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A39">
+        <v>92.5</v>
+      </c>
+      <c r="B39" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>1.8523399805593215</v>
+      </c>
+      <c r="C39" s="1">
+        <f t="shared" ca="1" si="1"/>
+        <v>0.44379356359803501</v>
+      </c>
+      <c r="D39" s="1">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A40">
+        <v>95</v>
+      </c>
+      <c r="B40" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>-0.43151134332202967</v>
+      </c>
+      <c r="C40" s="1">
+        <f t="shared" ca="1" si="1"/>
+        <v>-0.18992023137082681</v>
+      </c>
+      <c r="D40" s="1">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A41">
+        <v>97.5</v>
+      </c>
+      <c r="B41" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>0.57625419019474644</v>
+      </c>
+      <c r="C41" s="1">
+        <f t="shared" ca="1" si="1"/>
+        <v>-0.38617779424245846</v>
+      </c>
+      <c r="D41" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A42">
+        <v>100</v>
+      </c>
+      <c r="B42" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>1.6690287961223262</v>
+      </c>
+      <c r="C42" s="1">
+        <f t="shared" ca="1" si="1"/>
+        <v>0.5738753001134409</v>
+      </c>
+      <c r="D42" s="1">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="D43" s="1"/>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="D44" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>

--- a/reference/functions/spline_curve/waypoint.xlsx
+++ b/reference/functions/spline_curve/waypoint.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\acsl_students\Documents\GitHub_subfolder\drone\reference\functions\spline_curve\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2827643A-ACF6-4883-93E0-7DD306A82401}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8B08C2C-65AD-43CE-9B6C-26B763A01206}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5350" yWindow="3480" windowWidth="28800" windowHeight="15370" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4970" yWindow="4040" windowWidth="28800" windowHeight="15370" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -4526,7 +4526,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{97B39A8F-3377-4121-B7E5-7B859139780C}">
-  <dimension ref="A1:D44"/>
+  <dimension ref="A1:D46"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.35">
@@ -4549,15 +4549,15 @@
       </c>
       <c r="B2" s="1">
         <f ca="1">3*RAND()-1</f>
-        <v>0.79514260040494111</v>
+        <v>0.33919346262007632</v>
       </c>
       <c r="C2" s="1">
         <f ca="1">3*RAND()-1.5</f>
-        <v>0.28839355208060891</v>
+        <v>-0.9270856993356974</v>
       </c>
       <c r="D2" s="1">
         <f ca="1">1.5*RAND()+0.3</f>
-        <v>0.71374418136454543</v>
+        <v>1.6704227363807138</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.35">
@@ -4566,11 +4566,11 @@
       </c>
       <c r="B3" s="1">
         <f t="shared" ref="B3:B42" ca="1" si="0">3*RAND()-1</f>
-        <v>0.69244334459946311</v>
+        <v>0.3003047163371293</v>
       </c>
       <c r="C3" s="1">
         <f t="shared" ref="C3:C42" ca="1" si="1">3*RAND()-1.5</f>
-        <v>-0.53866880311789633</v>
+        <v>0.25064912753665336</v>
       </c>
       <c r="D3" s="1">
         <v>0.4</v>
@@ -4582,14 +4582,14 @@
       </c>
       <c r="B4" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>1.2569341820190751</v>
+        <v>-0.77423528856881763</v>
       </c>
       <c r="C4" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>-1.1432583419225413</v>
+        <v>-0.97442248846360691</v>
       </c>
       <c r="D4" s="1">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.35">
@@ -4598,14 +4598,14 @@
       </c>
       <c r="B5" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>0.98660399518649777</v>
+        <v>1.0326069744126478</v>
       </c>
       <c r="C5" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>-1.4353254447099326</v>
+        <v>-0.58774450982772009</v>
       </c>
       <c r="D5" s="1">
-        <v>1</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.35">
@@ -4614,14 +4614,14 @@
       </c>
       <c r="B6" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>0.45802509789825563</v>
+        <v>-0.92144988011367279</v>
       </c>
       <c r="C6" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>-0.61033153717600308</v>
+        <v>-0.56617557718838118</v>
       </c>
       <c r="D6" s="1">
-        <v>0.4</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.35">
@@ -4630,14 +4630,14 @@
       </c>
       <c r="B7" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>-0.4686101167112926</v>
+        <v>-0.31978343957785471</v>
       </c>
       <c r="C7" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>2.9868346262313494E-2</v>
+        <v>-0.25845298416836471</v>
       </c>
       <c r="D7" s="1">
-        <v>1.4</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.35">
@@ -4646,14 +4646,14 @@
       </c>
       <c r="B8" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>0.53522586248548465</v>
+        <v>-0.12373168187714667</v>
       </c>
       <c r="C8" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>0.31438033538939303</v>
+        <v>0.57793859340073661</v>
       </c>
       <c r="D8" s="1">
-        <v>0.5</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.35">
@@ -4662,11 +4662,11 @@
       </c>
       <c r="B9" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>5.6892264278400884E-2</v>
+        <v>-8.7305246182274199E-2</v>
       </c>
       <c r="C9" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>0.43783989072272078</v>
+        <v>0.95208942583918166</v>
       </c>
       <c r="D9" s="1">
         <v>0.4</v>
@@ -4678,14 +4678,14 @@
       </c>
       <c r="B10" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>7.1195321538141343E-2</v>
+        <v>1.384419500854583</v>
       </c>
       <c r="C10" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>0.1926492178871213</v>
+        <v>1.1808392882437309</v>
       </c>
       <c r="D10" s="1">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.35">
@@ -4694,14 +4694,14 @@
       </c>
       <c r="B11" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>0.7174969547919996</v>
+        <v>-0.44639219933878105</v>
       </c>
       <c r="C11" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>0.50146421929380747</v>
+        <v>0.80738244483807264</v>
       </c>
       <c r="D11" s="1">
-        <v>1</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.35">
@@ -4710,14 +4710,14 @@
       </c>
       <c r="B12" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>0.76379489834499426</v>
+        <v>0.99728098894127859</v>
       </c>
       <c r="C12" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>1.2947332050364255</v>
+        <v>0.30257795548666344</v>
       </c>
       <c r="D12" s="1">
-        <v>0.4</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.35">
@@ -4726,14 +4726,14 @@
       </c>
       <c r="B13" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>0.95851693019514039</v>
+        <v>-0.52502608736273104</v>
       </c>
       <c r="C13" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>0.87080061904923767</v>
+        <v>-0.4898998123545919</v>
       </c>
       <c r="D13" s="1">
-        <v>1.4</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.35">
@@ -4742,14 +4742,14 @@
       </c>
       <c r="B14" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>1.0357759961119064</v>
+        <v>0.88847115412327193</v>
       </c>
       <c r="C14" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>-0.28900261996549315</v>
+        <v>-0.47052990720371968</v>
       </c>
       <c r="D14" s="1">
-        <v>0.5</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.35">
@@ -4758,11 +4758,11 @@
       </c>
       <c r="B15" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>1.4471223969292377</v>
+        <v>1.7661384059197953</v>
       </c>
       <c r="C15" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>7.0045820680657345E-2</v>
+        <v>-0.28201475486120575</v>
       </c>
       <c r="D15" s="1">
         <v>0.4</v>
@@ -4774,14 +4774,14 @@
       </c>
       <c r="B16" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>1.1708305072784069</v>
+        <v>1.1917256713847926</v>
       </c>
       <c r="C16" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>-0.84083446292879904</v>
+        <v>1.3050669194953168</v>
       </c>
       <c r="D16" s="1">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.35">
@@ -4790,14 +4790,14 @@
       </c>
       <c r="B17" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>0.61312677940697968</v>
+        <v>0.28171202501755532</v>
       </c>
       <c r="C17" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>-0.3895606123480313</v>
+        <v>1.0674341108694341</v>
       </c>
       <c r="D17" s="1">
-        <v>1</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.35">
@@ -4806,14 +4806,14 @@
       </c>
       <c r="B18" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>1.038448490717748</v>
+        <v>1.1998402915673347</v>
       </c>
       <c r="C18" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>0.85468578171283127</v>
+        <v>0.41769695870888457</v>
       </c>
       <c r="D18" s="1">
-        <v>0.4</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.35">
@@ -4822,14 +4822,14 @@
       </c>
       <c r="B19" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>-0.40664929446432185</v>
+        <v>-0.62373972832389479</v>
       </c>
       <c r="C19" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>0.24483243431539781</v>
+        <v>1.0970799194460299</v>
       </c>
       <c r="D19" s="1">
-        <v>1.4</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.35">
@@ -4838,14 +4838,14 @@
       </c>
       <c r="B20" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>-0.43287833195767078</v>
+        <v>-0.96713950791988756</v>
       </c>
       <c r="C20" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>-0.41950736047213422</v>
+        <v>0.59928133151104701</v>
       </c>
       <c r="D20" s="1">
-        <v>0.5</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.35">
@@ -4854,11 +4854,11 @@
       </c>
       <c r="B21" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>1.308712205127982</v>
+        <v>0.59013163568793425</v>
       </c>
       <c r="C21" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>-1.3183711776036593</v>
+        <v>1.4327852963513896</v>
       </c>
       <c r="D21" s="1">
         <v>0.4</v>
@@ -4870,14 +4870,14 @@
       </c>
       <c r="B22" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>-0.75150849713559753</v>
+        <v>0.22425001215507079</v>
       </c>
       <c r="C22" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>-0.76544003416511497</v>
+        <v>-5.6920440893958535E-2</v>
       </c>
       <c r="D22" s="1">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.35">
@@ -4886,14 +4886,14 @@
       </c>
       <c r="B23" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>1.2352648758627773</v>
+        <v>-0.86075974450040826</v>
       </c>
       <c r="C23" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>-0.62146488119173704</v>
+        <v>-0.49115446459475098</v>
       </c>
       <c r="D23" s="1">
-        <v>1</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.35">
@@ -4902,14 +4902,14 @@
       </c>
       <c r="B24" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>0.89587189832200509</v>
+        <v>0.40770556401031044</v>
       </c>
       <c r="C24" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>-0.39791984038247041</v>
+        <v>-1.311567376500822</v>
       </c>
       <c r="D24" s="1">
-        <v>0.4</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.35">
@@ -4918,14 +4918,14 @@
       </c>
       <c r="B25" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>0.59229831901169971</v>
+        <v>0.10106333509088561</v>
       </c>
       <c r="C25" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>-0.81644197776365779</v>
+        <v>-0.13187944678243646</v>
       </c>
       <c r="D25" s="1">
-        <v>1.4</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.35">
@@ -4934,14 +4934,14 @@
       </c>
       <c r="B26" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>-0.79404955840331115</v>
+        <v>0.30047094176163514</v>
       </c>
       <c r="C26" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>-0.17702106599498668</v>
+        <v>1.3007264295176801</v>
       </c>
       <c r="D26" s="1">
-        <v>0.5</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.35">
@@ -4950,11 +4950,11 @@
       </c>
       <c r="B27" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>-0.50575979403399429</v>
+        <v>1.0450411931726156</v>
       </c>
       <c r="C27" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>1.2124442313583383</v>
+        <v>0.98840306576251979</v>
       </c>
       <c r="D27" s="1">
         <v>0.4</v>
@@ -4966,14 +4966,14 @@
       </c>
       <c r="B28" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>1.5804886278953556</v>
+        <v>1.2772718436709658</v>
       </c>
       <c r="C28" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>-1.3296398441606727</v>
+        <v>1.4334494636392328</v>
       </c>
       <c r="D28" s="1">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.35">
@@ -4982,14 +4982,14 @@
       </c>
       <c r="B29" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>0.25591750899825816</v>
+        <v>-0.84485604190394259</v>
       </c>
       <c r="C29" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>0.5744033305578311</v>
+        <v>0.93686728096651839</v>
       </c>
       <c r="D29" s="1">
-        <v>1</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.35">
@@ -4998,14 +4998,14 @@
       </c>
       <c r="B30" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>0.56539596868405573</v>
+        <v>-0.69041605321922139</v>
       </c>
       <c r="C30" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>-2.2430049319156264E-2</v>
+        <v>0.75700252623686071</v>
       </c>
       <c r="D30" s="1">
-        <v>0.4</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.35">
@@ -5014,14 +5014,14 @@
       </c>
       <c r="B31" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>0.71470378955272418</v>
+        <v>-4.343467756951902E-2</v>
       </c>
       <c r="C31" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>1.3432974264984763</v>
+        <v>-0.80609403506243893</v>
       </c>
       <c r="D31" s="1">
-        <v>1.4</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.35">
@@ -5030,14 +5030,14 @@
       </c>
       <c r="B32" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>-0.23686939455264033</v>
+        <v>0.43635931562836827</v>
       </c>
       <c r="C32" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>0.65945987951427476</v>
+        <v>0.52385325550687822</v>
       </c>
       <c r="D32" s="1">
-        <v>0.5</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.35">
@@ -5046,11 +5046,11 @@
       </c>
       <c r="B33" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>-0.48674691052005536</v>
+        <v>0.17101663162385128</v>
       </c>
       <c r="C33" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>-0.93081348490575211</v>
+        <v>-1.0188909375948294</v>
       </c>
       <c r="D33" s="1">
         <v>0.4</v>
@@ -5062,14 +5062,14 @@
       </c>
       <c r="B34" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>-4.9583502910854671E-2</v>
+        <v>0.24159714204280824</v>
       </c>
       <c r="C34" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>1.2156521056323508</v>
+        <v>-0.67752908007084167</v>
       </c>
       <c r="D34" s="1">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.35">
@@ -5078,14 +5078,14 @@
       </c>
       <c r="B35" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>1.7021276506631766E-2</v>
+        <v>0.31268633282349878</v>
       </c>
       <c r="C35" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>-0.52224461837489589</v>
+        <v>-1.4852799905951359</v>
       </c>
       <c r="D35" s="1">
-        <v>1</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.35">
@@ -5094,14 +5094,14 @@
       </c>
       <c r="B36" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>0.17643470572080622</v>
+        <v>1.2253028315994885</v>
       </c>
       <c r="C36" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>-0.63495180660013983</v>
+        <v>1.3029837418057393</v>
       </c>
       <c r="D36" s="1">
-        <v>0.4</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.35">
@@ -5110,14 +5110,14 @@
       </c>
       <c r="B37" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>1.8005860323732645</v>
+        <v>0.64149525458830281</v>
       </c>
       <c r="C37" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>-1.3769233710833411</v>
+        <v>0.28854879035749303</v>
       </c>
       <c r="D37" s="1">
-        <v>1.4</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.35">
@@ -5126,14 +5126,14 @@
       </c>
       <c r="B38" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>0.38665916581585158</v>
+        <v>1.8534438132424271</v>
       </c>
       <c r="C38" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>-0.43809888782331963</v>
+        <v>0.86259065266501533</v>
       </c>
       <c r="D38" s="1">
-        <v>0.5</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.35">
@@ -5142,11 +5142,11 @@
       </c>
       <c r="B39" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>1.8523399805593215</v>
+        <v>0.74239259793747525</v>
       </c>
       <c r="C39" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>0.44379356359803501</v>
+        <v>1.1000570843594577</v>
       </c>
       <c r="D39" s="1">
         <v>0.4</v>
@@ -5158,14 +5158,14 @@
       </c>
       <c r="B40" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>-0.43151134332202967</v>
+        <v>1.4713523203831733</v>
       </c>
       <c r="C40" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>-0.18992023137082681</v>
+        <v>1.216983812760271</v>
       </c>
       <c r="D40" s="1">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.35">
@@ -5174,14 +5174,14 @@
       </c>
       <c r="B41" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>0.57625419019474644</v>
+        <v>0.80296586854118024</v>
       </c>
       <c r="C41" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>-0.38617779424245846</v>
+        <v>-0.1051794287131318</v>
       </c>
       <c r="D41" s="1">
-        <v>1</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.35">
@@ -5190,14 +5190,14 @@
       </c>
       <c r="B42" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>1.6690287961223262</v>
+        <v>0.8909740812019824</v>
       </c>
       <c r="C42" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>0.5738753001134409</v>
+        <v>-0.93327754073680624</v>
       </c>
       <c r="D42" s="1">
-        <v>0.4</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.35">
@@ -5205,6 +5205,12 @@
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.35">
       <c r="D44" s="1"/>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="D45" s="1"/>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="D46" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
